--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A384674-DF73-4BE2-AD1A-0BFF30EC3497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5765BE-F1E5-407F-8126-16C1A5DA323E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="19" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="20" r:id="rId2"/>
-    <sheet name="【リクエストID】_クラス単体テスト" sheetId="26" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="25" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="24" r:id="rId5"/>
+    <sheet name="【テストターゲット名】_クラス単体" sheetId="26" r:id="rId3"/>
+    <sheet name="【リクエストID】_リクエスト単体" sheetId="25" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="24" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$382</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$382</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="565">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -7665,6 +7665,10 @@
   </si>
   <si>
     <t>5-4-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8900,84 +8904,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9084,6 +9010,84 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10539,55 +10543,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="172" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="207" t="s">
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="177"/>
+      <c r="O1" s="181" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="208"/>
-      <c r="Q1" s="208"/>
-      <c r="R1" s="209"/>
-      <c r="S1" s="216" t="s">
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="190" t="s">
         <v>70</v>
       </c>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="198" t="s">
+      <c r="T1" s="191"/>
+      <c r="U1" s="191"/>
+      <c r="V1" s="191"/>
+      <c r="W1" s="191"/>
+      <c r="X1" s="191"/>
+      <c r="Y1" s="191"/>
+      <c r="Z1" s="192"/>
+      <c r="AA1" s="172" t="s">
         <v>59</v>
       </c>
-      <c r="AB1" s="200"/>
-      <c r="AC1" s="225" t="str">
+      <c r="AB1" s="174"/>
+      <c r="AC1" s="199" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="226"/>
-      <c r="AE1" s="226"/>
-      <c r="AF1" s="227"/>
-      <c r="AG1" s="192" t="str">
+      <c r="AD1" s="200"/>
+      <c r="AE1" s="200"/>
+      <c r="AF1" s="201"/>
+      <c r="AG1" s="166" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="193"/>
-      <c r="AI1" s="194"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -10595,51 +10599,51 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="198" t="s">
+      <c r="A2" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="202"/>
-      <c r="J2" s="202"/>
-      <c r="K2" s="202"/>
-      <c r="L2" s="202"/>
-      <c r="M2" s="202"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="210"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="212"/>
-      <c r="S2" s="219"/>
-      <c r="T2" s="220"/>
-      <c r="U2" s="220"/>
-      <c r="V2" s="220"/>
-      <c r="W2" s="220"/>
-      <c r="X2" s="220"/>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="198" t="s">
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
+      <c r="N2" s="177"/>
+      <c r="O2" s="184"/>
+      <c r="P2" s="185"/>
+      <c r="Q2" s="185"/>
+      <c r="R2" s="186"/>
+      <c r="S2" s="193"/>
+      <c r="T2" s="194"/>
+      <c r="U2" s="194"/>
+      <c r="V2" s="194"/>
+      <c r="W2" s="194"/>
+      <c r="X2" s="194"/>
+      <c r="Y2" s="194"/>
+      <c r="Z2" s="195"/>
+      <c r="AA2" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="AB2" s="200"/>
-      <c r="AC2" s="204" t="str">
+      <c r="AB2" s="174"/>
+      <c r="AC2" s="178" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="205"/>
-      <c r="AE2" s="205"/>
-      <c r="AF2" s="206"/>
-      <c r="AG2" s="192" t="str">
+      <c r="AD2" s="179"/>
+      <c r="AE2" s="179"/>
+      <c r="AF2" s="180"/>
+      <c r="AG2" s="166" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="193"/>
-      <c r="AI2" s="194"/>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -10647,43 +10651,43 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="198" t="s">
+      <c r="A3" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="202"/>
-      <c r="M3" s="202"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="214"/>
-      <c r="R3" s="215"/>
-      <c r="S3" s="222"/>
-      <c r="T3" s="223"/>
-      <c r="U3" s="223"/>
-      <c r="V3" s="223"/>
-      <c r="W3" s="223"/>
-      <c r="X3" s="223"/>
-      <c r="Y3" s="223"/>
-      <c r="Z3" s="224"/>
-      <c r="AA3" s="198"/>
-      <c r="AB3" s="200"/>
-      <c r="AC3" s="225"/>
-      <c r="AD3" s="226"/>
-      <c r="AE3" s="226"/>
-      <c r="AF3" s="227"/>
-      <c r="AG3" s="192"/>
-      <c r="AH3" s="193"/>
-      <c r="AI3" s="194"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="173"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="176"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="188"/>
+      <c r="Q3" s="188"/>
+      <c r="R3" s="189"/>
+      <c r="S3" s="196"/>
+      <c r="T3" s="197"/>
+      <c r="U3" s="197"/>
+      <c r="V3" s="197"/>
+      <c r="W3" s="197"/>
+      <c r="X3" s="197"/>
+      <c r="Y3" s="197"/>
+      <c r="Z3" s="198"/>
+      <c r="AA3" s="172"/>
+      <c r="AB3" s="174"/>
+      <c r="AC3" s="199"/>
+      <c r="AD3" s="200"/>
+      <c r="AE3" s="200"/>
+      <c r="AF3" s="201"/>
+      <c r="AG3" s="166"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -10720,1020 +10724,1176 @@
       <c r="A7" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="169" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="196"/>
-      <c r="D7" s="195" t="s">
+      <c r="C7" s="170"/>
+      <c r="D7" s="169" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="197"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="195" t="s">
+      <c r="E7" s="171"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="197"/>
-      <c r="I7" s="196"/>
-      <c r="J7" s="195" t="s">
+      <c r="H7" s="171"/>
+      <c r="I7" s="170"/>
+      <c r="J7" s="169" t="s">
         <v>67</v>
       </c>
-      <c r="K7" s="197"/>
-      <c r="L7" s="197"/>
-      <c r="M7" s="197"/>
-      <c r="N7" s="197"/>
-      <c r="O7" s="197"/>
-      <c r="P7" s="196"/>
-      <c r="Q7" s="195" t="s">
+      <c r="K7" s="171"/>
+      <c r="L7" s="171"/>
+      <c r="M7" s="171"/>
+      <c r="N7" s="171"/>
+      <c r="O7" s="171"/>
+      <c r="P7" s="170"/>
+      <c r="Q7" s="169" t="s">
         <v>68</v>
       </c>
-      <c r="R7" s="197"/>
-      <c r="S7" s="197"/>
-      <c r="T7" s="197"/>
-      <c r="U7" s="197"/>
-      <c r="V7" s="197"/>
-      <c r="W7" s="197"/>
-      <c r="X7" s="197"/>
-      <c r="Y7" s="197"/>
-      <c r="Z7" s="197"/>
-      <c r="AA7" s="197"/>
-      <c r="AB7" s="197"/>
-      <c r="AC7" s="197"/>
-      <c r="AD7" s="197"/>
-      <c r="AE7" s="196"/>
-      <c r="AF7" s="195" t="s">
+      <c r="R7" s="171"/>
+      <c r="S7" s="171"/>
+      <c r="T7" s="171"/>
+      <c r="U7" s="171"/>
+      <c r="V7" s="171"/>
+      <c r="W7" s="171"/>
+      <c r="X7" s="171"/>
+      <c r="Y7" s="171"/>
+      <c r="Z7" s="171"/>
+      <c r="AA7" s="171"/>
+      <c r="AB7" s="171"/>
+      <c r="AC7" s="171"/>
+      <c r="AD7" s="171"/>
+      <c r="AE7" s="170"/>
+      <c r="AF7" s="169" t="s">
         <v>69</v>
       </c>
-      <c r="AG7" s="197"/>
-      <c r="AH7" s="197"/>
-      <c r="AI7" s="196"/>
+      <c r="AG7" s="171"/>
+      <c r="AH7" s="171"/>
+      <c r="AI7" s="170"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="21"/>
-      <c r="B8" s="179"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="181"/>
-      <c r="E8" s="182"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="184"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="186"/>
-      <c r="K8" s="187"/>
-      <c r="L8" s="187"/>
-      <c r="M8" s="187"/>
-      <c r="N8" s="187"/>
-      <c r="O8" s="187"/>
-      <c r="P8" s="188"/>
-      <c r="Q8" s="189"/>
-      <c r="R8" s="190"/>
-      <c r="S8" s="190"/>
-      <c r="T8" s="190"/>
-      <c r="U8" s="190"/>
-      <c r="V8" s="190"/>
-      <c r="W8" s="190"/>
-      <c r="X8" s="190"/>
-      <c r="Y8" s="190"/>
-      <c r="Z8" s="190"/>
-      <c r="AA8" s="190"/>
-      <c r="AB8" s="190"/>
-      <c r="AC8" s="190"/>
-      <c r="AD8" s="190"/>
-      <c r="AE8" s="191"/>
-      <c r="AF8" s="186"/>
-      <c r="AG8" s="187"/>
-      <c r="AH8" s="187"/>
-      <c r="AI8" s="188"/>
+      <c r="B8" s="214"/>
+      <c r="C8" s="215"/>
+      <c r="D8" s="216"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="219"/>
+      <c r="H8" s="220"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="221"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="222"/>
+      <c r="M8" s="222"/>
+      <c r="N8" s="222"/>
+      <c r="O8" s="222"/>
+      <c r="P8" s="223"/>
+      <c r="Q8" s="224"/>
+      <c r="R8" s="225"/>
+      <c r="S8" s="225"/>
+      <c r="T8" s="225"/>
+      <c r="U8" s="225"/>
+      <c r="V8" s="225"/>
+      <c r="W8" s="225"/>
+      <c r="X8" s="225"/>
+      <c r="Y8" s="225"/>
+      <c r="Z8" s="225"/>
+      <c r="AA8" s="225"/>
+      <c r="AB8" s="225"/>
+      <c r="AC8" s="225"/>
+      <c r="AD8" s="225"/>
+      <c r="AE8" s="226"/>
+      <c r="AF8" s="221"/>
+      <c r="AG8" s="222"/>
+      <c r="AH8" s="222"/>
+      <c r="AI8" s="223"/>
     </row>
     <row r="9" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="22"/>
-      <c r="B9" s="166"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="169"/>
-      <c r="F9" s="170"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="171"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="172"/>
-      <c r="K9" s="173"/>
-      <c r="L9" s="173"/>
-      <c r="M9" s="173"/>
-      <c r="N9" s="173"/>
-      <c r="O9" s="173"/>
-      <c r="P9" s="174"/>
-      <c r="Q9" s="175"/>
-      <c r="R9" s="176"/>
-      <c r="S9" s="176"/>
-      <c r="T9" s="176"/>
-      <c r="U9" s="176"/>
-      <c r="V9" s="176"/>
-      <c r="W9" s="176"/>
-      <c r="X9" s="176"/>
-      <c r="Y9" s="176"/>
-      <c r="Z9" s="176"/>
-      <c r="AA9" s="176"/>
-      <c r="AB9" s="176"/>
-      <c r="AC9" s="176"/>
-      <c r="AD9" s="176"/>
-      <c r="AE9" s="177"/>
-      <c r="AF9" s="172"/>
-      <c r="AG9" s="173"/>
-      <c r="AH9" s="173"/>
-      <c r="AI9" s="174"/>
+      <c r="B9" s="202"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="204"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="204"/>
+      <c r="H9" s="207"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="208"/>
+      <c r="K9" s="209"/>
+      <c r="L9" s="209"/>
+      <c r="M9" s="209"/>
+      <c r="N9" s="209"/>
+      <c r="O9" s="209"/>
+      <c r="P9" s="210"/>
+      <c r="Q9" s="211"/>
+      <c r="R9" s="212"/>
+      <c r="S9" s="212"/>
+      <c r="T9" s="212"/>
+      <c r="U9" s="212"/>
+      <c r="V9" s="212"/>
+      <c r="W9" s="212"/>
+      <c r="X9" s="212"/>
+      <c r="Y9" s="212"/>
+      <c r="Z9" s="212"/>
+      <c r="AA9" s="212"/>
+      <c r="AB9" s="212"/>
+      <c r="AC9" s="212"/>
+      <c r="AD9" s="212"/>
+      <c r="AE9" s="213"/>
+      <c r="AF9" s="208"/>
+      <c r="AG9" s="209"/>
+      <c r="AH9" s="209"/>
+      <c r="AI9" s="210"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="22"/>
-      <c r="B10" s="166"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="170"/>
-      <c r="G10" s="166"/>
-      <c r="H10" s="171"/>
-      <c r="I10" s="167"/>
-      <c r="J10" s="172"/>
-      <c r="K10" s="173"/>
-      <c r="L10" s="173"/>
-      <c r="M10" s="173"/>
-      <c r="N10" s="173"/>
-      <c r="O10" s="173"/>
-      <c r="P10" s="174"/>
-      <c r="Q10" s="175"/>
-      <c r="R10" s="176"/>
-      <c r="S10" s="176"/>
-      <c r="T10" s="176"/>
-      <c r="U10" s="176"/>
-      <c r="V10" s="176"/>
-      <c r="W10" s="176"/>
-      <c r="X10" s="176"/>
-      <c r="Y10" s="176"/>
-      <c r="Z10" s="176"/>
-      <c r="AA10" s="176"/>
-      <c r="AB10" s="176"/>
-      <c r="AC10" s="176"/>
-      <c r="AD10" s="176"/>
-      <c r="AE10" s="177"/>
-      <c r="AF10" s="172"/>
-      <c r="AG10" s="173"/>
-      <c r="AH10" s="173"/>
-      <c r="AI10" s="174"/>
+      <c r="B10" s="202"/>
+      <c r="C10" s="203"/>
+      <c r="D10" s="204"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="206"/>
+      <c r="G10" s="202"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="209"/>
+      <c r="L10" s="209"/>
+      <c r="M10" s="209"/>
+      <c r="N10" s="209"/>
+      <c r="O10" s="209"/>
+      <c r="P10" s="210"/>
+      <c r="Q10" s="211"/>
+      <c r="R10" s="212"/>
+      <c r="S10" s="212"/>
+      <c r="T10" s="212"/>
+      <c r="U10" s="212"/>
+      <c r="V10" s="212"/>
+      <c r="W10" s="212"/>
+      <c r="X10" s="212"/>
+      <c r="Y10" s="212"/>
+      <c r="Z10" s="212"/>
+      <c r="AA10" s="212"/>
+      <c r="AB10" s="212"/>
+      <c r="AC10" s="212"/>
+      <c r="AD10" s="212"/>
+      <c r="AE10" s="213"/>
+      <c r="AF10" s="208"/>
+      <c r="AG10" s="209"/>
+      <c r="AH10" s="209"/>
+      <c r="AI10" s="210"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="22"/>
-      <c r="B11" s="166"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="166"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="167"/>
-      <c r="J11" s="172"/>
-      <c r="K11" s="173"/>
-      <c r="L11" s="173"/>
-      <c r="M11" s="173"/>
-      <c r="N11" s="173"/>
-      <c r="O11" s="173"/>
-      <c r="P11" s="174"/>
-      <c r="Q11" s="175"/>
-      <c r="R11" s="176"/>
-      <c r="S11" s="176"/>
-      <c r="T11" s="176"/>
-      <c r="U11" s="176"/>
-      <c r="V11" s="176"/>
-      <c r="W11" s="176"/>
-      <c r="X11" s="176"/>
-      <c r="Y11" s="176"/>
-      <c r="Z11" s="176"/>
-      <c r="AA11" s="176"/>
-      <c r="AB11" s="176"/>
-      <c r="AC11" s="176"/>
-      <c r="AD11" s="176"/>
-      <c r="AE11" s="177"/>
-      <c r="AF11" s="172"/>
-      <c r="AG11" s="173"/>
-      <c r="AH11" s="173"/>
-      <c r="AI11" s="174"/>
+      <c r="B11" s="202"/>
+      <c r="C11" s="203"/>
+      <c r="D11" s="204"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="202"/>
+      <c r="H11" s="207"/>
+      <c r="I11" s="203"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="209"/>
+      <c r="L11" s="209"/>
+      <c r="M11" s="209"/>
+      <c r="N11" s="209"/>
+      <c r="O11" s="209"/>
+      <c r="P11" s="210"/>
+      <c r="Q11" s="211"/>
+      <c r="R11" s="212"/>
+      <c r="S11" s="212"/>
+      <c r="T11" s="212"/>
+      <c r="U11" s="212"/>
+      <c r="V11" s="212"/>
+      <c r="W11" s="212"/>
+      <c r="X11" s="212"/>
+      <c r="Y11" s="212"/>
+      <c r="Z11" s="212"/>
+      <c r="AA11" s="212"/>
+      <c r="AB11" s="212"/>
+      <c r="AC11" s="212"/>
+      <c r="AD11" s="212"/>
+      <c r="AE11" s="213"/>
+      <c r="AF11" s="208"/>
+      <c r="AG11" s="209"/>
+      <c r="AH11" s="209"/>
+      <c r="AI11" s="210"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="22"/>
-      <c r="B12" s="166"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="169"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="166"/>
-      <c r="H12" s="171"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="172"/>
-      <c r="K12" s="173"/>
-      <c r="L12" s="173"/>
-      <c r="M12" s="173"/>
-      <c r="N12" s="173"/>
-      <c r="O12" s="173"/>
-      <c r="P12" s="174"/>
-      <c r="Q12" s="175"/>
-      <c r="R12" s="176"/>
-      <c r="S12" s="176"/>
-      <c r="T12" s="176"/>
-      <c r="U12" s="176"/>
-      <c r="V12" s="176"/>
-      <c r="W12" s="176"/>
-      <c r="X12" s="176"/>
-      <c r="Y12" s="176"/>
-      <c r="Z12" s="176"/>
-      <c r="AA12" s="176"/>
-      <c r="AB12" s="176"/>
-      <c r="AC12" s="176"/>
-      <c r="AD12" s="176"/>
-      <c r="AE12" s="177"/>
-      <c r="AF12" s="172"/>
-      <c r="AG12" s="173"/>
-      <c r="AH12" s="173"/>
-      <c r="AI12" s="174"/>
+      <c r="B12" s="202"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="204"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="202"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="203"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="209"/>
+      <c r="L12" s="209"/>
+      <c r="M12" s="209"/>
+      <c r="N12" s="209"/>
+      <c r="O12" s="209"/>
+      <c r="P12" s="210"/>
+      <c r="Q12" s="211"/>
+      <c r="R12" s="212"/>
+      <c r="S12" s="212"/>
+      <c r="T12" s="212"/>
+      <c r="U12" s="212"/>
+      <c r="V12" s="212"/>
+      <c r="W12" s="212"/>
+      <c r="X12" s="212"/>
+      <c r="Y12" s="212"/>
+      <c r="Z12" s="212"/>
+      <c r="AA12" s="212"/>
+      <c r="AB12" s="212"/>
+      <c r="AC12" s="212"/>
+      <c r="AD12" s="212"/>
+      <c r="AE12" s="213"/>
+      <c r="AF12" s="208"/>
+      <c r="AG12" s="209"/>
+      <c r="AH12" s="209"/>
+      <c r="AI12" s="210"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="22"/>
-      <c r="B13" s="166"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="169"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="167"/>
-      <c r="J13" s="172"/>
-      <c r="K13" s="173"/>
-      <c r="L13" s="173"/>
-      <c r="M13" s="173"/>
-      <c r="N13" s="173"/>
-      <c r="O13" s="173"/>
-      <c r="P13" s="174"/>
-      <c r="Q13" s="175"/>
-      <c r="R13" s="176"/>
-      <c r="S13" s="176"/>
-      <c r="T13" s="176"/>
-      <c r="U13" s="176"/>
-      <c r="V13" s="176"/>
-      <c r="W13" s="176"/>
-      <c r="X13" s="176"/>
-      <c r="Y13" s="176"/>
-      <c r="Z13" s="176"/>
-      <c r="AA13" s="176"/>
-      <c r="AB13" s="176"/>
-      <c r="AC13" s="176"/>
-      <c r="AD13" s="176"/>
-      <c r="AE13" s="177"/>
-      <c r="AF13" s="172"/>
-      <c r="AG13" s="173"/>
-      <c r="AH13" s="173"/>
-      <c r="AI13" s="174"/>
+      <c r="B13" s="202"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="205"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="207"/>
+      <c r="I13" s="203"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="209"/>
+      <c r="L13" s="209"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="209"/>
+      <c r="O13" s="209"/>
+      <c r="P13" s="210"/>
+      <c r="Q13" s="211"/>
+      <c r="R13" s="212"/>
+      <c r="S13" s="212"/>
+      <c r="T13" s="212"/>
+      <c r="U13" s="212"/>
+      <c r="V13" s="212"/>
+      <c r="W13" s="212"/>
+      <c r="X13" s="212"/>
+      <c r="Y13" s="212"/>
+      <c r="Z13" s="212"/>
+      <c r="AA13" s="212"/>
+      <c r="AB13" s="212"/>
+      <c r="AC13" s="212"/>
+      <c r="AD13" s="212"/>
+      <c r="AE13" s="213"/>
+      <c r="AF13" s="208"/>
+      <c r="AG13" s="209"/>
+      <c r="AH13" s="209"/>
+      <c r="AI13" s="210"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="22"/>
-      <c r="B14" s="166"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="169"/>
-      <c r="F14" s="170"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="167"/>
-      <c r="J14" s="172"/>
-      <c r="K14" s="173"/>
-      <c r="L14" s="173"/>
-      <c r="M14" s="173"/>
-      <c r="N14" s="173"/>
-      <c r="O14" s="173"/>
-      <c r="P14" s="174"/>
-      <c r="Q14" s="175"/>
-      <c r="R14" s="176"/>
-      <c r="S14" s="176"/>
-      <c r="T14" s="176"/>
-      <c r="U14" s="176"/>
-      <c r="V14" s="176"/>
-      <c r="W14" s="176"/>
-      <c r="X14" s="176"/>
-      <c r="Y14" s="176"/>
-      <c r="Z14" s="176"/>
-      <c r="AA14" s="176"/>
-      <c r="AB14" s="176"/>
-      <c r="AC14" s="176"/>
-      <c r="AD14" s="176"/>
-      <c r="AE14" s="177"/>
-      <c r="AF14" s="172"/>
-      <c r="AG14" s="173"/>
-      <c r="AH14" s="173"/>
-      <c r="AI14" s="174"/>
+      <c r="B14" s="202"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="202"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="203"/>
+      <c r="J14" s="208"/>
+      <c r="K14" s="209"/>
+      <c r="L14" s="209"/>
+      <c r="M14" s="209"/>
+      <c r="N14" s="209"/>
+      <c r="O14" s="209"/>
+      <c r="P14" s="210"/>
+      <c r="Q14" s="211"/>
+      <c r="R14" s="212"/>
+      <c r="S14" s="212"/>
+      <c r="T14" s="212"/>
+      <c r="U14" s="212"/>
+      <c r="V14" s="212"/>
+      <c r="W14" s="212"/>
+      <c r="X14" s="212"/>
+      <c r="Y14" s="212"/>
+      <c r="Z14" s="212"/>
+      <c r="AA14" s="212"/>
+      <c r="AB14" s="212"/>
+      <c r="AC14" s="212"/>
+      <c r="AD14" s="212"/>
+      <c r="AE14" s="213"/>
+      <c r="AF14" s="208"/>
+      <c r="AG14" s="209"/>
+      <c r="AH14" s="209"/>
+      <c r="AI14" s="210"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="22"/>
-      <c r="B15" s="166"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="169"/>
-      <c r="F15" s="170"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="171"/>
-      <c r="I15" s="167"/>
-      <c r="J15" s="172"/>
-      <c r="K15" s="173"/>
-      <c r="L15" s="173"/>
-      <c r="M15" s="173"/>
-      <c r="N15" s="173"/>
-      <c r="O15" s="173"/>
-      <c r="P15" s="174"/>
-      <c r="Q15" s="175"/>
-      <c r="R15" s="176"/>
-      <c r="S15" s="176"/>
-      <c r="T15" s="176"/>
-      <c r="U15" s="176"/>
-      <c r="V15" s="176"/>
-      <c r="W15" s="176"/>
-      <c r="X15" s="176"/>
-      <c r="Y15" s="176"/>
-      <c r="Z15" s="176"/>
-      <c r="AA15" s="176"/>
-      <c r="AB15" s="176"/>
-      <c r="AC15" s="176"/>
-      <c r="AD15" s="176"/>
-      <c r="AE15" s="177"/>
-      <c r="AF15" s="172"/>
-      <c r="AG15" s="173"/>
-      <c r="AH15" s="173"/>
-      <c r="AI15" s="174"/>
+      <c r="B15" s="202"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="202"/>
+      <c r="H15" s="207"/>
+      <c r="I15" s="203"/>
+      <c r="J15" s="208"/>
+      <c r="K15" s="209"/>
+      <c r="L15" s="209"/>
+      <c r="M15" s="209"/>
+      <c r="N15" s="209"/>
+      <c r="O15" s="209"/>
+      <c r="P15" s="210"/>
+      <c r="Q15" s="211"/>
+      <c r="R15" s="212"/>
+      <c r="S15" s="212"/>
+      <c r="T15" s="212"/>
+      <c r="U15" s="212"/>
+      <c r="V15" s="212"/>
+      <c r="W15" s="212"/>
+      <c r="X15" s="212"/>
+      <c r="Y15" s="212"/>
+      <c r="Z15" s="212"/>
+      <c r="AA15" s="212"/>
+      <c r="AB15" s="212"/>
+      <c r="AC15" s="212"/>
+      <c r="AD15" s="212"/>
+      <c r="AE15" s="213"/>
+      <c r="AF15" s="208"/>
+      <c r="AG15" s="209"/>
+      <c r="AH15" s="209"/>
+      <c r="AI15" s="210"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="22"/>
-      <c r="B16" s="166"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="170"/>
-      <c r="G16" s="166"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="167"/>
-      <c r="J16" s="172"/>
-      <c r="K16" s="173"/>
-      <c r="L16" s="173"/>
-      <c r="M16" s="173"/>
-      <c r="N16" s="173"/>
-      <c r="O16" s="173"/>
-      <c r="P16" s="174"/>
-      <c r="Q16" s="175"/>
-      <c r="R16" s="176"/>
-      <c r="S16" s="176"/>
-      <c r="T16" s="176"/>
-      <c r="U16" s="176"/>
-      <c r="V16" s="176"/>
-      <c r="W16" s="176"/>
-      <c r="X16" s="176"/>
-      <c r="Y16" s="176"/>
-      <c r="Z16" s="176"/>
-      <c r="AA16" s="176"/>
-      <c r="AB16" s="176"/>
-      <c r="AC16" s="176"/>
-      <c r="AD16" s="176"/>
-      <c r="AE16" s="177"/>
-      <c r="AF16" s="172"/>
-      <c r="AG16" s="173"/>
-      <c r="AH16" s="173"/>
-      <c r="AI16" s="174"/>
+      <c r="B16" s="202"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="205"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="202"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="203"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="209"/>
+      <c r="O16" s="209"/>
+      <c r="P16" s="210"/>
+      <c r="Q16" s="211"/>
+      <c r="R16" s="212"/>
+      <c r="S16" s="212"/>
+      <c r="T16" s="212"/>
+      <c r="U16" s="212"/>
+      <c r="V16" s="212"/>
+      <c r="W16" s="212"/>
+      <c r="X16" s="212"/>
+      <c r="Y16" s="212"/>
+      <c r="Z16" s="212"/>
+      <c r="AA16" s="212"/>
+      <c r="AB16" s="212"/>
+      <c r="AC16" s="212"/>
+      <c r="AD16" s="212"/>
+      <c r="AE16" s="213"/>
+      <c r="AF16" s="208"/>
+      <c r="AG16" s="209"/>
+      <c r="AH16" s="209"/>
+      <c r="AI16" s="210"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="22"/>
-      <c r="B17" s="166"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="169"/>
-      <c r="F17" s="170"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="171"/>
-      <c r="I17" s="167"/>
-      <c r="J17" s="172"/>
-      <c r="K17" s="173"/>
-      <c r="L17" s="173"/>
-      <c r="M17" s="173"/>
-      <c r="N17" s="173"/>
-      <c r="O17" s="173"/>
-      <c r="P17" s="174"/>
-      <c r="Q17" s="175"/>
-      <c r="R17" s="176"/>
-      <c r="S17" s="176"/>
-      <c r="T17" s="176"/>
-      <c r="U17" s="176"/>
-      <c r="V17" s="176"/>
-      <c r="W17" s="176"/>
-      <c r="X17" s="176"/>
-      <c r="Y17" s="176"/>
-      <c r="Z17" s="176"/>
-      <c r="AA17" s="176"/>
-      <c r="AB17" s="176"/>
-      <c r="AC17" s="176"/>
-      <c r="AD17" s="176"/>
-      <c r="AE17" s="177"/>
-      <c r="AF17" s="172"/>
-      <c r="AG17" s="173"/>
-      <c r="AH17" s="173"/>
-      <c r="AI17" s="174"/>
+      <c r="B17" s="202"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="204"/>
+      <c r="E17" s="205"/>
+      <c r="F17" s="206"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="207"/>
+      <c r="I17" s="203"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="209"/>
+      <c r="L17" s="209"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="209"/>
+      <c r="O17" s="209"/>
+      <c r="P17" s="210"/>
+      <c r="Q17" s="211"/>
+      <c r="R17" s="212"/>
+      <c r="S17" s="212"/>
+      <c r="T17" s="212"/>
+      <c r="U17" s="212"/>
+      <c r="V17" s="212"/>
+      <c r="W17" s="212"/>
+      <c r="X17" s="212"/>
+      <c r="Y17" s="212"/>
+      <c r="Z17" s="212"/>
+      <c r="AA17" s="212"/>
+      <c r="AB17" s="212"/>
+      <c r="AC17" s="212"/>
+      <c r="AD17" s="212"/>
+      <c r="AE17" s="213"/>
+      <c r="AF17" s="208"/>
+      <c r="AG17" s="209"/>
+      <c r="AH17" s="209"/>
+      <c r="AI17" s="210"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="B18" s="166"/>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="169"/>
-      <c r="F18" s="170"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="171"/>
-      <c r="I18" s="167"/>
-      <c r="J18" s="172"/>
-      <c r="K18" s="173"/>
-      <c r="L18" s="173"/>
-      <c r="M18" s="173"/>
-      <c r="N18" s="173"/>
-      <c r="O18" s="173"/>
-      <c r="P18" s="174"/>
-      <c r="Q18" s="175"/>
-      <c r="R18" s="176"/>
-      <c r="S18" s="176"/>
-      <c r="T18" s="176"/>
-      <c r="U18" s="176"/>
-      <c r="V18" s="176"/>
-      <c r="W18" s="176"/>
-      <c r="X18" s="176"/>
-      <c r="Y18" s="176"/>
-      <c r="Z18" s="176"/>
-      <c r="AA18" s="176"/>
-      <c r="AB18" s="176"/>
-      <c r="AC18" s="176"/>
-      <c r="AD18" s="176"/>
-      <c r="AE18" s="177"/>
-      <c r="AF18" s="172"/>
-      <c r="AG18" s="173"/>
-      <c r="AH18" s="173"/>
-      <c r="AI18" s="174"/>
+      <c r="B18" s="202"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="204"/>
+      <c r="E18" s="205"/>
+      <c r="F18" s="206"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="207"/>
+      <c r="I18" s="203"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="209"/>
+      <c r="L18" s="209"/>
+      <c r="M18" s="209"/>
+      <c r="N18" s="209"/>
+      <c r="O18" s="209"/>
+      <c r="P18" s="210"/>
+      <c r="Q18" s="211"/>
+      <c r="R18" s="212"/>
+      <c r="S18" s="212"/>
+      <c r="T18" s="212"/>
+      <c r="U18" s="212"/>
+      <c r="V18" s="212"/>
+      <c r="W18" s="212"/>
+      <c r="X18" s="212"/>
+      <c r="Y18" s="212"/>
+      <c r="Z18" s="212"/>
+      <c r="AA18" s="212"/>
+      <c r="AB18" s="212"/>
+      <c r="AC18" s="212"/>
+      <c r="AD18" s="212"/>
+      <c r="AE18" s="213"/>
+      <c r="AF18" s="208"/>
+      <c r="AG18" s="209"/>
+      <c r="AH18" s="209"/>
+      <c r="AI18" s="210"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="22"/>
-      <c r="B19" s="166"/>
-      <c r="C19" s="167"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="170"/>
-      <c r="G19" s="166"/>
-      <c r="H19" s="171"/>
-      <c r="I19" s="167"/>
-      <c r="J19" s="172"/>
-      <c r="K19" s="173"/>
-      <c r="L19" s="173"/>
-      <c r="M19" s="173"/>
-      <c r="N19" s="173"/>
-      <c r="O19" s="173"/>
-      <c r="P19" s="174"/>
-      <c r="Q19" s="175"/>
-      <c r="R19" s="176"/>
-      <c r="S19" s="176"/>
-      <c r="T19" s="176"/>
-      <c r="U19" s="176"/>
-      <c r="V19" s="176"/>
-      <c r="W19" s="176"/>
-      <c r="X19" s="176"/>
-      <c r="Y19" s="176"/>
-      <c r="Z19" s="176"/>
-      <c r="AA19" s="176"/>
-      <c r="AB19" s="176"/>
-      <c r="AC19" s="176"/>
-      <c r="AD19" s="176"/>
-      <c r="AE19" s="177"/>
-      <c r="AF19" s="172"/>
-      <c r="AG19" s="173"/>
-      <c r="AH19" s="173"/>
-      <c r="AI19" s="174"/>
+      <c r="B19" s="202"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="204"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="202"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="203"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="209"/>
+      <c r="L19" s="209"/>
+      <c r="M19" s="209"/>
+      <c r="N19" s="209"/>
+      <c r="O19" s="209"/>
+      <c r="P19" s="210"/>
+      <c r="Q19" s="211"/>
+      <c r="R19" s="212"/>
+      <c r="S19" s="212"/>
+      <c r="T19" s="212"/>
+      <c r="U19" s="212"/>
+      <c r="V19" s="212"/>
+      <c r="W19" s="212"/>
+      <c r="X19" s="212"/>
+      <c r="Y19" s="212"/>
+      <c r="Z19" s="212"/>
+      <c r="AA19" s="212"/>
+      <c r="AB19" s="212"/>
+      <c r="AC19" s="212"/>
+      <c r="AD19" s="212"/>
+      <c r="AE19" s="213"/>
+      <c r="AF19" s="208"/>
+      <c r="AG19" s="209"/>
+      <c r="AH19" s="209"/>
+      <c r="AI19" s="210"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="22"/>
-      <c r="B20" s="166"/>
-      <c r="C20" s="167"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="169"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="166"/>
-      <c r="H20" s="171"/>
-      <c r="I20" s="167"/>
-      <c r="J20" s="172"/>
-      <c r="K20" s="173"/>
-      <c r="L20" s="173"/>
-      <c r="M20" s="173"/>
-      <c r="N20" s="173"/>
-      <c r="O20" s="173"/>
-      <c r="P20" s="174"/>
-      <c r="Q20" s="175"/>
-      <c r="R20" s="176"/>
-      <c r="S20" s="176"/>
-      <c r="T20" s="176"/>
-      <c r="U20" s="176"/>
-      <c r="V20" s="176"/>
-      <c r="W20" s="176"/>
-      <c r="X20" s="176"/>
-      <c r="Y20" s="176"/>
-      <c r="Z20" s="176"/>
-      <c r="AA20" s="176"/>
-      <c r="AB20" s="176"/>
-      <c r="AC20" s="176"/>
-      <c r="AD20" s="176"/>
-      <c r="AE20" s="177"/>
-      <c r="AF20" s="172"/>
-      <c r="AG20" s="173"/>
-      <c r="AH20" s="173"/>
-      <c r="AI20" s="174"/>
+      <c r="B20" s="202"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="204"/>
+      <c r="E20" s="205"/>
+      <c r="F20" s="206"/>
+      <c r="G20" s="202"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="203"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="209"/>
+      <c r="L20" s="209"/>
+      <c r="M20" s="209"/>
+      <c r="N20" s="209"/>
+      <c r="O20" s="209"/>
+      <c r="P20" s="210"/>
+      <c r="Q20" s="211"/>
+      <c r="R20" s="212"/>
+      <c r="S20" s="212"/>
+      <c r="T20" s="212"/>
+      <c r="U20" s="212"/>
+      <c r="V20" s="212"/>
+      <c r="W20" s="212"/>
+      <c r="X20" s="212"/>
+      <c r="Y20" s="212"/>
+      <c r="Z20" s="212"/>
+      <c r="AA20" s="212"/>
+      <c r="AB20" s="212"/>
+      <c r="AC20" s="212"/>
+      <c r="AD20" s="212"/>
+      <c r="AE20" s="213"/>
+      <c r="AF20" s="208"/>
+      <c r="AG20" s="209"/>
+      <c r="AH20" s="209"/>
+      <c r="AI20" s="210"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="22"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="167"/>
-      <c r="D21" s="168"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="170"/>
-      <c r="G21" s="166"/>
-      <c r="H21" s="171"/>
-      <c r="I21" s="167"/>
-      <c r="J21" s="172"/>
-      <c r="K21" s="173"/>
-      <c r="L21" s="173"/>
-      <c r="M21" s="173"/>
-      <c r="N21" s="173"/>
-      <c r="O21" s="173"/>
-      <c r="P21" s="174"/>
-      <c r="Q21" s="175"/>
-      <c r="R21" s="176"/>
-      <c r="S21" s="176"/>
-      <c r="T21" s="176"/>
-      <c r="U21" s="176"/>
-      <c r="V21" s="176"/>
-      <c r="W21" s="176"/>
-      <c r="X21" s="176"/>
-      <c r="Y21" s="176"/>
-      <c r="Z21" s="176"/>
-      <c r="AA21" s="176"/>
-      <c r="AB21" s="176"/>
-      <c r="AC21" s="176"/>
-      <c r="AD21" s="176"/>
-      <c r="AE21" s="177"/>
-      <c r="AF21" s="172"/>
-      <c r="AG21" s="173"/>
-      <c r="AH21" s="173"/>
-      <c r="AI21" s="174"/>
+      <c r="B21" s="202"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="204"/>
+      <c r="E21" s="205"/>
+      <c r="F21" s="206"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="207"/>
+      <c r="I21" s="203"/>
+      <c r="J21" s="208"/>
+      <c r="K21" s="209"/>
+      <c r="L21" s="209"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="209"/>
+      <c r="O21" s="209"/>
+      <c r="P21" s="210"/>
+      <c r="Q21" s="211"/>
+      <c r="R21" s="212"/>
+      <c r="S21" s="212"/>
+      <c r="T21" s="212"/>
+      <c r="U21" s="212"/>
+      <c r="V21" s="212"/>
+      <c r="W21" s="212"/>
+      <c r="X21" s="212"/>
+      <c r="Y21" s="212"/>
+      <c r="Z21" s="212"/>
+      <c r="AA21" s="212"/>
+      <c r="AB21" s="212"/>
+      <c r="AC21" s="212"/>
+      <c r="AD21" s="212"/>
+      <c r="AE21" s="213"/>
+      <c r="AF21" s="208"/>
+      <c r="AG21" s="209"/>
+      <c r="AH21" s="209"/>
+      <c r="AI21" s="210"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="22"/>
-      <c r="B22" s="166"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="168"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="170"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="171"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="172"/>
-      <c r="K22" s="173"/>
-      <c r="L22" s="173"/>
-      <c r="M22" s="173"/>
-      <c r="N22" s="173"/>
-      <c r="O22" s="173"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="175"/>
-      <c r="R22" s="176"/>
-      <c r="S22" s="176"/>
-      <c r="T22" s="176"/>
-      <c r="U22" s="176"/>
-      <c r="V22" s="176"/>
-      <c r="W22" s="176"/>
-      <c r="X22" s="176"/>
-      <c r="Y22" s="176"/>
-      <c r="Z22" s="176"/>
-      <c r="AA22" s="176"/>
-      <c r="AB22" s="176"/>
-      <c r="AC22" s="176"/>
-      <c r="AD22" s="176"/>
-      <c r="AE22" s="177"/>
-      <c r="AF22" s="172"/>
-      <c r="AG22" s="173"/>
-      <c r="AH22" s="173"/>
-      <c r="AI22" s="174"/>
+      <c r="B22" s="202"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="204"/>
+      <c r="E22" s="205"/>
+      <c r="F22" s="206"/>
+      <c r="G22" s="202"/>
+      <c r="H22" s="207"/>
+      <c r="I22" s="203"/>
+      <c r="J22" s="208"/>
+      <c r="K22" s="209"/>
+      <c r="L22" s="209"/>
+      <c r="M22" s="209"/>
+      <c r="N22" s="209"/>
+      <c r="O22" s="209"/>
+      <c r="P22" s="210"/>
+      <c r="Q22" s="211"/>
+      <c r="R22" s="212"/>
+      <c r="S22" s="212"/>
+      <c r="T22" s="212"/>
+      <c r="U22" s="212"/>
+      <c r="V22" s="212"/>
+      <c r="W22" s="212"/>
+      <c r="X22" s="212"/>
+      <c r="Y22" s="212"/>
+      <c r="Z22" s="212"/>
+      <c r="AA22" s="212"/>
+      <c r="AB22" s="212"/>
+      <c r="AC22" s="212"/>
+      <c r="AD22" s="212"/>
+      <c r="AE22" s="213"/>
+      <c r="AF22" s="208"/>
+      <c r="AG22" s="209"/>
+      <c r="AH22" s="209"/>
+      <c r="AI22" s="210"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="22"/>
-      <c r="B23" s="166"/>
-      <c r="C23" s="167"/>
-      <c r="D23" s="168"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="171"/>
-      <c r="I23" s="167"/>
-      <c r="J23" s="172"/>
-      <c r="K23" s="173"/>
-      <c r="L23" s="173"/>
-      <c r="M23" s="173"/>
-      <c r="N23" s="173"/>
-      <c r="O23" s="173"/>
-      <c r="P23" s="174"/>
-      <c r="Q23" s="175"/>
-      <c r="R23" s="176"/>
-      <c r="S23" s="176"/>
-      <c r="T23" s="176"/>
-      <c r="U23" s="176"/>
-      <c r="V23" s="176"/>
-      <c r="W23" s="176"/>
-      <c r="X23" s="176"/>
-      <c r="Y23" s="176"/>
-      <c r="Z23" s="176"/>
-      <c r="AA23" s="176"/>
-      <c r="AB23" s="176"/>
-      <c r="AC23" s="176"/>
-      <c r="AD23" s="176"/>
-      <c r="AE23" s="177"/>
-      <c r="AF23" s="172"/>
-      <c r="AG23" s="173"/>
-      <c r="AH23" s="173"/>
-      <c r="AI23" s="174"/>
+      <c r="B23" s="202"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="204"/>
+      <c r="E23" s="205"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="202"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="203"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="209"/>
+      <c r="L23" s="209"/>
+      <c r="M23" s="209"/>
+      <c r="N23" s="209"/>
+      <c r="O23" s="209"/>
+      <c r="P23" s="210"/>
+      <c r="Q23" s="211"/>
+      <c r="R23" s="212"/>
+      <c r="S23" s="212"/>
+      <c r="T23" s="212"/>
+      <c r="U23" s="212"/>
+      <c r="V23" s="212"/>
+      <c r="W23" s="212"/>
+      <c r="X23" s="212"/>
+      <c r="Y23" s="212"/>
+      <c r="Z23" s="212"/>
+      <c r="AA23" s="212"/>
+      <c r="AB23" s="212"/>
+      <c r="AC23" s="212"/>
+      <c r="AD23" s="212"/>
+      <c r="AE23" s="213"/>
+      <c r="AF23" s="208"/>
+      <c r="AG23" s="209"/>
+      <c r="AH23" s="209"/>
+      <c r="AI23" s="210"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="22"/>
-      <c r="B24" s="166"/>
-      <c r="C24" s="167"/>
-      <c r="D24" s="168"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="171"/>
-      <c r="I24" s="167"/>
-      <c r="J24" s="172"/>
-      <c r="K24" s="173"/>
-      <c r="L24" s="173"/>
-      <c r="M24" s="173"/>
-      <c r="N24" s="173"/>
-      <c r="O24" s="173"/>
-      <c r="P24" s="174"/>
-      <c r="Q24" s="175"/>
-      <c r="R24" s="176"/>
-      <c r="S24" s="176"/>
-      <c r="T24" s="176"/>
-      <c r="U24" s="176"/>
-      <c r="V24" s="176"/>
-      <c r="W24" s="176"/>
-      <c r="X24" s="176"/>
-      <c r="Y24" s="176"/>
-      <c r="Z24" s="176"/>
-      <c r="AA24" s="176"/>
-      <c r="AB24" s="176"/>
-      <c r="AC24" s="176"/>
-      <c r="AD24" s="176"/>
-      <c r="AE24" s="177"/>
-      <c r="AF24" s="172"/>
-      <c r="AG24" s="173"/>
-      <c r="AH24" s="173"/>
-      <c r="AI24" s="174"/>
+      <c r="B24" s="202"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="204"/>
+      <c r="E24" s="205"/>
+      <c r="F24" s="206"/>
+      <c r="G24" s="202"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="203"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="209"/>
+      <c r="L24" s="209"/>
+      <c r="M24" s="209"/>
+      <c r="N24" s="209"/>
+      <c r="O24" s="209"/>
+      <c r="P24" s="210"/>
+      <c r="Q24" s="211"/>
+      <c r="R24" s="212"/>
+      <c r="S24" s="212"/>
+      <c r="T24" s="212"/>
+      <c r="U24" s="212"/>
+      <c r="V24" s="212"/>
+      <c r="W24" s="212"/>
+      <c r="X24" s="212"/>
+      <c r="Y24" s="212"/>
+      <c r="Z24" s="212"/>
+      <c r="AA24" s="212"/>
+      <c r="AB24" s="212"/>
+      <c r="AC24" s="212"/>
+      <c r="AD24" s="212"/>
+      <c r="AE24" s="213"/>
+      <c r="AF24" s="208"/>
+      <c r="AG24" s="209"/>
+      <c r="AH24" s="209"/>
+      <c r="AI24" s="210"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="22"/>
-      <c r="B25" s="166"/>
-      <c r="C25" s="167"/>
-      <c r="D25" s="168"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="170"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="171"/>
-      <c r="I25" s="167"/>
-      <c r="J25" s="172"/>
-      <c r="K25" s="173"/>
-      <c r="L25" s="173"/>
-      <c r="M25" s="173"/>
-      <c r="N25" s="173"/>
-      <c r="O25" s="173"/>
-      <c r="P25" s="174"/>
-      <c r="Q25" s="175"/>
-      <c r="R25" s="176"/>
-      <c r="S25" s="176"/>
-      <c r="T25" s="176"/>
-      <c r="U25" s="176"/>
-      <c r="V25" s="176"/>
-      <c r="W25" s="176"/>
-      <c r="X25" s="176"/>
-      <c r="Y25" s="176"/>
-      <c r="Z25" s="176"/>
-      <c r="AA25" s="176"/>
-      <c r="AB25" s="176"/>
-      <c r="AC25" s="176"/>
-      <c r="AD25" s="176"/>
-      <c r="AE25" s="177"/>
-      <c r="AF25" s="172"/>
-      <c r="AG25" s="173"/>
-      <c r="AH25" s="173"/>
-      <c r="AI25" s="174"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="204"/>
+      <c r="E25" s="205"/>
+      <c r="F25" s="206"/>
+      <c r="G25" s="202"/>
+      <c r="H25" s="207"/>
+      <c r="I25" s="203"/>
+      <c r="J25" s="208"/>
+      <c r="K25" s="209"/>
+      <c r="L25" s="209"/>
+      <c r="M25" s="209"/>
+      <c r="N25" s="209"/>
+      <c r="O25" s="209"/>
+      <c r="P25" s="210"/>
+      <c r="Q25" s="211"/>
+      <c r="R25" s="212"/>
+      <c r="S25" s="212"/>
+      <c r="T25" s="212"/>
+      <c r="U25" s="212"/>
+      <c r="V25" s="212"/>
+      <c r="W25" s="212"/>
+      <c r="X25" s="212"/>
+      <c r="Y25" s="212"/>
+      <c r="Z25" s="212"/>
+      <c r="AA25" s="212"/>
+      <c r="AB25" s="212"/>
+      <c r="AC25" s="212"/>
+      <c r="AD25" s="212"/>
+      <c r="AE25" s="213"/>
+      <c r="AF25" s="208"/>
+      <c r="AG25" s="209"/>
+      <c r="AH25" s="209"/>
+      <c r="AI25" s="210"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="22"/>
-      <c r="B26" s="166"/>
-      <c r="C26" s="167"/>
-      <c r="D26" s="168"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="170"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="171"/>
-      <c r="I26" s="167"/>
-      <c r="J26" s="172"/>
-      <c r="K26" s="173"/>
-      <c r="L26" s="173"/>
-      <c r="M26" s="173"/>
-      <c r="N26" s="173"/>
-      <c r="O26" s="173"/>
-      <c r="P26" s="174"/>
-      <c r="Q26" s="175"/>
-      <c r="R26" s="176"/>
-      <c r="S26" s="176"/>
-      <c r="T26" s="176"/>
-      <c r="U26" s="176"/>
-      <c r="V26" s="176"/>
-      <c r="W26" s="176"/>
-      <c r="X26" s="176"/>
-      <c r="Y26" s="176"/>
-      <c r="Z26" s="176"/>
-      <c r="AA26" s="176"/>
-      <c r="AB26" s="176"/>
-      <c r="AC26" s="176"/>
-      <c r="AD26" s="176"/>
-      <c r="AE26" s="177"/>
-      <c r="AF26" s="172"/>
-      <c r="AG26" s="173"/>
-      <c r="AH26" s="173"/>
-      <c r="AI26" s="174"/>
+      <c r="B26" s="202"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="204"/>
+      <c r="E26" s="205"/>
+      <c r="F26" s="206"/>
+      <c r="G26" s="202"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="203"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="209"/>
+      <c r="L26" s="209"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="209"/>
+      <c r="O26" s="209"/>
+      <c r="P26" s="210"/>
+      <c r="Q26" s="211"/>
+      <c r="R26" s="212"/>
+      <c r="S26" s="212"/>
+      <c r="T26" s="212"/>
+      <c r="U26" s="212"/>
+      <c r="V26" s="212"/>
+      <c r="W26" s="212"/>
+      <c r="X26" s="212"/>
+      <c r="Y26" s="212"/>
+      <c r="Z26" s="212"/>
+      <c r="AA26" s="212"/>
+      <c r="AB26" s="212"/>
+      <c r="AC26" s="212"/>
+      <c r="AD26" s="212"/>
+      <c r="AE26" s="213"/>
+      <c r="AF26" s="208"/>
+      <c r="AG26" s="209"/>
+      <c r="AH26" s="209"/>
+      <c r="AI26" s="210"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="22"/>
-      <c r="B27" s="166"/>
-      <c r="C27" s="167"/>
-      <c r="D27" s="168"/>
-      <c r="E27" s="169"/>
-      <c r="F27" s="170"/>
-      <c r="G27" s="166"/>
-      <c r="H27" s="171"/>
-      <c r="I27" s="167"/>
-      <c r="J27" s="172"/>
-      <c r="K27" s="173"/>
-      <c r="L27" s="173"/>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
-      <c r="O27" s="173"/>
-      <c r="P27" s="174"/>
-      <c r="Q27" s="175"/>
-      <c r="R27" s="176"/>
-      <c r="S27" s="176"/>
-      <c r="T27" s="176"/>
-      <c r="U27" s="176"/>
-      <c r="V27" s="176"/>
-      <c r="W27" s="176"/>
-      <c r="X27" s="176"/>
-      <c r="Y27" s="176"/>
-      <c r="Z27" s="176"/>
-      <c r="AA27" s="176"/>
-      <c r="AB27" s="176"/>
-      <c r="AC27" s="176"/>
-      <c r="AD27" s="176"/>
-      <c r="AE27" s="177"/>
-      <c r="AF27" s="172"/>
-      <c r="AG27" s="173"/>
-      <c r="AH27" s="173"/>
-      <c r="AI27" s="174"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="204"/>
+      <c r="E27" s="205"/>
+      <c r="F27" s="206"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="207"/>
+      <c r="I27" s="203"/>
+      <c r="J27" s="208"/>
+      <c r="K27" s="209"/>
+      <c r="L27" s="209"/>
+      <c r="M27" s="209"/>
+      <c r="N27" s="209"/>
+      <c r="O27" s="209"/>
+      <c r="P27" s="210"/>
+      <c r="Q27" s="211"/>
+      <c r="R27" s="212"/>
+      <c r="S27" s="212"/>
+      <c r="T27" s="212"/>
+      <c r="U27" s="212"/>
+      <c r="V27" s="212"/>
+      <c r="W27" s="212"/>
+      <c r="X27" s="212"/>
+      <c r="Y27" s="212"/>
+      <c r="Z27" s="212"/>
+      <c r="AA27" s="212"/>
+      <c r="AB27" s="212"/>
+      <c r="AC27" s="212"/>
+      <c r="AD27" s="212"/>
+      <c r="AE27" s="213"/>
+      <c r="AF27" s="208"/>
+      <c r="AG27" s="209"/>
+      <c r="AH27" s="209"/>
+      <c r="AI27" s="210"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="22"/>
-      <c r="B28" s="166"/>
-      <c r="C28" s="167"/>
-      <c r="D28" s="168"/>
-      <c r="E28" s="169"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="166"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="167"/>
-      <c r="J28" s="172"/>
-      <c r="K28" s="173"/>
-      <c r="L28" s="173"/>
-      <c r="M28" s="173"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="173"/>
-      <c r="P28" s="174"/>
-      <c r="Q28" s="175"/>
-      <c r="R28" s="176"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="176"/>
-      <c r="U28" s="176"/>
-      <c r="V28" s="176"/>
-      <c r="W28" s="176"/>
-      <c r="X28" s="176"/>
-      <c r="Y28" s="176"/>
-      <c r="Z28" s="176"/>
-      <c r="AA28" s="176"/>
-      <c r="AB28" s="176"/>
-      <c r="AC28" s="176"/>
-      <c r="AD28" s="176"/>
-      <c r="AE28" s="177"/>
-      <c r="AF28" s="172"/>
-      <c r="AG28" s="173"/>
-      <c r="AH28" s="173"/>
-      <c r="AI28" s="174"/>
+      <c r="B28" s="202"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="206"/>
+      <c r="G28" s="202"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="203"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="209"/>
+      <c r="L28" s="209"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="209"/>
+      <c r="O28" s="209"/>
+      <c r="P28" s="210"/>
+      <c r="Q28" s="211"/>
+      <c r="R28" s="212"/>
+      <c r="S28" s="212"/>
+      <c r="T28" s="212"/>
+      <c r="U28" s="212"/>
+      <c r="V28" s="212"/>
+      <c r="W28" s="212"/>
+      <c r="X28" s="212"/>
+      <c r="Y28" s="212"/>
+      <c r="Z28" s="212"/>
+      <c r="AA28" s="212"/>
+      <c r="AB28" s="212"/>
+      <c r="AC28" s="212"/>
+      <c r="AD28" s="212"/>
+      <c r="AE28" s="213"/>
+      <c r="AF28" s="208"/>
+      <c r="AG28" s="209"/>
+      <c r="AH28" s="209"/>
+      <c r="AI28" s="210"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="22"/>
-      <c r="B29" s="166"/>
-      <c r="C29" s="167"/>
-      <c r="D29" s="168"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="170"/>
-      <c r="G29" s="166"/>
-      <c r="H29" s="171"/>
-      <c r="I29" s="167"/>
-      <c r="J29" s="172"/>
-      <c r="K29" s="173"/>
-      <c r="L29" s="173"/>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173"/>
-      <c r="O29" s="173"/>
-      <c r="P29" s="174"/>
-      <c r="Q29" s="175"/>
-      <c r="R29" s="176"/>
-      <c r="S29" s="176"/>
-      <c r="T29" s="176"/>
-      <c r="U29" s="176"/>
-      <c r="V29" s="176"/>
-      <c r="W29" s="176"/>
-      <c r="X29" s="176"/>
-      <c r="Y29" s="176"/>
-      <c r="Z29" s="176"/>
-      <c r="AA29" s="176"/>
-      <c r="AB29" s="176"/>
-      <c r="AC29" s="176"/>
-      <c r="AD29" s="176"/>
-      <c r="AE29" s="177"/>
-      <c r="AF29" s="172"/>
-      <c r="AG29" s="173"/>
-      <c r="AH29" s="173"/>
-      <c r="AI29" s="174"/>
+      <c r="B29" s="202"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="204"/>
+      <c r="E29" s="205"/>
+      <c r="F29" s="206"/>
+      <c r="G29" s="202"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="203"/>
+      <c r="J29" s="208"/>
+      <c r="K29" s="209"/>
+      <c r="L29" s="209"/>
+      <c r="M29" s="209"/>
+      <c r="N29" s="209"/>
+      <c r="O29" s="209"/>
+      <c r="P29" s="210"/>
+      <c r="Q29" s="211"/>
+      <c r="R29" s="212"/>
+      <c r="S29" s="212"/>
+      <c r="T29" s="212"/>
+      <c r="U29" s="212"/>
+      <c r="V29" s="212"/>
+      <c r="W29" s="212"/>
+      <c r="X29" s="212"/>
+      <c r="Y29" s="212"/>
+      <c r="Z29" s="212"/>
+      <c r="AA29" s="212"/>
+      <c r="AB29" s="212"/>
+      <c r="AC29" s="212"/>
+      <c r="AD29" s="212"/>
+      <c r="AE29" s="213"/>
+      <c r="AF29" s="208"/>
+      <c r="AG29" s="209"/>
+      <c r="AH29" s="209"/>
+      <c r="AI29" s="210"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="22"/>
-      <c r="B30" s="166"/>
-      <c r="C30" s="167"/>
-      <c r="D30" s="168"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="170"/>
-      <c r="G30" s="166"/>
-      <c r="H30" s="171"/>
-      <c r="I30" s="167"/>
-      <c r="J30" s="172"/>
-      <c r="K30" s="173"/>
-      <c r="L30" s="173"/>
-      <c r="M30" s="173"/>
-      <c r="N30" s="173"/>
-      <c r="O30" s="173"/>
-      <c r="P30" s="174"/>
-      <c r="Q30" s="175"/>
-      <c r="R30" s="176"/>
-      <c r="S30" s="176"/>
-      <c r="T30" s="176"/>
-      <c r="U30" s="176"/>
-      <c r="V30" s="176"/>
-      <c r="W30" s="176"/>
-      <c r="X30" s="176"/>
-      <c r="Y30" s="176"/>
-      <c r="Z30" s="176"/>
-      <c r="AA30" s="176"/>
-      <c r="AB30" s="176"/>
-      <c r="AC30" s="176"/>
-      <c r="AD30" s="176"/>
-      <c r="AE30" s="177"/>
-      <c r="AF30" s="172"/>
-      <c r="AG30" s="173"/>
-      <c r="AH30" s="173"/>
-      <c r="AI30" s="174"/>
+      <c r="B30" s="202"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="204"/>
+      <c r="E30" s="205"/>
+      <c r="F30" s="206"/>
+      <c r="G30" s="202"/>
+      <c r="H30" s="207"/>
+      <c r="I30" s="203"/>
+      <c r="J30" s="208"/>
+      <c r="K30" s="209"/>
+      <c r="L30" s="209"/>
+      <c r="M30" s="209"/>
+      <c r="N30" s="209"/>
+      <c r="O30" s="209"/>
+      <c r="P30" s="210"/>
+      <c r="Q30" s="211"/>
+      <c r="R30" s="212"/>
+      <c r="S30" s="212"/>
+      <c r="T30" s="212"/>
+      <c r="U30" s="212"/>
+      <c r="V30" s="212"/>
+      <c r="W30" s="212"/>
+      <c r="X30" s="212"/>
+      <c r="Y30" s="212"/>
+      <c r="Z30" s="212"/>
+      <c r="AA30" s="212"/>
+      <c r="AB30" s="212"/>
+      <c r="AC30" s="212"/>
+      <c r="AD30" s="212"/>
+      <c r="AE30" s="213"/>
+      <c r="AF30" s="208"/>
+      <c r="AG30" s="209"/>
+      <c r="AH30" s="209"/>
+      <c r="AI30" s="210"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="22"/>
-      <c r="B31" s="166"/>
-      <c r="C31" s="167"/>
-      <c r="D31" s="168"/>
-      <c r="E31" s="169"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="171"/>
-      <c r="I31" s="167"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="173"/>
-      <c r="L31" s="173"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="173"/>
-      <c r="O31" s="173"/>
-      <c r="P31" s="174"/>
-      <c r="Q31" s="175"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="176"/>
-      <c r="T31" s="176"/>
-      <c r="U31" s="176"/>
-      <c r="V31" s="176"/>
-      <c r="W31" s="176"/>
-      <c r="X31" s="176"/>
-      <c r="Y31" s="176"/>
-      <c r="Z31" s="176"/>
-      <c r="AA31" s="176"/>
-      <c r="AB31" s="176"/>
-      <c r="AC31" s="176"/>
-      <c r="AD31" s="176"/>
-      <c r="AE31" s="177"/>
-      <c r="AF31" s="172"/>
-      <c r="AG31" s="173"/>
-      <c r="AH31" s="173"/>
-      <c r="AI31" s="174"/>
+      <c r="B31" s="202"/>
+      <c r="C31" s="203"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="205"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="202"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="203"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="209"/>
+      <c r="L31" s="209"/>
+      <c r="M31" s="209"/>
+      <c r="N31" s="209"/>
+      <c r="O31" s="209"/>
+      <c r="P31" s="210"/>
+      <c r="Q31" s="211"/>
+      <c r="R31" s="212"/>
+      <c r="S31" s="212"/>
+      <c r="T31" s="212"/>
+      <c r="U31" s="212"/>
+      <c r="V31" s="212"/>
+      <c r="W31" s="212"/>
+      <c r="X31" s="212"/>
+      <c r="Y31" s="212"/>
+      <c r="Z31" s="212"/>
+      <c r="AA31" s="212"/>
+      <c r="AB31" s="212"/>
+      <c r="AC31" s="212"/>
+      <c r="AD31" s="212"/>
+      <c r="AE31" s="213"/>
+      <c r="AF31" s="208"/>
+      <c r="AG31" s="209"/>
+      <c r="AH31" s="209"/>
+      <c r="AI31" s="210"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="22"/>
-      <c r="B32" s="166"/>
-      <c r="C32" s="167"/>
-      <c r="D32" s="168"/>
-      <c r="E32" s="169"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="166"/>
-      <c r="H32" s="171"/>
-      <c r="I32" s="167"/>
-      <c r="J32" s="172"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="173"/>
-      <c r="M32" s="173"/>
-      <c r="N32" s="173"/>
-      <c r="O32" s="173"/>
-      <c r="P32" s="174"/>
-      <c r="Q32" s="175"/>
-      <c r="R32" s="176"/>
-      <c r="S32" s="176"/>
-      <c r="T32" s="176"/>
-      <c r="U32" s="176"/>
-      <c r="V32" s="176"/>
-      <c r="W32" s="176"/>
-      <c r="X32" s="176"/>
-      <c r="Y32" s="176"/>
-      <c r="Z32" s="176"/>
-      <c r="AA32" s="176"/>
-      <c r="AB32" s="176"/>
-      <c r="AC32" s="176"/>
-      <c r="AD32" s="176"/>
-      <c r="AE32" s="177"/>
-      <c r="AF32" s="172"/>
-      <c r="AG32" s="173"/>
-      <c r="AH32" s="173"/>
-      <c r="AI32" s="174"/>
+      <c r="B32" s="202"/>
+      <c r="C32" s="203"/>
+      <c r="D32" s="204"/>
+      <c r="E32" s="205"/>
+      <c r="F32" s="206"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="203"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="227"/>
+      <c r="L32" s="209"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="209"/>
+      <c r="O32" s="209"/>
+      <c r="P32" s="210"/>
+      <c r="Q32" s="211"/>
+      <c r="R32" s="212"/>
+      <c r="S32" s="212"/>
+      <c r="T32" s="212"/>
+      <c r="U32" s="212"/>
+      <c r="V32" s="212"/>
+      <c r="W32" s="212"/>
+      <c r="X32" s="212"/>
+      <c r="Y32" s="212"/>
+      <c r="Z32" s="212"/>
+      <c r="AA32" s="212"/>
+      <c r="AB32" s="212"/>
+      <c r="AC32" s="212"/>
+      <c r="AD32" s="212"/>
+      <c r="AE32" s="213"/>
+      <c r="AF32" s="208"/>
+      <c r="AG32" s="209"/>
+      <c r="AH32" s="209"/>
+      <c r="AI32" s="210"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="22"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="167"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="169"/>
-      <c r="F33" s="170"/>
-      <c r="G33" s="166"/>
-      <c r="H33" s="171"/>
-      <c r="I33" s="167"/>
-      <c r="J33" s="172"/>
-      <c r="K33" s="173"/>
-      <c r="L33" s="173"/>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
-      <c r="O33" s="173"/>
-      <c r="P33" s="174"/>
-      <c r="Q33" s="175"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="176"/>
-      <c r="T33" s="176"/>
-      <c r="U33" s="176"/>
-      <c r="V33" s="176"/>
-      <c r="W33" s="176"/>
-      <c r="X33" s="176"/>
-      <c r="Y33" s="176"/>
-      <c r="Z33" s="176"/>
-      <c r="AA33" s="176"/>
-      <c r="AB33" s="176"/>
-      <c r="AC33" s="176"/>
-      <c r="AD33" s="176"/>
-      <c r="AE33" s="177"/>
-      <c r="AF33" s="172"/>
-      <c r="AG33" s="173"/>
-      <c r="AH33" s="173"/>
-      <c r="AI33" s="174"/>
+      <c r="B33" s="202"/>
+      <c r="C33" s="203"/>
+      <c r="D33" s="204"/>
+      <c r="E33" s="205"/>
+      <c r="F33" s="206"/>
+      <c r="G33" s="202"/>
+      <c r="H33" s="207"/>
+      <c r="I33" s="203"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="209"/>
+      <c r="L33" s="209"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="209"/>
+      <c r="O33" s="209"/>
+      <c r="P33" s="210"/>
+      <c r="Q33" s="211"/>
+      <c r="R33" s="212"/>
+      <c r="S33" s="212"/>
+      <c r="T33" s="212"/>
+      <c r="U33" s="212"/>
+      <c r="V33" s="212"/>
+      <c r="W33" s="212"/>
+      <c r="X33" s="212"/>
+      <c r="Y33" s="212"/>
+      <c r="Z33" s="212"/>
+      <c r="AA33" s="212"/>
+      <c r="AB33" s="212"/>
+      <c r="AC33" s="212"/>
+      <c r="AD33" s="212"/>
+      <c r="AE33" s="213"/>
+      <c r="AF33" s="208"/>
+      <c r="AG33" s="209"/>
+      <c r="AH33" s="209"/>
+      <c r="AI33" s="210"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -11757,162 +11917,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -21907,7 +21911,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="25" t="s">
-        <v>20</v>
+        <v>564</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>22</v>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B308434-6659-4900-A709-B511C1478D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D47826-AD4B-44E5-8841-D18C331B4473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="19" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="20" r:id="rId2"/>
     <sheet name="【テストターゲット名】_クラス単体" sheetId="26" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体" sheetId="25" r:id="rId4"/>
+    <sheet name="【テストターゲット名】_リクエスト単体" sheetId="25" r:id="rId4"/>
     <sheet name="取引単体" sheetId="24" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【テストターゲット名】_リクエスト単体!$A$10:$R$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$382</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【テストターゲット名】_リクエスト単体!$A$1:$R$382</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【テストターゲット名】_リクエスト単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="554">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -7626,10 +7626,6 @@
   <si>
     <t>ケースNo.</t>
     <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>リクエストID：</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -8855,84 +8851,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9039,6 +8957,84 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10494,55 +10490,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="204" t="s">
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="205"/>
-      <c r="Q1" s="205"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="213" t="s">
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
+      <c r="R1" s="180"/>
+      <c r="S1" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="215"/>
-      <c r="AA1" s="195" t="s">
+      <c r="T1" s="188"/>
+      <c r="U1" s="188"/>
+      <c r="V1" s="188"/>
+      <c r="W1" s="188"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="188"/>
+      <c r="Z1" s="189"/>
+      <c r="AA1" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" s="197"/>
-      <c r="AC1" s="222" t="str">
+      <c r="AB1" s="171"/>
+      <c r="AC1" s="196" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="223"/>
-      <c r="AF1" s="224"/>
-      <c r="AG1" s="189" t="str">
+      <c r="AD1" s="197"/>
+      <c r="AE1" s="197"/>
+      <c r="AF1" s="198"/>
+      <c r="AG1" s="163" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="190"/>
-      <c r="AI1" s="191"/>
+      <c r="AH1" s="164"/>
+      <c r="AI1" s="165"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -10550,51 +10546,51 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="199"/>
-      <c r="K2" s="199"/>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="207"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="209"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="217"/>
-      <c r="V2" s="217"/>
-      <c r="W2" s="217"/>
-      <c r="X2" s="217"/>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="195" t="s">
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="182"/>
+      <c r="Q2" s="182"/>
+      <c r="R2" s="183"/>
+      <c r="S2" s="190"/>
+      <c r="T2" s="191"/>
+      <c r="U2" s="191"/>
+      <c r="V2" s="191"/>
+      <c r="W2" s="191"/>
+      <c r="X2" s="191"/>
+      <c r="Y2" s="191"/>
+      <c r="Z2" s="192"/>
+      <c r="AA2" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="AB2" s="197"/>
-      <c r="AC2" s="201" t="str">
+      <c r="AB2" s="171"/>
+      <c r="AC2" s="175" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="202"/>
-      <c r="AE2" s="202"/>
-      <c r="AF2" s="203"/>
-      <c r="AG2" s="189" t="str">
+      <c r="AD2" s="176"/>
+      <c r="AE2" s="176"/>
+      <c r="AF2" s="177"/>
+      <c r="AG2" s="163" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="190"/>
-      <c r="AI2" s="191"/>
+      <c r="AH2" s="164"/>
+      <c r="AI2" s="165"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -10602,43 +10598,43 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="199"/>
-      <c r="N3" s="200"/>
-      <c r="O3" s="210"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="219"/>
-      <c r="T3" s="220"/>
-      <c r="U3" s="220"/>
-      <c r="V3" s="220"/>
-      <c r="W3" s="220"/>
-      <c r="X3" s="220"/>
-      <c r="Y3" s="220"/>
-      <c r="Z3" s="221"/>
-      <c r="AA3" s="195"/>
-      <c r="AB3" s="197"/>
-      <c r="AC3" s="222"/>
-      <c r="AD3" s="223"/>
-      <c r="AE3" s="223"/>
-      <c r="AF3" s="224"/>
-      <c r="AG3" s="189"/>
-      <c r="AH3" s="190"/>
-      <c r="AI3" s="191"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="184"/>
+      <c r="P3" s="185"/>
+      <c r="Q3" s="185"/>
+      <c r="R3" s="186"/>
+      <c r="S3" s="193"/>
+      <c r="T3" s="194"/>
+      <c r="U3" s="194"/>
+      <c r="V3" s="194"/>
+      <c r="W3" s="194"/>
+      <c r="X3" s="194"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="195"/>
+      <c r="AA3" s="169"/>
+      <c r="AB3" s="171"/>
+      <c r="AC3" s="196"/>
+      <c r="AD3" s="197"/>
+      <c r="AE3" s="197"/>
+      <c r="AF3" s="198"/>
+      <c r="AG3" s="163"/>
+      <c r="AH3" s="164"/>
+      <c r="AI3" s="165"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -10675,1020 +10671,1176 @@
       <c r="A7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="192" t="s">
+      <c r="B7" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="192" t="s">
+      <c r="C7" s="167"/>
+      <c r="D7" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="194"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="192" t="s">
+      <c r="E7" s="168"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="194"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="192" t="s">
+      <c r="H7" s="168"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="166" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="194"/>
-      <c r="L7" s="194"/>
-      <c r="M7" s="194"/>
-      <c r="N7" s="194"/>
-      <c r="O7" s="194"/>
-      <c r="P7" s="193"/>
-      <c r="Q7" s="192" t="s">
+      <c r="K7" s="168"/>
+      <c r="L7" s="168"/>
+      <c r="M7" s="168"/>
+      <c r="N7" s="168"/>
+      <c r="O7" s="168"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="194"/>
-      <c r="S7" s="194"/>
-      <c r="T7" s="194"/>
-      <c r="U7" s="194"/>
-      <c r="V7" s="194"/>
-      <c r="W7" s="194"/>
-      <c r="X7" s="194"/>
-      <c r="Y7" s="194"/>
-      <c r="Z7" s="194"/>
-      <c r="AA7" s="194"/>
-      <c r="AB7" s="194"/>
-      <c r="AC7" s="194"/>
-      <c r="AD7" s="194"/>
-      <c r="AE7" s="193"/>
-      <c r="AF7" s="192" t="s">
+      <c r="R7" s="168"/>
+      <c r="S7" s="168"/>
+      <c r="T7" s="168"/>
+      <c r="U7" s="168"/>
+      <c r="V7" s="168"/>
+      <c r="W7" s="168"/>
+      <c r="X7" s="168"/>
+      <c r="Y7" s="168"/>
+      <c r="Z7" s="168"/>
+      <c r="AA7" s="168"/>
+      <c r="AB7" s="168"/>
+      <c r="AC7" s="168"/>
+      <c r="AD7" s="168"/>
+      <c r="AE7" s="167"/>
+      <c r="AF7" s="166" t="s">
         <v>61</v>
       </c>
-      <c r="AG7" s="194"/>
-      <c r="AH7" s="194"/>
-      <c r="AI7" s="193"/>
+      <c r="AG7" s="168"/>
+      <c r="AH7" s="168"/>
+      <c r="AI7" s="167"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="21"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="177"/>
-      <c r="D8" s="178"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="181"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="177"/>
-      <c r="J8" s="183"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="185"/>
-      <c r="Q8" s="186"/>
-      <c r="R8" s="187"/>
-      <c r="S8" s="187"/>
-      <c r="T8" s="187"/>
-      <c r="U8" s="187"/>
-      <c r="V8" s="187"/>
-      <c r="W8" s="187"/>
-      <c r="X8" s="187"/>
-      <c r="Y8" s="187"/>
-      <c r="Z8" s="187"/>
-      <c r="AA8" s="187"/>
-      <c r="AB8" s="187"/>
-      <c r="AC8" s="187"/>
-      <c r="AD8" s="187"/>
-      <c r="AE8" s="188"/>
-      <c r="AF8" s="183"/>
-      <c r="AG8" s="184"/>
-      <c r="AH8" s="184"/>
-      <c r="AI8" s="185"/>
+      <c r="B8" s="211"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="213"/>
+      <c r="E8" s="214"/>
+      <c r="F8" s="215"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="212"/>
+      <c r="J8" s="218"/>
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="220"/>
+      <c r="Q8" s="221"/>
+      <c r="R8" s="222"/>
+      <c r="S8" s="222"/>
+      <c r="T8" s="222"/>
+      <c r="U8" s="222"/>
+      <c r="V8" s="222"/>
+      <c r="W8" s="222"/>
+      <c r="X8" s="222"/>
+      <c r="Y8" s="222"/>
+      <c r="Z8" s="222"/>
+      <c r="AA8" s="222"/>
+      <c r="AB8" s="222"/>
+      <c r="AC8" s="222"/>
+      <c r="AD8" s="222"/>
+      <c r="AE8" s="223"/>
+      <c r="AF8" s="218"/>
+      <c r="AG8" s="219"/>
+      <c r="AH8" s="219"/>
+      <c r="AI8" s="220"/>
     </row>
     <row r="9" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="22"/>
-      <c r="B9" s="163"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="166"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="168"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="170"/>
-      <c r="L9" s="170"/>
-      <c r="M9" s="170"/>
-      <c r="N9" s="170"/>
-      <c r="O9" s="170"/>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="172"/>
-      <c r="R9" s="173"/>
-      <c r="S9" s="173"/>
-      <c r="T9" s="173"/>
-      <c r="U9" s="173"/>
-      <c r="V9" s="173"/>
-      <c r="W9" s="173"/>
-      <c r="X9" s="173"/>
-      <c r="Y9" s="173"/>
-      <c r="Z9" s="173"/>
-      <c r="AA9" s="173"/>
-      <c r="AB9" s="173"/>
-      <c r="AC9" s="173"/>
-      <c r="AD9" s="173"/>
-      <c r="AE9" s="174"/>
-      <c r="AF9" s="169"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="171"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="202"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="201"/>
+      <c r="H9" s="204"/>
+      <c r="I9" s="200"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="206"/>
+      <c r="O9" s="206"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="209"/>
+      <c r="S9" s="209"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="209"/>
+      <c r="V9" s="209"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
+      <c r="AD9" s="209"/>
+      <c r="AE9" s="210"/>
+      <c r="AF9" s="205"/>
+      <c r="AG9" s="206"/>
+      <c r="AH9" s="206"/>
+      <c r="AI9" s="207"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="22"/>
-      <c r="B10" s="163"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="165"/>
-      <c r="E10" s="166"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="170"/>
-      <c r="L10" s="170"/>
-      <c r="M10" s="170"/>
-      <c r="N10" s="170"/>
-      <c r="O10" s="170"/>
-      <c r="P10" s="171"/>
-      <c r="Q10" s="172"/>
-      <c r="R10" s="173"/>
-      <c r="S10" s="173"/>
-      <c r="T10" s="173"/>
-      <c r="U10" s="173"/>
-      <c r="V10" s="173"/>
-      <c r="W10" s="173"/>
-      <c r="X10" s="173"/>
-      <c r="Y10" s="173"/>
-      <c r="Z10" s="173"/>
-      <c r="AA10" s="173"/>
-      <c r="AB10" s="173"/>
-      <c r="AC10" s="173"/>
-      <c r="AD10" s="173"/>
-      <c r="AE10" s="174"/>
-      <c r="AF10" s="169"/>
-      <c r="AG10" s="170"/>
-      <c r="AH10" s="170"/>
-      <c r="AI10" s="171"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="204"/>
+      <c r="I10" s="200"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="206"/>
+      <c r="L10" s="206"/>
+      <c r="M10" s="206"/>
+      <c r="N10" s="206"/>
+      <c r="O10" s="206"/>
+      <c r="P10" s="207"/>
+      <c r="Q10" s="208"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="209"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="209"/>
+      <c r="V10" s="209"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
+      <c r="Z10" s="209"/>
+      <c r="AA10" s="209"/>
+      <c r="AB10" s="209"/>
+      <c r="AC10" s="209"/>
+      <c r="AD10" s="209"/>
+      <c r="AE10" s="210"/>
+      <c r="AF10" s="205"/>
+      <c r="AG10" s="206"/>
+      <c r="AH10" s="206"/>
+      <c r="AI10" s="207"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="22"/>
-      <c r="B11" s="163"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="166"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="168"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="169"/>
-      <c r="K11" s="170"/>
-      <c r="L11" s="170"/>
-      <c r="M11" s="170"/>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="172"/>
-      <c r="R11" s="173"/>
-      <c r="S11" s="173"/>
-      <c r="T11" s="173"/>
-      <c r="U11" s="173"/>
-      <c r="V11" s="173"/>
-      <c r="W11" s="173"/>
-      <c r="X11" s="173"/>
-      <c r="Y11" s="173"/>
-      <c r="Z11" s="173"/>
-      <c r="AA11" s="173"/>
-      <c r="AB11" s="173"/>
-      <c r="AC11" s="173"/>
-      <c r="AD11" s="173"/>
-      <c r="AE11" s="174"/>
-      <c r="AF11" s="169"/>
-      <c r="AG11" s="170"/>
-      <c r="AH11" s="170"/>
-      <c r="AI11" s="171"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="201"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="204"/>
+      <c r="I11" s="200"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="206"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="206"/>
+      <c r="P11" s="207"/>
+      <c r="Q11" s="208"/>
+      <c r="R11" s="209"/>
+      <c r="S11" s="209"/>
+      <c r="T11" s="209"/>
+      <c r="U11" s="209"/>
+      <c r="V11" s="209"/>
+      <c r="W11" s="209"/>
+      <c r="X11" s="209"/>
+      <c r="Y11" s="209"/>
+      <c r="Z11" s="209"/>
+      <c r="AA11" s="209"/>
+      <c r="AB11" s="209"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="209"/>
+      <c r="AE11" s="210"/>
+      <c r="AF11" s="205"/>
+      <c r="AG11" s="206"/>
+      <c r="AH11" s="206"/>
+      <c r="AI11" s="207"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="22"/>
-      <c r="B12" s="163"/>
-      <c r="C12" s="164"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="166"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="168"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="170"/>
-      <c r="L12" s="170"/>
-      <c r="M12" s="170"/>
-      <c r="N12" s="170"/>
-      <c r="O12" s="170"/>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="173"/>
-      <c r="S12" s="173"/>
-      <c r="T12" s="173"/>
-      <c r="U12" s="173"/>
-      <c r="V12" s="173"/>
-      <c r="W12" s="173"/>
-      <c r="X12" s="173"/>
-      <c r="Y12" s="173"/>
-      <c r="Z12" s="173"/>
-      <c r="AA12" s="173"/>
-      <c r="AB12" s="173"/>
-      <c r="AC12" s="173"/>
-      <c r="AD12" s="173"/>
-      <c r="AE12" s="174"/>
-      <c r="AF12" s="169"/>
-      <c r="AG12" s="170"/>
-      <c r="AH12" s="170"/>
-      <c r="AI12" s="171"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="200"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="204"/>
+      <c r="I12" s="200"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="206"/>
+      <c r="L12" s="206"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="206"/>
+      <c r="O12" s="206"/>
+      <c r="P12" s="207"/>
+      <c r="Q12" s="208"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="209"/>
+      <c r="T12" s="209"/>
+      <c r="U12" s="209"/>
+      <c r="V12" s="209"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
+      <c r="Z12" s="209"/>
+      <c r="AA12" s="209"/>
+      <c r="AB12" s="209"/>
+      <c r="AC12" s="209"/>
+      <c r="AD12" s="209"/>
+      <c r="AE12" s="210"/>
+      <c r="AF12" s="205"/>
+      <c r="AG12" s="206"/>
+      <c r="AH12" s="206"/>
+      <c r="AI12" s="207"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="22"/>
-      <c r="B13" s="163"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="167"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="168"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="169"/>
-      <c r="K13" s="170"/>
-      <c r="L13" s="170"/>
-      <c r="M13" s="170"/>
-      <c r="N13" s="170"/>
-      <c r="O13" s="170"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="172"/>
-      <c r="R13" s="173"/>
-      <c r="S13" s="173"/>
-      <c r="T13" s="173"/>
-      <c r="U13" s="173"/>
-      <c r="V13" s="173"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="173"/>
-      <c r="Y13" s="173"/>
-      <c r="Z13" s="173"/>
-      <c r="AA13" s="173"/>
-      <c r="AB13" s="173"/>
-      <c r="AC13" s="173"/>
-      <c r="AD13" s="173"/>
-      <c r="AE13" s="174"/>
-      <c r="AF13" s="169"/>
-      <c r="AG13" s="170"/>
-      <c r="AH13" s="170"/>
-      <c r="AI13" s="171"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="199"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="200"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="206"/>
+      <c r="L13" s="206"/>
+      <c r="M13" s="206"/>
+      <c r="N13" s="206"/>
+      <c r="O13" s="206"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="208"/>
+      <c r="R13" s="209"/>
+      <c r="S13" s="209"/>
+      <c r="T13" s="209"/>
+      <c r="U13" s="209"/>
+      <c r="V13" s="209"/>
+      <c r="W13" s="209"/>
+      <c r="X13" s="209"/>
+      <c r="Y13" s="209"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="209"/>
+      <c r="AB13" s="209"/>
+      <c r="AC13" s="209"/>
+      <c r="AD13" s="209"/>
+      <c r="AE13" s="210"/>
+      <c r="AF13" s="205"/>
+      <c r="AG13" s="206"/>
+      <c r="AH13" s="206"/>
+      <c r="AI13" s="207"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="22"/>
-      <c r="B14" s="163"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="165"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="168"/>
-      <c r="I14" s="164"/>
-      <c r="J14" s="169"/>
-      <c r="K14" s="170"/>
-      <c r="L14" s="170"/>
-      <c r="M14" s="170"/>
-      <c r="N14" s="170"/>
-      <c r="O14" s="170"/>
-      <c r="P14" s="171"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="173"/>
-      <c r="S14" s="173"/>
-      <c r="T14" s="173"/>
-      <c r="U14" s="173"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="173"/>
-      <c r="X14" s="173"/>
-      <c r="Y14" s="173"/>
-      <c r="Z14" s="173"/>
-      <c r="AA14" s="173"/>
-      <c r="AB14" s="173"/>
-      <c r="AC14" s="173"/>
-      <c r="AD14" s="173"/>
-      <c r="AE14" s="174"/>
-      <c r="AF14" s="169"/>
-      <c r="AG14" s="170"/>
-      <c r="AH14" s="170"/>
-      <c r="AI14" s="171"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="199"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="200"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="206"/>
+      <c r="L14" s="206"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="206"/>
+      <c r="O14" s="206"/>
+      <c r="P14" s="207"/>
+      <c r="Q14" s="208"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="209"/>
+      <c r="T14" s="209"/>
+      <c r="U14" s="209"/>
+      <c r="V14" s="209"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
+      <c r="Z14" s="209"/>
+      <c r="AA14" s="209"/>
+      <c r="AB14" s="209"/>
+      <c r="AC14" s="209"/>
+      <c r="AD14" s="209"/>
+      <c r="AE14" s="210"/>
+      <c r="AF14" s="205"/>
+      <c r="AG14" s="206"/>
+      <c r="AH14" s="206"/>
+      <c r="AI14" s="207"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="22"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="167"/>
-      <c r="G15" s="163"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="164"/>
-      <c r="J15" s="169"/>
-      <c r="K15" s="170"/>
-      <c r="L15" s="170"/>
-      <c r="M15" s="170"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="170"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="172"/>
-      <c r="R15" s="173"/>
-      <c r="S15" s="173"/>
-      <c r="T15" s="173"/>
-      <c r="U15" s="173"/>
-      <c r="V15" s="173"/>
-      <c r="W15" s="173"/>
-      <c r="X15" s="173"/>
-      <c r="Y15" s="173"/>
-      <c r="Z15" s="173"/>
-      <c r="AA15" s="173"/>
-      <c r="AB15" s="173"/>
-      <c r="AC15" s="173"/>
-      <c r="AD15" s="173"/>
-      <c r="AE15" s="174"/>
-      <c r="AF15" s="169"/>
-      <c r="AG15" s="170"/>
-      <c r="AH15" s="170"/>
-      <c r="AI15" s="171"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="199"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="206"/>
+      <c r="L15" s="206"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="206"/>
+      <c r="P15" s="207"/>
+      <c r="Q15" s="208"/>
+      <c r="R15" s="209"/>
+      <c r="S15" s="209"/>
+      <c r="T15" s="209"/>
+      <c r="U15" s="209"/>
+      <c r="V15" s="209"/>
+      <c r="W15" s="209"/>
+      <c r="X15" s="209"/>
+      <c r="Y15" s="209"/>
+      <c r="Z15" s="209"/>
+      <c r="AA15" s="209"/>
+      <c r="AB15" s="209"/>
+      <c r="AC15" s="209"/>
+      <c r="AD15" s="209"/>
+      <c r="AE15" s="210"/>
+      <c r="AF15" s="205"/>
+      <c r="AG15" s="206"/>
+      <c r="AH15" s="206"/>
+      <c r="AI15" s="207"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="22"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="164"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="170"/>
-      <c r="L16" s="170"/>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="170"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="172"/>
-      <c r="R16" s="173"/>
-      <c r="S16" s="173"/>
-      <c r="T16" s="173"/>
-      <c r="U16" s="173"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="173"/>
-      <c r="X16" s="173"/>
-      <c r="Y16" s="173"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="173"/>
-      <c r="AB16" s="173"/>
-      <c r="AC16" s="173"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="174"/>
-      <c r="AF16" s="169"/>
-      <c r="AG16" s="170"/>
-      <c r="AH16" s="170"/>
-      <c r="AI16" s="171"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="199"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="200"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="206"/>
+      <c r="L16" s="206"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="206"/>
+      <c r="O16" s="206"/>
+      <c r="P16" s="207"/>
+      <c r="Q16" s="208"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="209"/>
+      <c r="U16" s="209"/>
+      <c r="V16" s="209"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
+      <c r="Z16" s="209"/>
+      <c r="AA16" s="209"/>
+      <c r="AB16" s="209"/>
+      <c r="AC16" s="209"/>
+      <c r="AD16" s="209"/>
+      <c r="AE16" s="210"/>
+      <c r="AF16" s="205"/>
+      <c r="AG16" s="206"/>
+      <c r="AH16" s="206"/>
+      <c r="AI16" s="207"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="22"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="166"/>
-      <c r="F17" s="167"/>
-      <c r="G17" s="163"/>
-      <c r="H17" s="168"/>
-      <c r="I17" s="164"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="170"/>
-      <c r="L17" s="170"/>
-      <c r="M17" s="170"/>
-      <c r="N17" s="170"/>
-      <c r="O17" s="170"/>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="172"/>
-      <c r="R17" s="173"/>
-      <c r="S17" s="173"/>
-      <c r="T17" s="173"/>
-      <c r="U17" s="173"/>
-      <c r="V17" s="173"/>
-      <c r="W17" s="173"/>
-      <c r="X17" s="173"/>
-      <c r="Y17" s="173"/>
-      <c r="Z17" s="173"/>
-      <c r="AA17" s="173"/>
-      <c r="AB17" s="173"/>
-      <c r="AC17" s="173"/>
-      <c r="AD17" s="173"/>
-      <c r="AE17" s="174"/>
-      <c r="AF17" s="169"/>
-      <c r="AG17" s="170"/>
-      <c r="AH17" s="170"/>
-      <c r="AI17" s="171"/>
+      <c r="B17" s="199"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="201"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="199"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="200"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="206"/>
+      <c r="L17" s="206"/>
+      <c r="M17" s="206"/>
+      <c r="N17" s="206"/>
+      <c r="O17" s="206"/>
+      <c r="P17" s="207"/>
+      <c r="Q17" s="208"/>
+      <c r="R17" s="209"/>
+      <c r="S17" s="209"/>
+      <c r="T17" s="209"/>
+      <c r="U17" s="209"/>
+      <c r="V17" s="209"/>
+      <c r="W17" s="209"/>
+      <c r="X17" s="209"/>
+      <c r="Y17" s="209"/>
+      <c r="Z17" s="209"/>
+      <c r="AA17" s="209"/>
+      <c r="AB17" s="209"/>
+      <c r="AC17" s="209"/>
+      <c r="AD17" s="209"/>
+      <c r="AE17" s="210"/>
+      <c r="AF17" s="205"/>
+      <c r="AG17" s="206"/>
+      <c r="AH17" s="206"/>
+      <c r="AI17" s="207"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="B18" s="163"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="168"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="169"/>
-      <c r="K18" s="170"/>
-      <c r="L18" s="170"/>
-      <c r="M18" s="170"/>
-      <c r="N18" s="170"/>
-      <c r="O18" s="170"/>
-      <c r="P18" s="171"/>
-      <c r="Q18" s="172"/>
-      <c r="R18" s="173"/>
-      <c r="S18" s="173"/>
-      <c r="T18" s="173"/>
-      <c r="U18" s="173"/>
-      <c r="V18" s="173"/>
-      <c r="W18" s="173"/>
-      <c r="X18" s="173"/>
-      <c r="Y18" s="173"/>
-      <c r="Z18" s="173"/>
-      <c r="AA18" s="173"/>
-      <c r="AB18" s="173"/>
-      <c r="AC18" s="173"/>
-      <c r="AD18" s="173"/>
-      <c r="AE18" s="174"/>
-      <c r="AF18" s="169"/>
-      <c r="AG18" s="170"/>
-      <c r="AH18" s="170"/>
-      <c r="AI18" s="171"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="200"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="199"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="200"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="206"/>
+      <c r="L18" s="206"/>
+      <c r="M18" s="206"/>
+      <c r="N18" s="206"/>
+      <c r="O18" s="206"/>
+      <c r="P18" s="207"/>
+      <c r="Q18" s="208"/>
+      <c r="R18" s="209"/>
+      <c r="S18" s="209"/>
+      <c r="T18" s="209"/>
+      <c r="U18" s="209"/>
+      <c r="V18" s="209"/>
+      <c r="W18" s="209"/>
+      <c r="X18" s="209"/>
+      <c r="Y18" s="209"/>
+      <c r="Z18" s="209"/>
+      <c r="AA18" s="209"/>
+      <c r="AB18" s="209"/>
+      <c r="AC18" s="209"/>
+      <c r="AD18" s="209"/>
+      <c r="AE18" s="210"/>
+      <c r="AF18" s="205"/>
+      <c r="AG18" s="206"/>
+      <c r="AH18" s="206"/>
+      <c r="AI18" s="207"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="22"/>
-      <c r="B19" s="163"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="167"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="168"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="169"/>
-      <c r="K19" s="170"/>
-      <c r="L19" s="170"/>
-      <c r="M19" s="170"/>
-      <c r="N19" s="170"/>
-      <c r="O19" s="170"/>
-      <c r="P19" s="171"/>
-      <c r="Q19" s="172"/>
-      <c r="R19" s="173"/>
-      <c r="S19" s="173"/>
-      <c r="T19" s="173"/>
-      <c r="U19" s="173"/>
-      <c r="V19" s="173"/>
-      <c r="W19" s="173"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="173"/>
-      <c r="AA19" s="173"/>
-      <c r="AB19" s="173"/>
-      <c r="AC19" s="173"/>
-      <c r="AD19" s="173"/>
-      <c r="AE19" s="174"/>
-      <c r="AF19" s="169"/>
-      <c r="AG19" s="170"/>
-      <c r="AH19" s="170"/>
-      <c r="AI19" s="171"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="200"/>
+      <c r="D19" s="201"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="199"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="200"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="206"/>
+      <c r="L19" s="206"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="206"/>
+      <c r="P19" s="207"/>
+      <c r="Q19" s="208"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
+      <c r="W19" s="209"/>
+      <c r="X19" s="209"/>
+      <c r="Y19" s="209"/>
+      <c r="Z19" s="209"/>
+      <c r="AA19" s="209"/>
+      <c r="AB19" s="209"/>
+      <c r="AC19" s="209"/>
+      <c r="AD19" s="209"/>
+      <c r="AE19" s="210"/>
+      <c r="AF19" s="205"/>
+      <c r="AG19" s="206"/>
+      <c r="AH19" s="206"/>
+      <c r="AI19" s="207"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="22"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="166"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="168"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="170"/>
-      <c r="L20" s="170"/>
-      <c r="M20" s="170"/>
-      <c r="N20" s="170"/>
-      <c r="O20" s="170"/>
-      <c r="P20" s="171"/>
-      <c r="Q20" s="172"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="173"/>
-      <c r="T20" s="173"/>
-      <c r="U20" s="173"/>
-      <c r="V20" s="173"/>
-      <c r="W20" s="173"/>
-      <c r="X20" s="173"/>
-      <c r="Y20" s="173"/>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="173"/>
-      <c r="AB20" s="173"/>
-      <c r="AC20" s="173"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="174"/>
-      <c r="AF20" s="169"/>
-      <c r="AG20" s="170"/>
-      <c r="AH20" s="170"/>
-      <c r="AI20" s="171"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="201"/>
+      <c r="E20" s="202"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="199"/>
+      <c r="H20" s="204"/>
+      <c r="I20" s="200"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="206"/>
+      <c r="L20" s="206"/>
+      <c r="M20" s="206"/>
+      <c r="N20" s="206"/>
+      <c r="O20" s="206"/>
+      <c r="P20" s="207"/>
+      <c r="Q20" s="208"/>
+      <c r="R20" s="209"/>
+      <c r="S20" s="209"/>
+      <c r="T20" s="209"/>
+      <c r="U20" s="209"/>
+      <c r="V20" s="209"/>
+      <c r="W20" s="209"/>
+      <c r="X20" s="209"/>
+      <c r="Y20" s="209"/>
+      <c r="Z20" s="209"/>
+      <c r="AA20" s="209"/>
+      <c r="AB20" s="209"/>
+      <c r="AC20" s="209"/>
+      <c r="AD20" s="209"/>
+      <c r="AE20" s="210"/>
+      <c r="AF20" s="205"/>
+      <c r="AG20" s="206"/>
+      <c r="AH20" s="206"/>
+      <c r="AI20" s="207"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="22"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="164"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="167"/>
-      <c r="G21" s="163"/>
-      <c r="H21" s="168"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="170"/>
-      <c r="L21" s="170"/>
-      <c r="M21" s="170"/>
-      <c r="N21" s="170"/>
-      <c r="O21" s="170"/>
-      <c r="P21" s="171"/>
-      <c r="Q21" s="172"/>
-      <c r="R21" s="173"/>
-      <c r="S21" s="173"/>
-      <c r="T21" s="173"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="174"/>
-      <c r="AF21" s="169"/>
-      <c r="AG21" s="170"/>
-      <c r="AH21" s="170"/>
-      <c r="AI21" s="171"/>
+      <c r="B21" s="199"/>
+      <c r="C21" s="200"/>
+      <c r="D21" s="201"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="199"/>
+      <c r="H21" s="204"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="206"/>
+      <c r="M21" s="206"/>
+      <c r="N21" s="206"/>
+      <c r="O21" s="206"/>
+      <c r="P21" s="207"/>
+      <c r="Q21" s="208"/>
+      <c r="R21" s="209"/>
+      <c r="S21" s="209"/>
+      <c r="T21" s="209"/>
+      <c r="U21" s="209"/>
+      <c r="V21" s="209"/>
+      <c r="W21" s="209"/>
+      <c r="X21" s="209"/>
+      <c r="Y21" s="209"/>
+      <c r="Z21" s="209"/>
+      <c r="AA21" s="209"/>
+      <c r="AB21" s="209"/>
+      <c r="AC21" s="209"/>
+      <c r="AD21" s="209"/>
+      <c r="AE21" s="210"/>
+      <c r="AF21" s="205"/>
+      <c r="AG21" s="206"/>
+      <c r="AH21" s="206"/>
+      <c r="AI21" s="207"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="22"/>
-      <c r="B22" s="163"/>
-      <c r="C22" s="164"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="167"/>
-      <c r="G22" s="163"/>
-      <c r="H22" s="168"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="170"/>
-      <c r="M22" s="170"/>
-      <c r="N22" s="170"/>
-      <c r="O22" s="170"/>
-      <c r="P22" s="171"/>
-      <c r="Q22" s="172"/>
-      <c r="R22" s="173"/>
-      <c r="S22" s="173"/>
-      <c r="T22" s="173"/>
-      <c r="U22" s="173"/>
-      <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
-      <c r="X22" s="173"/>
-      <c r="Y22" s="173"/>
-      <c r="Z22" s="173"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="173"/>
-      <c r="AC22" s="173"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="174"/>
-      <c r="AF22" s="169"/>
-      <c r="AG22" s="170"/>
-      <c r="AH22" s="170"/>
-      <c r="AI22" s="171"/>
+      <c r="B22" s="199"/>
+      <c r="C22" s="200"/>
+      <c r="D22" s="201"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="204"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="206"/>
+      <c r="L22" s="206"/>
+      <c r="M22" s="206"/>
+      <c r="N22" s="206"/>
+      <c r="O22" s="206"/>
+      <c r="P22" s="207"/>
+      <c r="Q22" s="208"/>
+      <c r="R22" s="209"/>
+      <c r="S22" s="209"/>
+      <c r="T22" s="209"/>
+      <c r="U22" s="209"/>
+      <c r="V22" s="209"/>
+      <c r="W22" s="209"/>
+      <c r="X22" s="209"/>
+      <c r="Y22" s="209"/>
+      <c r="Z22" s="209"/>
+      <c r="AA22" s="209"/>
+      <c r="AB22" s="209"/>
+      <c r="AC22" s="209"/>
+      <c r="AD22" s="209"/>
+      <c r="AE22" s="210"/>
+      <c r="AF22" s="205"/>
+      <c r="AG22" s="206"/>
+      <c r="AH22" s="206"/>
+      <c r="AI22" s="207"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="22"/>
-      <c r="B23" s="163"/>
-      <c r="C23" s="164"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="167"/>
-      <c r="G23" s="163"/>
-      <c r="H23" s="168"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="170"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="170"/>
-      <c r="O23" s="170"/>
-      <c r="P23" s="171"/>
-      <c r="Q23" s="172"/>
-      <c r="R23" s="173"/>
-      <c r="S23" s="173"/>
-      <c r="T23" s="173"/>
-      <c r="U23" s="173"/>
-      <c r="V23" s="173"/>
-      <c r="W23" s="173"/>
-      <c r="X23" s="173"/>
-      <c r="Y23" s="173"/>
-      <c r="Z23" s="173"/>
-      <c r="AA23" s="173"/>
-      <c r="AB23" s="173"/>
-      <c r="AC23" s="173"/>
-      <c r="AD23" s="173"/>
-      <c r="AE23" s="174"/>
-      <c r="AF23" s="169"/>
-      <c r="AG23" s="170"/>
-      <c r="AH23" s="170"/>
-      <c r="AI23" s="171"/>
+      <c r="B23" s="199"/>
+      <c r="C23" s="200"/>
+      <c r="D23" s="201"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="199"/>
+      <c r="H23" s="204"/>
+      <c r="I23" s="200"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="206"/>
+      <c r="L23" s="206"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="206"/>
+      <c r="O23" s="206"/>
+      <c r="P23" s="207"/>
+      <c r="Q23" s="208"/>
+      <c r="R23" s="209"/>
+      <c r="S23" s="209"/>
+      <c r="T23" s="209"/>
+      <c r="U23" s="209"/>
+      <c r="V23" s="209"/>
+      <c r="W23" s="209"/>
+      <c r="X23" s="209"/>
+      <c r="Y23" s="209"/>
+      <c r="Z23" s="209"/>
+      <c r="AA23" s="209"/>
+      <c r="AB23" s="209"/>
+      <c r="AC23" s="209"/>
+      <c r="AD23" s="209"/>
+      <c r="AE23" s="210"/>
+      <c r="AF23" s="205"/>
+      <c r="AG23" s="206"/>
+      <c r="AH23" s="206"/>
+      <c r="AI23" s="207"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="22"/>
-      <c r="B24" s="163"/>
-      <c r="C24" s="164"/>
-      <c r="D24" s="165"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="170"/>
-      <c r="O24" s="170"/>
-      <c r="P24" s="171"/>
-      <c r="Q24" s="172"/>
-      <c r="R24" s="173"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="174"/>
-      <c r="AF24" s="169"/>
-      <c r="AG24" s="170"/>
-      <c r="AH24" s="170"/>
-      <c r="AI24" s="171"/>
+      <c r="B24" s="199"/>
+      <c r="C24" s="200"/>
+      <c r="D24" s="201"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="199"/>
+      <c r="H24" s="204"/>
+      <c r="I24" s="200"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="206"/>
+      <c r="L24" s="206"/>
+      <c r="M24" s="206"/>
+      <c r="N24" s="206"/>
+      <c r="O24" s="206"/>
+      <c r="P24" s="207"/>
+      <c r="Q24" s="208"/>
+      <c r="R24" s="209"/>
+      <c r="S24" s="209"/>
+      <c r="T24" s="209"/>
+      <c r="U24" s="209"/>
+      <c r="V24" s="209"/>
+      <c r="W24" s="209"/>
+      <c r="X24" s="209"/>
+      <c r="Y24" s="209"/>
+      <c r="Z24" s="209"/>
+      <c r="AA24" s="209"/>
+      <c r="AB24" s="209"/>
+      <c r="AC24" s="209"/>
+      <c r="AD24" s="209"/>
+      <c r="AE24" s="210"/>
+      <c r="AF24" s="205"/>
+      <c r="AG24" s="206"/>
+      <c r="AH24" s="206"/>
+      <c r="AI24" s="207"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="22"/>
-      <c r="B25" s="163"/>
-      <c r="C25" s="164"/>
-      <c r="D25" s="165"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="167"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="168"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="170"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="170"/>
-      <c r="O25" s="170"/>
-      <c r="P25" s="171"/>
-      <c r="Q25" s="172"/>
-      <c r="R25" s="173"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="173"/>
-      <c r="U25" s="173"/>
-      <c r="V25" s="173"/>
-      <c r="W25" s="173"/>
-      <c r="X25" s="173"/>
-      <c r="Y25" s="173"/>
-      <c r="Z25" s="173"/>
-      <c r="AA25" s="173"/>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="173"/>
-      <c r="AD25" s="173"/>
-      <c r="AE25" s="174"/>
-      <c r="AF25" s="169"/>
-      <c r="AG25" s="170"/>
-      <c r="AH25" s="170"/>
-      <c r="AI25" s="171"/>
+      <c r="B25" s="199"/>
+      <c r="C25" s="200"/>
+      <c r="D25" s="201"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="199"/>
+      <c r="H25" s="204"/>
+      <c r="I25" s="200"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="206"/>
+      <c r="L25" s="206"/>
+      <c r="M25" s="206"/>
+      <c r="N25" s="206"/>
+      <c r="O25" s="206"/>
+      <c r="P25" s="207"/>
+      <c r="Q25" s="208"/>
+      <c r="R25" s="209"/>
+      <c r="S25" s="209"/>
+      <c r="T25" s="209"/>
+      <c r="U25" s="209"/>
+      <c r="V25" s="209"/>
+      <c r="W25" s="209"/>
+      <c r="X25" s="209"/>
+      <c r="Y25" s="209"/>
+      <c r="Z25" s="209"/>
+      <c r="AA25" s="209"/>
+      <c r="AB25" s="209"/>
+      <c r="AC25" s="209"/>
+      <c r="AD25" s="209"/>
+      <c r="AE25" s="210"/>
+      <c r="AF25" s="205"/>
+      <c r="AG25" s="206"/>
+      <c r="AH25" s="206"/>
+      <c r="AI25" s="207"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="22"/>
-      <c r="B26" s="163"/>
-      <c r="C26" s="164"/>
-      <c r="D26" s="165"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="163"/>
-      <c r="H26" s="168"/>
-      <c r="I26" s="164"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="170"/>
-      <c r="M26" s="170"/>
-      <c r="N26" s="170"/>
-      <c r="O26" s="170"/>
-      <c r="P26" s="171"/>
-      <c r="Q26" s="172"/>
-      <c r="R26" s="173"/>
-      <c r="S26" s="173"/>
-      <c r="T26" s="173"/>
-      <c r="U26" s="173"/>
-      <c r="V26" s="173"/>
-      <c r="W26" s="173"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="173"/>
-      <c r="Z26" s="173"/>
-      <c r="AA26" s="173"/>
-      <c r="AB26" s="173"/>
-      <c r="AC26" s="173"/>
-      <c r="AD26" s="173"/>
-      <c r="AE26" s="174"/>
-      <c r="AF26" s="169"/>
-      <c r="AG26" s="170"/>
-      <c r="AH26" s="170"/>
-      <c r="AI26" s="171"/>
+      <c r="B26" s="199"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="201"/>
+      <c r="E26" s="202"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="199"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="206"/>
+      <c r="L26" s="206"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="206"/>
+      <c r="O26" s="206"/>
+      <c r="P26" s="207"/>
+      <c r="Q26" s="208"/>
+      <c r="R26" s="209"/>
+      <c r="S26" s="209"/>
+      <c r="T26" s="209"/>
+      <c r="U26" s="209"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="209"/>
+      <c r="X26" s="209"/>
+      <c r="Y26" s="209"/>
+      <c r="Z26" s="209"/>
+      <c r="AA26" s="209"/>
+      <c r="AB26" s="209"/>
+      <c r="AC26" s="209"/>
+      <c r="AD26" s="209"/>
+      <c r="AE26" s="210"/>
+      <c r="AF26" s="205"/>
+      <c r="AG26" s="206"/>
+      <c r="AH26" s="206"/>
+      <c r="AI26" s="207"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="22"/>
-      <c r="B27" s="163"/>
-      <c r="C27" s="164"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="166"/>
-      <c r="F27" s="167"/>
-      <c r="G27" s="163"/>
-      <c r="H27" s="168"/>
-      <c r="I27" s="164"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
-      <c r="P27" s="171"/>
-      <c r="Q27" s="172"/>
-      <c r="R27" s="173"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="173"/>
-      <c r="V27" s="173"/>
-      <c r="W27" s="173"/>
-      <c r="X27" s="173"/>
-      <c r="Y27" s="173"/>
-      <c r="Z27" s="173"/>
-      <c r="AA27" s="173"/>
-      <c r="AB27" s="173"/>
-      <c r="AC27" s="173"/>
-      <c r="AD27" s="173"/>
-      <c r="AE27" s="174"/>
-      <c r="AF27" s="169"/>
-      <c r="AG27" s="170"/>
-      <c r="AH27" s="170"/>
-      <c r="AI27" s="171"/>
+      <c r="B27" s="199"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="199"/>
+      <c r="H27" s="204"/>
+      <c r="I27" s="200"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="206"/>
+      <c r="L27" s="206"/>
+      <c r="M27" s="206"/>
+      <c r="N27" s="206"/>
+      <c r="O27" s="206"/>
+      <c r="P27" s="207"/>
+      <c r="Q27" s="208"/>
+      <c r="R27" s="209"/>
+      <c r="S27" s="209"/>
+      <c r="T27" s="209"/>
+      <c r="U27" s="209"/>
+      <c r="V27" s="209"/>
+      <c r="W27" s="209"/>
+      <c r="X27" s="209"/>
+      <c r="Y27" s="209"/>
+      <c r="Z27" s="209"/>
+      <c r="AA27" s="209"/>
+      <c r="AB27" s="209"/>
+      <c r="AC27" s="209"/>
+      <c r="AD27" s="209"/>
+      <c r="AE27" s="210"/>
+      <c r="AF27" s="205"/>
+      <c r="AG27" s="206"/>
+      <c r="AH27" s="206"/>
+      <c r="AI27" s="207"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="22"/>
-      <c r="B28" s="163"/>
-      <c r="C28" s="164"/>
-      <c r="D28" s="165"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="168"/>
-      <c r="I28" s="164"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
-      <c r="P28" s="171"/>
-      <c r="Q28" s="172"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="173"/>
-      <c r="V28" s="173"/>
-      <c r="W28" s="173"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="173"/>
-      <c r="Z28" s="173"/>
-      <c r="AA28" s="173"/>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="173"/>
-      <c r="AD28" s="173"/>
-      <c r="AE28" s="174"/>
-      <c r="AF28" s="169"/>
-      <c r="AG28" s="170"/>
-      <c r="AH28" s="170"/>
-      <c r="AI28" s="171"/>
+      <c r="B28" s="199"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="201"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="199"/>
+      <c r="H28" s="204"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="206"/>
+      <c r="L28" s="206"/>
+      <c r="M28" s="206"/>
+      <c r="N28" s="206"/>
+      <c r="O28" s="206"/>
+      <c r="P28" s="207"/>
+      <c r="Q28" s="208"/>
+      <c r="R28" s="209"/>
+      <c r="S28" s="209"/>
+      <c r="T28" s="209"/>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="209"/>
+      <c r="Z28" s="209"/>
+      <c r="AA28" s="209"/>
+      <c r="AB28" s="209"/>
+      <c r="AC28" s="209"/>
+      <c r="AD28" s="209"/>
+      <c r="AE28" s="210"/>
+      <c r="AF28" s="205"/>
+      <c r="AG28" s="206"/>
+      <c r="AH28" s="206"/>
+      <c r="AI28" s="207"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="22"/>
-      <c r="B29" s="163"/>
-      <c r="C29" s="164"/>
-      <c r="D29" s="165"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
-      <c r="G29" s="163"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="169"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
-      <c r="P29" s="171"/>
-      <c r="Q29" s="172"/>
-      <c r="R29" s="173"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="173"/>
-      <c r="V29" s="173"/>
-      <c r="W29" s="173"/>
-      <c r="X29" s="173"/>
-      <c r="Y29" s="173"/>
-      <c r="Z29" s="173"/>
-      <c r="AA29" s="173"/>
-      <c r="AB29" s="173"/>
-      <c r="AC29" s="173"/>
-      <c r="AD29" s="173"/>
-      <c r="AE29" s="174"/>
-      <c r="AF29" s="169"/>
-      <c r="AG29" s="170"/>
-      <c r="AH29" s="170"/>
-      <c r="AI29" s="171"/>
+      <c r="B29" s="199"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="201"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="199"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="206"/>
+      <c r="L29" s="206"/>
+      <c r="M29" s="206"/>
+      <c r="N29" s="206"/>
+      <c r="O29" s="206"/>
+      <c r="P29" s="207"/>
+      <c r="Q29" s="208"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="209"/>
+      <c r="T29" s="209"/>
+      <c r="U29" s="209"/>
+      <c r="V29" s="209"/>
+      <c r="W29" s="209"/>
+      <c r="X29" s="209"/>
+      <c r="Y29" s="209"/>
+      <c r="Z29" s="209"/>
+      <c r="AA29" s="209"/>
+      <c r="AB29" s="209"/>
+      <c r="AC29" s="209"/>
+      <c r="AD29" s="209"/>
+      <c r="AE29" s="210"/>
+      <c r="AF29" s="205"/>
+      <c r="AG29" s="206"/>
+      <c r="AH29" s="206"/>
+      <c r="AI29" s="207"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="22"/>
-      <c r="B30" s="163"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="166"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="163"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="171"/>
-      <c r="Q30" s="172"/>
-      <c r="R30" s="173"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="173"/>
-      <c r="V30" s="173"/>
-      <c r="W30" s="173"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="173"/>
-      <c r="Z30" s="173"/>
-      <c r="AA30" s="173"/>
-      <c r="AB30" s="173"/>
-      <c r="AC30" s="173"/>
-      <c r="AD30" s="173"/>
-      <c r="AE30" s="174"/>
-      <c r="AF30" s="169"/>
-      <c r="AG30" s="170"/>
-      <c r="AH30" s="170"/>
-      <c r="AI30" s="171"/>
+      <c r="B30" s="199"/>
+      <c r="C30" s="200"/>
+      <c r="D30" s="201"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="199"/>
+      <c r="H30" s="204"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="206"/>
+      <c r="L30" s="206"/>
+      <c r="M30" s="206"/>
+      <c r="N30" s="206"/>
+      <c r="O30" s="206"/>
+      <c r="P30" s="207"/>
+      <c r="Q30" s="208"/>
+      <c r="R30" s="209"/>
+      <c r="S30" s="209"/>
+      <c r="T30" s="209"/>
+      <c r="U30" s="209"/>
+      <c r="V30" s="209"/>
+      <c r="W30" s="209"/>
+      <c r="X30" s="209"/>
+      <c r="Y30" s="209"/>
+      <c r="Z30" s="209"/>
+      <c r="AA30" s="209"/>
+      <c r="AB30" s="209"/>
+      <c r="AC30" s="209"/>
+      <c r="AD30" s="209"/>
+      <c r="AE30" s="210"/>
+      <c r="AF30" s="205"/>
+      <c r="AG30" s="206"/>
+      <c r="AH30" s="206"/>
+      <c r="AI30" s="207"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="22"/>
-      <c r="B31" s="163"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="165"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="167"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="168"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="171"/>
-      <c r="Q31" s="172"/>
-      <c r="R31" s="173"/>
-      <c r="S31" s="173"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="173"/>
-      <c r="V31" s="173"/>
-      <c r="W31" s="173"/>
-      <c r="X31" s="173"/>
-      <c r="Y31" s="173"/>
-      <c r="Z31" s="173"/>
-      <c r="AA31" s="173"/>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="174"/>
-      <c r="AF31" s="169"/>
-      <c r="AG31" s="170"/>
-      <c r="AH31" s="170"/>
-      <c r="AI31" s="171"/>
+      <c r="B31" s="199"/>
+      <c r="C31" s="200"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="199"/>
+      <c r="H31" s="204"/>
+      <c r="I31" s="200"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="206"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="206"/>
+      <c r="O31" s="206"/>
+      <c r="P31" s="207"/>
+      <c r="Q31" s="208"/>
+      <c r="R31" s="209"/>
+      <c r="S31" s="209"/>
+      <c r="T31" s="209"/>
+      <c r="U31" s="209"/>
+      <c r="V31" s="209"/>
+      <c r="W31" s="209"/>
+      <c r="X31" s="209"/>
+      <c r="Y31" s="209"/>
+      <c r="Z31" s="209"/>
+      <c r="AA31" s="209"/>
+      <c r="AB31" s="209"/>
+      <c r="AC31" s="209"/>
+      <c r="AD31" s="209"/>
+      <c r="AE31" s="210"/>
+      <c r="AF31" s="205"/>
+      <c r="AG31" s="206"/>
+      <c r="AH31" s="206"/>
+      <c r="AI31" s="207"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="22"/>
-      <c r="B32" s="163"/>
-      <c r="C32" s="164"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="166"/>
-      <c r="F32" s="167"/>
-      <c r="G32" s="163"/>
-      <c r="H32" s="168"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
-      <c r="P32" s="171"/>
-      <c r="Q32" s="172"/>
-      <c r="R32" s="173"/>
-      <c r="S32" s="173"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="173"/>
-      <c r="V32" s="173"/>
-      <c r="W32" s="173"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="173"/>
-      <c r="Z32" s="173"/>
-      <c r="AA32" s="173"/>
-      <c r="AB32" s="173"/>
-      <c r="AC32" s="173"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="174"/>
-      <c r="AF32" s="169"/>
-      <c r="AG32" s="170"/>
-      <c r="AH32" s="170"/>
-      <c r="AI32" s="171"/>
+      <c r="B32" s="199"/>
+      <c r="C32" s="200"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="199"/>
+      <c r="H32" s="204"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="206"/>
+      <c r="O32" s="206"/>
+      <c r="P32" s="207"/>
+      <c r="Q32" s="208"/>
+      <c r="R32" s="209"/>
+      <c r="S32" s="209"/>
+      <c r="T32" s="209"/>
+      <c r="U32" s="209"/>
+      <c r="V32" s="209"/>
+      <c r="W32" s="209"/>
+      <c r="X32" s="209"/>
+      <c r="Y32" s="209"/>
+      <c r="Z32" s="209"/>
+      <c r="AA32" s="209"/>
+      <c r="AB32" s="209"/>
+      <c r="AC32" s="209"/>
+      <c r="AD32" s="209"/>
+      <c r="AE32" s="210"/>
+      <c r="AF32" s="205"/>
+      <c r="AG32" s="206"/>
+      <c r="AH32" s="206"/>
+      <c r="AI32" s="207"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="22"/>
-      <c r="B33" s="163"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="165"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="167"/>
-      <c r="G33" s="163"/>
-      <c r="H33" s="168"/>
-      <c r="I33" s="164"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="170"/>
-      <c r="L33" s="170"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="170"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="171"/>
-      <c r="Q33" s="172"/>
-      <c r="R33" s="173"/>
-      <c r="S33" s="173"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="173"/>
-      <c r="V33" s="173"/>
-      <c r="W33" s="173"/>
-      <c r="X33" s="173"/>
-      <c r="Y33" s="173"/>
-      <c r="Z33" s="173"/>
-      <c r="AA33" s="173"/>
-      <c r="AB33" s="173"/>
-      <c r="AC33" s="173"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="174"/>
-      <c r="AF33" s="169"/>
-      <c r="AG33" s="170"/>
-      <c r="AH33" s="170"/>
-      <c r="AI33" s="171"/>
+      <c r="B33" s="199"/>
+      <c r="C33" s="200"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="202"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="199"/>
+      <c r="H33" s="204"/>
+      <c r="I33" s="200"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="206"/>
+      <c r="P33" s="207"/>
+      <c r="Q33" s="208"/>
+      <c r="R33" s="209"/>
+      <c r="S33" s="209"/>
+      <c r="T33" s="209"/>
+      <c r="U33" s="209"/>
+      <c r="V33" s="209"/>
+      <c r="W33" s="209"/>
+      <c r="X33" s="209"/>
+      <c r="Y33" s="209"/>
+      <c r="Z33" s="209"/>
+      <c r="AA33" s="209"/>
+      <c r="AB33" s="209"/>
+      <c r="AC33" s="209"/>
+      <c r="AD33" s="209"/>
+      <c r="AE33" s="210"/>
+      <c r="AF33" s="205"/>
+      <c r="AG33" s="206"/>
+      <c r="AH33" s="206"/>
+      <c r="AI33" s="207"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -11712,162 +11864,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -21862,7 +21858,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="25" t="s">
-        <v>554</v>
+        <v>20</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>22</v>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D47826-AD4B-44E5-8841-D18C331B4473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D11AB5E-CF61-443E-BF4D-0D9EE7A7AD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8851,6 +8851,84 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8957,84 +9035,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10490,55 +10490,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="174"/>
-      <c r="O1" s="178" t="s">
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="200"/>
+      <c r="O1" s="204" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="179"/>
-      <c r="Q1" s="179"/>
-      <c r="R1" s="180"/>
-      <c r="S1" s="187" t="s">
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="188"/>
-      <c r="U1" s="188"/>
-      <c r="V1" s="188"/>
-      <c r="W1" s="188"/>
-      <c r="X1" s="188"/>
-      <c r="Y1" s="188"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="169" t="s">
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="214"/>
+      <c r="Y1" s="214"/>
+      <c r="Z1" s="215"/>
+      <c r="AA1" s="195" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" s="171"/>
-      <c r="AC1" s="196" t="str">
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="222" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="197"/>
-      <c r="AE1" s="197"/>
-      <c r="AF1" s="198"/>
-      <c r="AG1" s="163" t="str">
+      <c r="AD1" s="223"/>
+      <c r="AE1" s="223"/>
+      <c r="AF1" s="224"/>
+      <c r="AG1" s="189" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="164"/>
-      <c r="AI1" s="165"/>
+      <c r="AH1" s="190"/>
+      <c r="AI1" s="191"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -10546,51 +10546,51 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="195" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="174"/>
-      <c r="O2" s="181"/>
-      <c r="P2" s="182"/>
-      <c r="Q2" s="182"/>
-      <c r="R2" s="183"/>
-      <c r="S2" s="190"/>
-      <c r="T2" s="191"/>
-      <c r="U2" s="191"/>
-      <c r="V2" s="191"/>
-      <c r="W2" s="191"/>
-      <c r="X2" s="191"/>
-      <c r="Y2" s="191"/>
-      <c r="Z2" s="192"/>
-      <c r="AA2" s="169" t="s">
+      <c r="B2" s="196"/>
+      <c r="C2" s="196"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+      <c r="J2" s="199"/>
+      <c r="K2" s="199"/>
+      <c r="L2" s="199"/>
+      <c r="M2" s="199"/>
+      <c r="N2" s="200"/>
+      <c r="O2" s="207"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="209"/>
+      <c r="S2" s="216"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="217"/>
+      <c r="V2" s="217"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="217"/>
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="AB2" s="171"/>
-      <c r="AC2" s="175" t="str">
+      <c r="AB2" s="197"/>
+      <c r="AC2" s="201" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="176"/>
-      <c r="AE2" s="176"/>
-      <c r="AF2" s="177"/>
-      <c r="AG2" s="163" t="str">
+      <c r="AD2" s="202"/>
+      <c r="AE2" s="202"/>
+      <c r="AF2" s="203"/>
+      <c r="AG2" s="189" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="164"/>
-      <c r="AI2" s="165"/>
+      <c r="AH2" s="190"/>
+      <c r="AI2" s="191"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -10598,43 +10598,43 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="195" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="184"/>
-      <c r="P3" s="185"/>
-      <c r="Q3" s="185"/>
-      <c r="R3" s="186"/>
-      <c r="S3" s="193"/>
-      <c r="T3" s="194"/>
-      <c r="U3" s="194"/>
-      <c r="V3" s="194"/>
-      <c r="W3" s="194"/>
-      <c r="X3" s="194"/>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="195"/>
-      <c r="AA3" s="169"/>
-      <c r="AB3" s="171"/>
-      <c r="AC3" s="196"/>
-      <c r="AD3" s="197"/>
-      <c r="AE3" s="197"/>
-      <c r="AF3" s="198"/>
-      <c r="AG3" s="163"/>
-      <c r="AH3" s="164"/>
-      <c r="AI3" s="165"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="199"/>
+      <c r="I3" s="199"/>
+      <c r="J3" s="199"/>
+      <c r="K3" s="199"/>
+      <c r="L3" s="199"/>
+      <c r="M3" s="199"/>
+      <c r="N3" s="200"/>
+      <c r="O3" s="210"/>
+      <c r="P3" s="211"/>
+      <c r="Q3" s="211"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="219"/>
+      <c r="T3" s="220"/>
+      <c r="U3" s="220"/>
+      <c r="V3" s="220"/>
+      <c r="W3" s="220"/>
+      <c r="X3" s="220"/>
+      <c r="Y3" s="220"/>
+      <c r="Z3" s="221"/>
+      <c r="AA3" s="195"/>
+      <c r="AB3" s="197"/>
+      <c r="AC3" s="222"/>
+      <c r="AD3" s="223"/>
+      <c r="AE3" s="223"/>
+      <c r="AF3" s="224"/>
+      <c r="AG3" s="189"/>
+      <c r="AH3" s="190"/>
+      <c r="AI3" s="191"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -10671,1176 +10671,1020 @@
       <c r="A7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="166" t="s">
+      <c r="B7" s="192" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="167"/>
-      <c r="D7" s="166" t="s">
+      <c r="C7" s="193"/>
+      <c r="D7" s="192" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="168"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="166" t="s">
+      <c r="E7" s="194"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="192" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="168"/>
-      <c r="I7" s="167"/>
-      <c r="J7" s="166" t="s">
+      <c r="H7" s="194"/>
+      <c r="I7" s="193"/>
+      <c r="J7" s="192" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="166" t="s">
+      <c r="K7" s="194"/>
+      <c r="L7" s="194"/>
+      <c r="M7" s="194"/>
+      <c r="N7" s="194"/>
+      <c r="O7" s="194"/>
+      <c r="P7" s="193"/>
+      <c r="Q7" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="168"/>
-      <c r="S7" s="168"/>
-      <c r="T7" s="168"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="168"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="168"/>
-      <c r="AA7" s="168"/>
-      <c r="AB7" s="168"/>
-      <c r="AC7" s="168"/>
-      <c r="AD7" s="168"/>
-      <c r="AE7" s="167"/>
-      <c r="AF7" s="166" t="s">
+      <c r="R7" s="194"/>
+      <c r="S7" s="194"/>
+      <c r="T7" s="194"/>
+      <c r="U7" s="194"/>
+      <c r="V7" s="194"/>
+      <c r="W7" s="194"/>
+      <c r="X7" s="194"/>
+      <c r="Y7" s="194"/>
+      <c r="Z7" s="194"/>
+      <c r="AA7" s="194"/>
+      <c r="AB7" s="194"/>
+      <c r="AC7" s="194"/>
+      <c r="AD7" s="194"/>
+      <c r="AE7" s="193"/>
+      <c r="AF7" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="AG7" s="168"/>
-      <c r="AH7" s="168"/>
-      <c r="AI7" s="167"/>
+      <c r="AG7" s="194"/>
+      <c r="AH7" s="194"/>
+      <c r="AI7" s="193"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="21"/>
-      <c r="B8" s="211"/>
-      <c r="C8" s="212"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="214"/>
-      <c r="F8" s="215"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="217"/>
-      <c r="I8" s="212"/>
-      <c r="J8" s="218"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="220"/>
-      <c r="Q8" s="221"/>
-      <c r="R8" s="222"/>
-      <c r="S8" s="222"/>
-      <c r="T8" s="222"/>
-      <c r="U8" s="222"/>
-      <c r="V8" s="222"/>
-      <c r="W8" s="222"/>
-      <c r="X8" s="222"/>
-      <c r="Y8" s="222"/>
-      <c r="Z8" s="222"/>
-      <c r="AA8" s="222"/>
-      <c r="AB8" s="222"/>
-      <c r="AC8" s="222"/>
-      <c r="AD8" s="222"/>
-      <c r="AE8" s="223"/>
-      <c r="AF8" s="218"/>
-      <c r="AG8" s="219"/>
-      <c r="AH8" s="219"/>
-      <c r="AI8" s="220"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="179"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="181"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="177"/>
+      <c r="J8" s="183"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="186"/>
+      <c r="R8" s="187"/>
+      <c r="S8" s="187"/>
+      <c r="T8" s="187"/>
+      <c r="U8" s="187"/>
+      <c r="V8" s="187"/>
+      <c r="W8" s="187"/>
+      <c r="X8" s="187"/>
+      <c r="Y8" s="187"/>
+      <c r="Z8" s="187"/>
+      <c r="AA8" s="187"/>
+      <c r="AB8" s="187"/>
+      <c r="AC8" s="187"/>
+      <c r="AD8" s="187"/>
+      <c r="AE8" s="188"/>
+      <c r="AF8" s="183"/>
+      <c r="AG8" s="184"/>
+      <c r="AH8" s="184"/>
+      <c r="AI8" s="185"/>
     </row>
     <row r="9" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="22"/>
-      <c r="B9" s="199"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="203"/>
-      <c r="G9" s="201"/>
-      <c r="H9" s="204"/>
-      <c r="I9" s="200"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="206"/>
-      <c r="L9" s="206"/>
-      <c r="M9" s="206"/>
-      <c r="N9" s="206"/>
-      <c r="O9" s="206"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="209"/>
-      <c r="S9" s="209"/>
-      <c r="T9" s="209"/>
-      <c r="U9" s="209"/>
-      <c r="V9" s="209"/>
-      <c r="W9" s="209"/>
-      <c r="X9" s="209"/>
-      <c r="Y9" s="209"/>
-      <c r="Z9" s="209"/>
-      <c r="AA9" s="209"/>
-      <c r="AB9" s="209"/>
-      <c r="AC9" s="209"/>
-      <c r="AD9" s="209"/>
-      <c r="AE9" s="210"/>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="206"/>
-      <c r="AH9" s="206"/>
-      <c r="AI9" s="207"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="168"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="170"/>
+      <c r="L9" s="170"/>
+      <c r="M9" s="170"/>
+      <c r="N9" s="170"/>
+      <c r="O9" s="170"/>
+      <c r="P9" s="171"/>
+      <c r="Q9" s="172"/>
+      <c r="R9" s="173"/>
+      <c r="S9" s="173"/>
+      <c r="T9" s="173"/>
+      <c r="U9" s="173"/>
+      <c r="V9" s="173"/>
+      <c r="W9" s="173"/>
+      <c r="X9" s="173"/>
+      <c r="Y9" s="173"/>
+      <c r="Z9" s="173"/>
+      <c r="AA9" s="173"/>
+      <c r="AB9" s="173"/>
+      <c r="AC9" s="173"/>
+      <c r="AD9" s="173"/>
+      <c r="AE9" s="174"/>
+      <c r="AF9" s="169"/>
+      <c r="AG9" s="170"/>
+      <c r="AH9" s="170"/>
+      <c r="AI9" s="171"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="22"/>
-      <c r="B10" s="199"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="202"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="199"/>
-      <c r="H10" s="204"/>
-      <c r="I10" s="200"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="206"/>
-      <c r="L10" s="206"/>
-      <c r="M10" s="206"/>
-      <c r="N10" s="206"/>
-      <c r="O10" s="206"/>
-      <c r="P10" s="207"/>
-      <c r="Q10" s="208"/>
-      <c r="R10" s="209"/>
-      <c r="S10" s="209"/>
-      <c r="T10" s="209"/>
-      <c r="U10" s="209"/>
-      <c r="V10" s="209"/>
-      <c r="W10" s="209"/>
-      <c r="X10" s="209"/>
-      <c r="Y10" s="209"/>
-      <c r="Z10" s="209"/>
-      <c r="AA10" s="209"/>
-      <c r="AB10" s="209"/>
-      <c r="AC10" s="209"/>
-      <c r="AD10" s="209"/>
-      <c r="AE10" s="210"/>
-      <c r="AF10" s="205"/>
-      <c r="AG10" s="206"/>
-      <c r="AH10" s="206"/>
-      <c r="AI10" s="207"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="164"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="163"/>
+      <c r="H10" s="168"/>
+      <c r="I10" s="164"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="170"/>
+      <c r="L10" s="170"/>
+      <c r="M10" s="170"/>
+      <c r="N10" s="170"/>
+      <c r="O10" s="170"/>
+      <c r="P10" s="171"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="173"/>
+      <c r="S10" s="173"/>
+      <c r="T10" s="173"/>
+      <c r="U10" s="173"/>
+      <c r="V10" s="173"/>
+      <c r="W10" s="173"/>
+      <c r="X10" s="173"/>
+      <c r="Y10" s="173"/>
+      <c r="Z10" s="173"/>
+      <c r="AA10" s="173"/>
+      <c r="AB10" s="173"/>
+      <c r="AC10" s="173"/>
+      <c r="AD10" s="173"/>
+      <c r="AE10" s="174"/>
+      <c r="AF10" s="169"/>
+      <c r="AG10" s="170"/>
+      <c r="AH10" s="170"/>
+      <c r="AI10" s="171"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="22"/>
-      <c r="B11" s="199"/>
-      <c r="C11" s="200"/>
-      <c r="D11" s="201"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="204"/>
-      <c r="I11" s="200"/>
-      <c r="J11" s="205"/>
-      <c r="K11" s="206"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="206"/>
-      <c r="N11" s="206"/>
-      <c r="O11" s="206"/>
-      <c r="P11" s="207"/>
-      <c r="Q11" s="208"/>
-      <c r="R11" s="209"/>
-      <c r="S11" s="209"/>
-      <c r="T11" s="209"/>
-      <c r="U11" s="209"/>
-      <c r="V11" s="209"/>
-      <c r="W11" s="209"/>
-      <c r="X11" s="209"/>
-      <c r="Y11" s="209"/>
-      <c r="Z11" s="209"/>
-      <c r="AA11" s="209"/>
-      <c r="AB11" s="209"/>
-      <c r="AC11" s="209"/>
-      <c r="AD11" s="209"/>
-      <c r="AE11" s="210"/>
-      <c r="AF11" s="205"/>
-      <c r="AG11" s="206"/>
-      <c r="AH11" s="206"/>
-      <c r="AI11" s="207"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="163"/>
+      <c r="H11" s="168"/>
+      <c r="I11" s="164"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="170"/>
+      <c r="L11" s="170"/>
+      <c r="M11" s="170"/>
+      <c r="N11" s="170"/>
+      <c r="O11" s="170"/>
+      <c r="P11" s="171"/>
+      <c r="Q11" s="172"/>
+      <c r="R11" s="173"/>
+      <c r="S11" s="173"/>
+      <c r="T11" s="173"/>
+      <c r="U11" s="173"/>
+      <c r="V11" s="173"/>
+      <c r="W11" s="173"/>
+      <c r="X11" s="173"/>
+      <c r="Y11" s="173"/>
+      <c r="Z11" s="173"/>
+      <c r="AA11" s="173"/>
+      <c r="AB11" s="173"/>
+      <c r="AC11" s="173"/>
+      <c r="AD11" s="173"/>
+      <c r="AE11" s="174"/>
+      <c r="AF11" s="169"/>
+      <c r="AG11" s="170"/>
+      <c r="AH11" s="170"/>
+      <c r="AI11" s="171"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="22"/>
-      <c r="B12" s="199"/>
-      <c r="C12" s="200"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="199"/>
-      <c r="H12" s="204"/>
-      <c r="I12" s="200"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="206"/>
-      <c r="L12" s="206"/>
-      <c r="M12" s="206"/>
-      <c r="N12" s="206"/>
-      <c r="O12" s="206"/>
-      <c r="P12" s="207"/>
-      <c r="Q12" s="208"/>
-      <c r="R12" s="209"/>
-      <c r="S12" s="209"/>
-      <c r="T12" s="209"/>
-      <c r="U12" s="209"/>
-      <c r="V12" s="209"/>
-      <c r="W12" s="209"/>
-      <c r="X12" s="209"/>
-      <c r="Y12" s="209"/>
-      <c r="Z12" s="209"/>
-      <c r="AA12" s="209"/>
-      <c r="AB12" s="209"/>
-      <c r="AC12" s="209"/>
-      <c r="AD12" s="209"/>
-      <c r="AE12" s="210"/>
-      <c r="AF12" s="205"/>
-      <c r="AG12" s="206"/>
-      <c r="AH12" s="206"/>
-      <c r="AI12" s="207"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="163"/>
+      <c r="H12" s="168"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="170"/>
+      <c r="L12" s="170"/>
+      <c r="M12" s="170"/>
+      <c r="N12" s="170"/>
+      <c r="O12" s="170"/>
+      <c r="P12" s="171"/>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="173"/>
+      <c r="S12" s="173"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173"/>
+      <c r="V12" s="173"/>
+      <c r="W12" s="173"/>
+      <c r="X12" s="173"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="173"/>
+      <c r="AB12" s="173"/>
+      <c r="AC12" s="173"/>
+      <c r="AD12" s="173"/>
+      <c r="AE12" s="174"/>
+      <c r="AF12" s="169"/>
+      <c r="AG12" s="170"/>
+      <c r="AH12" s="170"/>
+      <c r="AI12" s="171"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="22"/>
-      <c r="B13" s="199"/>
-      <c r="C13" s="200"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="202"/>
-      <c r="F13" s="203"/>
-      <c r="G13" s="199"/>
-      <c r="H13" s="204"/>
-      <c r="I13" s="200"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="206"/>
-      <c r="L13" s="206"/>
-      <c r="M13" s="206"/>
-      <c r="N13" s="206"/>
-      <c r="O13" s="206"/>
-      <c r="P13" s="207"/>
-      <c r="Q13" s="208"/>
-      <c r="R13" s="209"/>
-      <c r="S13" s="209"/>
-      <c r="T13" s="209"/>
-      <c r="U13" s="209"/>
-      <c r="V13" s="209"/>
-      <c r="W13" s="209"/>
-      <c r="X13" s="209"/>
-      <c r="Y13" s="209"/>
-      <c r="Z13" s="209"/>
-      <c r="AA13" s="209"/>
-      <c r="AB13" s="209"/>
-      <c r="AC13" s="209"/>
-      <c r="AD13" s="209"/>
-      <c r="AE13" s="210"/>
-      <c r="AF13" s="205"/>
-      <c r="AG13" s="206"/>
-      <c r="AH13" s="206"/>
-      <c r="AI13" s="207"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="168"/>
+      <c r="I13" s="164"/>
+      <c r="J13" s="169"/>
+      <c r="K13" s="170"/>
+      <c r="L13" s="170"/>
+      <c r="M13" s="170"/>
+      <c r="N13" s="170"/>
+      <c r="O13" s="170"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="172"/>
+      <c r="R13" s="173"/>
+      <c r="S13" s="173"/>
+      <c r="T13" s="173"/>
+      <c r="U13" s="173"/>
+      <c r="V13" s="173"/>
+      <c r="W13" s="173"/>
+      <c r="X13" s="173"/>
+      <c r="Y13" s="173"/>
+      <c r="Z13" s="173"/>
+      <c r="AA13" s="173"/>
+      <c r="AB13" s="173"/>
+      <c r="AC13" s="173"/>
+      <c r="AD13" s="173"/>
+      <c r="AE13" s="174"/>
+      <c r="AF13" s="169"/>
+      <c r="AG13" s="170"/>
+      <c r="AH13" s="170"/>
+      <c r="AI13" s="171"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="22"/>
-      <c r="B14" s="199"/>
-      <c r="C14" s="200"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="199"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="200"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="206"/>
-      <c r="L14" s="206"/>
-      <c r="M14" s="206"/>
-      <c r="N14" s="206"/>
-      <c r="O14" s="206"/>
-      <c r="P14" s="207"/>
-      <c r="Q14" s="208"/>
-      <c r="R14" s="209"/>
-      <c r="S14" s="209"/>
-      <c r="T14" s="209"/>
-      <c r="U14" s="209"/>
-      <c r="V14" s="209"/>
-      <c r="W14" s="209"/>
-      <c r="X14" s="209"/>
-      <c r="Y14" s="209"/>
-      <c r="Z14" s="209"/>
-      <c r="AA14" s="209"/>
-      <c r="AB14" s="209"/>
-      <c r="AC14" s="209"/>
-      <c r="AD14" s="209"/>
-      <c r="AE14" s="210"/>
-      <c r="AF14" s="205"/>
-      <c r="AG14" s="206"/>
-      <c r="AH14" s="206"/>
-      <c r="AI14" s="207"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="163"/>
+      <c r="H14" s="168"/>
+      <c r="I14" s="164"/>
+      <c r="J14" s="169"/>
+      <c r="K14" s="170"/>
+      <c r="L14" s="170"/>
+      <c r="M14" s="170"/>
+      <c r="N14" s="170"/>
+      <c r="O14" s="170"/>
+      <c r="P14" s="171"/>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="173"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="173"/>
+      <c r="AC14" s="173"/>
+      <c r="AD14" s="173"/>
+      <c r="AE14" s="174"/>
+      <c r="AF14" s="169"/>
+      <c r="AG14" s="170"/>
+      <c r="AH14" s="170"/>
+      <c r="AI14" s="171"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="22"/>
-      <c r="B15" s="199"/>
-      <c r="C15" s="200"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="203"/>
-      <c r="G15" s="199"/>
-      <c r="H15" s="204"/>
-      <c r="I15" s="200"/>
-      <c r="J15" s="205"/>
-      <c r="K15" s="206"/>
-      <c r="L15" s="206"/>
-      <c r="M15" s="206"/>
-      <c r="N15" s="206"/>
-      <c r="O15" s="206"/>
-      <c r="P15" s="207"/>
-      <c r="Q15" s="208"/>
-      <c r="R15" s="209"/>
-      <c r="S15" s="209"/>
-      <c r="T15" s="209"/>
-      <c r="U15" s="209"/>
-      <c r="V15" s="209"/>
-      <c r="W15" s="209"/>
-      <c r="X15" s="209"/>
-      <c r="Y15" s="209"/>
-      <c r="Z15" s="209"/>
-      <c r="AA15" s="209"/>
-      <c r="AB15" s="209"/>
-      <c r="AC15" s="209"/>
-      <c r="AD15" s="209"/>
-      <c r="AE15" s="210"/>
-      <c r="AF15" s="205"/>
-      <c r="AG15" s="206"/>
-      <c r="AH15" s="206"/>
-      <c r="AI15" s="207"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="163"/>
+      <c r="H15" s="168"/>
+      <c r="I15" s="164"/>
+      <c r="J15" s="169"/>
+      <c r="K15" s="170"/>
+      <c r="L15" s="170"/>
+      <c r="M15" s="170"/>
+      <c r="N15" s="170"/>
+      <c r="O15" s="170"/>
+      <c r="P15" s="171"/>
+      <c r="Q15" s="172"/>
+      <c r="R15" s="173"/>
+      <c r="S15" s="173"/>
+      <c r="T15" s="173"/>
+      <c r="U15" s="173"/>
+      <c r="V15" s="173"/>
+      <c r="W15" s="173"/>
+      <c r="X15" s="173"/>
+      <c r="Y15" s="173"/>
+      <c r="Z15" s="173"/>
+      <c r="AA15" s="173"/>
+      <c r="AB15" s="173"/>
+      <c r="AC15" s="173"/>
+      <c r="AD15" s="173"/>
+      <c r="AE15" s="174"/>
+      <c r="AF15" s="169"/>
+      <c r="AG15" s="170"/>
+      <c r="AH15" s="170"/>
+      <c r="AI15" s="171"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="22"/>
-      <c r="B16" s="199"/>
-      <c r="C16" s="200"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="202"/>
-      <c r="F16" s="203"/>
-      <c r="G16" s="199"/>
-      <c r="H16" s="204"/>
-      <c r="I16" s="200"/>
-      <c r="J16" s="205"/>
-      <c r="K16" s="206"/>
-      <c r="L16" s="206"/>
-      <c r="M16" s="206"/>
-      <c r="N16" s="206"/>
-      <c r="O16" s="206"/>
-      <c r="P16" s="207"/>
-      <c r="Q16" s="208"/>
-      <c r="R16" s="209"/>
-      <c r="S16" s="209"/>
-      <c r="T16" s="209"/>
-      <c r="U16" s="209"/>
-      <c r="V16" s="209"/>
-      <c r="W16" s="209"/>
-      <c r="X16" s="209"/>
-      <c r="Y16" s="209"/>
-      <c r="Z16" s="209"/>
-      <c r="AA16" s="209"/>
-      <c r="AB16" s="209"/>
-      <c r="AC16" s="209"/>
-      <c r="AD16" s="209"/>
-      <c r="AE16" s="210"/>
-      <c r="AF16" s="205"/>
-      <c r="AG16" s="206"/>
-      <c r="AH16" s="206"/>
-      <c r="AI16" s="207"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="168"/>
+      <c r="I16" s="164"/>
+      <c r="J16" s="169"/>
+      <c r="K16" s="170"/>
+      <c r="L16" s="170"/>
+      <c r="M16" s="170"/>
+      <c r="N16" s="170"/>
+      <c r="O16" s="170"/>
+      <c r="P16" s="171"/>
+      <c r="Q16" s="172"/>
+      <c r="R16" s="173"/>
+      <c r="S16" s="173"/>
+      <c r="T16" s="173"/>
+      <c r="U16" s="173"/>
+      <c r="V16" s="173"/>
+      <c r="W16" s="173"/>
+      <c r="X16" s="173"/>
+      <c r="Y16" s="173"/>
+      <c r="Z16" s="173"/>
+      <c r="AA16" s="173"/>
+      <c r="AB16" s="173"/>
+      <c r="AC16" s="173"/>
+      <c r="AD16" s="173"/>
+      <c r="AE16" s="174"/>
+      <c r="AF16" s="169"/>
+      <c r="AG16" s="170"/>
+      <c r="AH16" s="170"/>
+      <c r="AI16" s="171"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="22"/>
-      <c r="B17" s="199"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="202"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="204"/>
-      <c r="I17" s="200"/>
-      <c r="J17" s="205"/>
-      <c r="K17" s="206"/>
-      <c r="L17" s="206"/>
-      <c r="M17" s="206"/>
-      <c r="N17" s="206"/>
-      <c r="O17" s="206"/>
-      <c r="P17" s="207"/>
-      <c r="Q17" s="208"/>
-      <c r="R17" s="209"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="209"/>
-      <c r="U17" s="209"/>
-      <c r="V17" s="209"/>
-      <c r="W17" s="209"/>
-      <c r="X17" s="209"/>
-      <c r="Y17" s="209"/>
-      <c r="Z17" s="209"/>
-      <c r="AA17" s="209"/>
-      <c r="AB17" s="209"/>
-      <c r="AC17" s="209"/>
-      <c r="AD17" s="209"/>
-      <c r="AE17" s="210"/>
-      <c r="AF17" s="205"/>
-      <c r="AG17" s="206"/>
-      <c r="AH17" s="206"/>
-      <c r="AI17" s="207"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="163"/>
+      <c r="H17" s="168"/>
+      <c r="I17" s="164"/>
+      <c r="J17" s="169"/>
+      <c r="K17" s="170"/>
+      <c r="L17" s="170"/>
+      <c r="M17" s="170"/>
+      <c r="N17" s="170"/>
+      <c r="O17" s="170"/>
+      <c r="P17" s="171"/>
+      <c r="Q17" s="172"/>
+      <c r="R17" s="173"/>
+      <c r="S17" s="173"/>
+      <c r="T17" s="173"/>
+      <c r="U17" s="173"/>
+      <c r="V17" s="173"/>
+      <c r="W17" s="173"/>
+      <c r="X17" s="173"/>
+      <c r="Y17" s="173"/>
+      <c r="Z17" s="173"/>
+      <c r="AA17" s="173"/>
+      <c r="AB17" s="173"/>
+      <c r="AC17" s="173"/>
+      <c r="AD17" s="173"/>
+      <c r="AE17" s="174"/>
+      <c r="AF17" s="169"/>
+      <c r="AG17" s="170"/>
+      <c r="AH17" s="170"/>
+      <c r="AI17" s="171"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="B18" s="199"/>
-      <c r="C18" s="200"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="202"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="199"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="200"/>
-      <c r="J18" s="205"/>
-      <c r="K18" s="206"/>
-      <c r="L18" s="206"/>
-      <c r="M18" s="206"/>
-      <c r="N18" s="206"/>
-      <c r="O18" s="206"/>
-      <c r="P18" s="207"/>
-      <c r="Q18" s="208"/>
-      <c r="R18" s="209"/>
-      <c r="S18" s="209"/>
-      <c r="T18" s="209"/>
-      <c r="U18" s="209"/>
-      <c r="V18" s="209"/>
-      <c r="W18" s="209"/>
-      <c r="X18" s="209"/>
-      <c r="Y18" s="209"/>
-      <c r="Z18" s="209"/>
-      <c r="AA18" s="209"/>
-      <c r="AB18" s="209"/>
-      <c r="AC18" s="209"/>
-      <c r="AD18" s="209"/>
-      <c r="AE18" s="210"/>
-      <c r="AF18" s="205"/>
-      <c r="AG18" s="206"/>
-      <c r="AH18" s="206"/>
-      <c r="AI18" s="207"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="163"/>
+      <c r="H18" s="168"/>
+      <c r="I18" s="164"/>
+      <c r="J18" s="169"/>
+      <c r="K18" s="170"/>
+      <c r="L18" s="170"/>
+      <c r="M18" s="170"/>
+      <c r="N18" s="170"/>
+      <c r="O18" s="170"/>
+      <c r="P18" s="171"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="173"/>
+      <c r="S18" s="173"/>
+      <c r="T18" s="173"/>
+      <c r="U18" s="173"/>
+      <c r="V18" s="173"/>
+      <c r="W18" s="173"/>
+      <c r="X18" s="173"/>
+      <c r="Y18" s="173"/>
+      <c r="Z18" s="173"/>
+      <c r="AA18" s="173"/>
+      <c r="AB18" s="173"/>
+      <c r="AC18" s="173"/>
+      <c r="AD18" s="173"/>
+      <c r="AE18" s="174"/>
+      <c r="AF18" s="169"/>
+      <c r="AG18" s="170"/>
+      <c r="AH18" s="170"/>
+      <c r="AI18" s="171"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="22"/>
-      <c r="B19" s="199"/>
-      <c r="C19" s="200"/>
-      <c r="D19" s="201"/>
-      <c r="E19" s="202"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="199"/>
-      <c r="H19" s="204"/>
-      <c r="I19" s="200"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="206"/>
-      <c r="L19" s="206"/>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="207"/>
-      <c r="Q19" s="208"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
-      <c r="W19" s="209"/>
-      <c r="X19" s="209"/>
-      <c r="Y19" s="209"/>
-      <c r="Z19" s="209"/>
-      <c r="AA19" s="209"/>
-      <c r="AB19" s="209"/>
-      <c r="AC19" s="209"/>
-      <c r="AD19" s="209"/>
-      <c r="AE19" s="210"/>
-      <c r="AF19" s="205"/>
-      <c r="AG19" s="206"/>
-      <c r="AH19" s="206"/>
-      <c r="AI19" s="207"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="163"/>
+      <c r="H19" s="168"/>
+      <c r="I19" s="164"/>
+      <c r="J19" s="169"/>
+      <c r="K19" s="170"/>
+      <c r="L19" s="170"/>
+      <c r="M19" s="170"/>
+      <c r="N19" s="170"/>
+      <c r="O19" s="170"/>
+      <c r="P19" s="171"/>
+      <c r="Q19" s="172"/>
+      <c r="R19" s="173"/>
+      <c r="S19" s="173"/>
+      <c r="T19" s="173"/>
+      <c r="U19" s="173"/>
+      <c r="V19" s="173"/>
+      <c r="W19" s="173"/>
+      <c r="X19" s="173"/>
+      <c r="Y19" s="173"/>
+      <c r="Z19" s="173"/>
+      <c r="AA19" s="173"/>
+      <c r="AB19" s="173"/>
+      <c r="AC19" s="173"/>
+      <c r="AD19" s="173"/>
+      <c r="AE19" s="174"/>
+      <c r="AF19" s="169"/>
+      <c r="AG19" s="170"/>
+      <c r="AH19" s="170"/>
+      <c r="AI19" s="171"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="22"/>
-      <c r="B20" s="199"/>
-      <c r="C20" s="200"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="202"/>
-      <c r="F20" s="203"/>
-      <c r="G20" s="199"/>
-      <c r="H20" s="204"/>
-      <c r="I20" s="200"/>
-      <c r="J20" s="205"/>
-      <c r="K20" s="206"/>
-      <c r="L20" s="206"/>
-      <c r="M20" s="206"/>
-      <c r="N20" s="206"/>
-      <c r="O20" s="206"/>
-      <c r="P20" s="207"/>
-      <c r="Q20" s="208"/>
-      <c r="R20" s="209"/>
-      <c r="S20" s="209"/>
-      <c r="T20" s="209"/>
-      <c r="U20" s="209"/>
-      <c r="V20" s="209"/>
-      <c r="W20" s="209"/>
-      <c r="X20" s="209"/>
-      <c r="Y20" s="209"/>
-      <c r="Z20" s="209"/>
-      <c r="AA20" s="209"/>
-      <c r="AB20" s="209"/>
-      <c r="AC20" s="209"/>
-      <c r="AD20" s="209"/>
-      <c r="AE20" s="210"/>
-      <c r="AF20" s="205"/>
-      <c r="AG20" s="206"/>
-      <c r="AH20" s="206"/>
-      <c r="AI20" s="207"/>
+      <c r="B20" s="163"/>
+      <c r="C20" s="164"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="163"/>
+      <c r="H20" s="168"/>
+      <c r="I20" s="164"/>
+      <c r="J20" s="169"/>
+      <c r="K20" s="170"/>
+      <c r="L20" s="170"/>
+      <c r="M20" s="170"/>
+      <c r="N20" s="170"/>
+      <c r="O20" s="170"/>
+      <c r="P20" s="171"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="173"/>
+      <c r="S20" s="173"/>
+      <c r="T20" s="173"/>
+      <c r="U20" s="173"/>
+      <c r="V20" s="173"/>
+      <c r="W20" s="173"/>
+      <c r="X20" s="173"/>
+      <c r="Y20" s="173"/>
+      <c r="Z20" s="173"/>
+      <c r="AA20" s="173"/>
+      <c r="AB20" s="173"/>
+      <c r="AC20" s="173"/>
+      <c r="AD20" s="173"/>
+      <c r="AE20" s="174"/>
+      <c r="AF20" s="169"/>
+      <c r="AG20" s="170"/>
+      <c r="AH20" s="170"/>
+      <c r="AI20" s="171"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="22"/>
-      <c r="B21" s="199"/>
-      <c r="C21" s="200"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="203"/>
-      <c r="G21" s="199"/>
-      <c r="H21" s="204"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="206"/>
-      <c r="L21" s="206"/>
-      <c r="M21" s="206"/>
-      <c r="N21" s="206"/>
-      <c r="O21" s="206"/>
-      <c r="P21" s="207"/>
-      <c r="Q21" s="208"/>
-      <c r="R21" s="209"/>
-      <c r="S21" s="209"/>
-      <c r="T21" s="209"/>
-      <c r="U21" s="209"/>
-      <c r="V21" s="209"/>
-      <c r="W21" s="209"/>
-      <c r="X21" s="209"/>
-      <c r="Y21" s="209"/>
-      <c r="Z21" s="209"/>
-      <c r="AA21" s="209"/>
-      <c r="AB21" s="209"/>
-      <c r="AC21" s="209"/>
-      <c r="AD21" s="209"/>
-      <c r="AE21" s="210"/>
-      <c r="AF21" s="205"/>
-      <c r="AG21" s="206"/>
-      <c r="AH21" s="206"/>
-      <c r="AI21" s="207"/>
+      <c r="B21" s="163"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="168"/>
+      <c r="I21" s="164"/>
+      <c r="J21" s="169"/>
+      <c r="K21" s="170"/>
+      <c r="L21" s="170"/>
+      <c r="M21" s="170"/>
+      <c r="N21" s="170"/>
+      <c r="O21" s="170"/>
+      <c r="P21" s="171"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="173"/>
+      <c r="S21" s="173"/>
+      <c r="T21" s="173"/>
+      <c r="U21" s="173"/>
+      <c r="V21" s="173"/>
+      <c r="W21" s="173"/>
+      <c r="X21" s="173"/>
+      <c r="Y21" s="173"/>
+      <c r="Z21" s="173"/>
+      <c r="AA21" s="173"/>
+      <c r="AB21" s="173"/>
+      <c r="AC21" s="173"/>
+      <c r="AD21" s="173"/>
+      <c r="AE21" s="174"/>
+      <c r="AF21" s="169"/>
+      <c r="AG21" s="170"/>
+      <c r="AH21" s="170"/>
+      <c r="AI21" s="171"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="22"/>
-      <c r="B22" s="199"/>
-      <c r="C22" s="200"/>
-      <c r="D22" s="201"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="199"/>
-      <c r="H22" s="204"/>
-      <c r="I22" s="200"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="206"/>
-      <c r="L22" s="206"/>
-      <c r="M22" s="206"/>
-      <c r="N22" s="206"/>
-      <c r="O22" s="206"/>
-      <c r="P22" s="207"/>
-      <c r="Q22" s="208"/>
-      <c r="R22" s="209"/>
-      <c r="S22" s="209"/>
-      <c r="T22" s="209"/>
-      <c r="U22" s="209"/>
-      <c r="V22" s="209"/>
-      <c r="W22" s="209"/>
-      <c r="X22" s="209"/>
-      <c r="Y22" s="209"/>
-      <c r="Z22" s="209"/>
-      <c r="AA22" s="209"/>
-      <c r="AB22" s="209"/>
-      <c r="AC22" s="209"/>
-      <c r="AD22" s="209"/>
-      <c r="AE22" s="210"/>
-      <c r="AF22" s="205"/>
-      <c r="AG22" s="206"/>
-      <c r="AH22" s="206"/>
-      <c r="AI22" s="207"/>
+      <c r="B22" s="163"/>
+      <c r="C22" s="164"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="167"/>
+      <c r="G22" s="163"/>
+      <c r="H22" s="168"/>
+      <c r="I22" s="164"/>
+      <c r="J22" s="169"/>
+      <c r="K22" s="170"/>
+      <c r="L22" s="170"/>
+      <c r="M22" s="170"/>
+      <c r="N22" s="170"/>
+      <c r="O22" s="170"/>
+      <c r="P22" s="171"/>
+      <c r="Q22" s="172"/>
+      <c r="R22" s="173"/>
+      <c r="S22" s="173"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
+      <c r="V22" s="173"/>
+      <c r="W22" s="173"/>
+      <c r="X22" s="173"/>
+      <c r="Y22" s="173"/>
+      <c r="Z22" s="173"/>
+      <c r="AA22" s="173"/>
+      <c r="AB22" s="173"/>
+      <c r="AC22" s="173"/>
+      <c r="AD22" s="173"/>
+      <c r="AE22" s="174"/>
+      <c r="AF22" s="169"/>
+      <c r="AG22" s="170"/>
+      <c r="AH22" s="170"/>
+      <c r="AI22" s="171"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="22"/>
-      <c r="B23" s="199"/>
-      <c r="C23" s="200"/>
-      <c r="D23" s="201"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="203"/>
-      <c r="G23" s="199"/>
-      <c r="H23" s="204"/>
-      <c r="I23" s="200"/>
-      <c r="J23" s="205"/>
-      <c r="K23" s="206"/>
-      <c r="L23" s="206"/>
-      <c r="M23" s="206"/>
-      <c r="N23" s="206"/>
-      <c r="O23" s="206"/>
-      <c r="P23" s="207"/>
-      <c r="Q23" s="208"/>
-      <c r="R23" s="209"/>
-      <c r="S23" s="209"/>
-      <c r="T23" s="209"/>
-      <c r="U23" s="209"/>
-      <c r="V23" s="209"/>
-      <c r="W23" s="209"/>
-      <c r="X23" s="209"/>
-      <c r="Y23" s="209"/>
-      <c r="Z23" s="209"/>
-      <c r="AA23" s="209"/>
-      <c r="AB23" s="209"/>
-      <c r="AC23" s="209"/>
-      <c r="AD23" s="209"/>
-      <c r="AE23" s="210"/>
-      <c r="AF23" s="205"/>
-      <c r="AG23" s="206"/>
-      <c r="AH23" s="206"/>
-      <c r="AI23" s="207"/>
+      <c r="B23" s="163"/>
+      <c r="C23" s="164"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="163"/>
+      <c r="H23" s="168"/>
+      <c r="I23" s="164"/>
+      <c r="J23" s="169"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="170"/>
+      <c r="M23" s="170"/>
+      <c r="N23" s="170"/>
+      <c r="O23" s="170"/>
+      <c r="P23" s="171"/>
+      <c r="Q23" s="172"/>
+      <c r="R23" s="173"/>
+      <c r="S23" s="173"/>
+      <c r="T23" s="173"/>
+      <c r="U23" s="173"/>
+      <c r="V23" s="173"/>
+      <c r="W23" s="173"/>
+      <c r="X23" s="173"/>
+      <c r="Y23" s="173"/>
+      <c r="Z23" s="173"/>
+      <c r="AA23" s="173"/>
+      <c r="AB23" s="173"/>
+      <c r="AC23" s="173"/>
+      <c r="AD23" s="173"/>
+      <c r="AE23" s="174"/>
+      <c r="AF23" s="169"/>
+      <c r="AG23" s="170"/>
+      <c r="AH23" s="170"/>
+      <c r="AI23" s="171"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="22"/>
-      <c r="B24" s="199"/>
-      <c r="C24" s="200"/>
-      <c r="D24" s="201"/>
-      <c r="E24" s="202"/>
-      <c r="F24" s="203"/>
-      <c r="G24" s="199"/>
-      <c r="H24" s="204"/>
-      <c r="I24" s="200"/>
-      <c r="J24" s="205"/>
-      <c r="K24" s="206"/>
-      <c r="L24" s="206"/>
-      <c r="M24" s="206"/>
-      <c r="N24" s="206"/>
-      <c r="O24" s="206"/>
-      <c r="P24" s="207"/>
-      <c r="Q24" s="208"/>
-      <c r="R24" s="209"/>
-      <c r="S24" s="209"/>
-      <c r="T24" s="209"/>
-      <c r="U24" s="209"/>
-      <c r="V24" s="209"/>
-      <c r="W24" s="209"/>
-      <c r="X24" s="209"/>
-      <c r="Y24" s="209"/>
-      <c r="Z24" s="209"/>
-      <c r="AA24" s="209"/>
-      <c r="AB24" s="209"/>
-      <c r="AC24" s="209"/>
-      <c r="AD24" s="209"/>
-      <c r="AE24" s="210"/>
-      <c r="AF24" s="205"/>
-      <c r="AG24" s="206"/>
-      <c r="AH24" s="206"/>
-      <c r="AI24" s="207"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="165"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="163"/>
+      <c r="H24" s="168"/>
+      <c r="I24" s="164"/>
+      <c r="J24" s="169"/>
+      <c r="K24" s="170"/>
+      <c r="L24" s="170"/>
+      <c r="M24" s="170"/>
+      <c r="N24" s="170"/>
+      <c r="O24" s="170"/>
+      <c r="P24" s="171"/>
+      <c r="Q24" s="172"/>
+      <c r="R24" s="173"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="173"/>
+      <c r="AB24" s="173"/>
+      <c r="AC24" s="173"/>
+      <c r="AD24" s="173"/>
+      <c r="AE24" s="174"/>
+      <c r="AF24" s="169"/>
+      <c r="AG24" s="170"/>
+      <c r="AH24" s="170"/>
+      <c r="AI24" s="171"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="22"/>
-      <c r="B25" s="199"/>
-      <c r="C25" s="200"/>
-      <c r="D25" s="201"/>
-      <c r="E25" s="202"/>
-      <c r="F25" s="203"/>
-      <c r="G25" s="199"/>
-      <c r="H25" s="204"/>
-      <c r="I25" s="200"/>
-      <c r="J25" s="205"/>
-      <c r="K25" s="206"/>
-      <c r="L25" s="206"/>
-      <c r="M25" s="206"/>
-      <c r="N25" s="206"/>
-      <c r="O25" s="206"/>
-      <c r="P25" s="207"/>
-      <c r="Q25" s="208"/>
-      <c r="R25" s="209"/>
-      <c r="S25" s="209"/>
-      <c r="T25" s="209"/>
-      <c r="U25" s="209"/>
-      <c r="V25" s="209"/>
-      <c r="W25" s="209"/>
-      <c r="X25" s="209"/>
-      <c r="Y25" s="209"/>
-      <c r="Z25" s="209"/>
-      <c r="AA25" s="209"/>
-      <c r="AB25" s="209"/>
-      <c r="AC25" s="209"/>
-      <c r="AD25" s="209"/>
-      <c r="AE25" s="210"/>
-      <c r="AF25" s="205"/>
-      <c r="AG25" s="206"/>
-      <c r="AH25" s="206"/>
-      <c r="AI25" s="207"/>
+      <c r="B25" s="163"/>
+      <c r="C25" s="164"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="167"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="168"/>
+      <c r="I25" s="164"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="170"/>
+      <c r="L25" s="170"/>
+      <c r="M25" s="170"/>
+      <c r="N25" s="170"/>
+      <c r="O25" s="170"/>
+      <c r="P25" s="171"/>
+      <c r="Q25" s="172"/>
+      <c r="R25" s="173"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="173"/>
+      <c r="U25" s="173"/>
+      <c r="V25" s="173"/>
+      <c r="W25" s="173"/>
+      <c r="X25" s="173"/>
+      <c r="Y25" s="173"/>
+      <c r="Z25" s="173"/>
+      <c r="AA25" s="173"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="173"/>
+      <c r="AD25" s="173"/>
+      <c r="AE25" s="174"/>
+      <c r="AF25" s="169"/>
+      <c r="AG25" s="170"/>
+      <c r="AH25" s="170"/>
+      <c r="AI25" s="171"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="22"/>
-      <c r="B26" s="199"/>
-      <c r="C26" s="200"/>
-      <c r="D26" s="201"/>
-      <c r="E26" s="202"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="199"/>
-      <c r="H26" s="204"/>
-      <c r="I26" s="200"/>
-      <c r="J26" s="205"/>
-      <c r="K26" s="206"/>
-      <c r="L26" s="206"/>
-      <c r="M26" s="206"/>
-      <c r="N26" s="206"/>
-      <c r="O26" s="206"/>
-      <c r="P26" s="207"/>
-      <c r="Q26" s="208"/>
-      <c r="R26" s="209"/>
-      <c r="S26" s="209"/>
-      <c r="T26" s="209"/>
-      <c r="U26" s="209"/>
-      <c r="V26" s="209"/>
-      <c r="W26" s="209"/>
-      <c r="X26" s="209"/>
-      <c r="Y26" s="209"/>
-      <c r="Z26" s="209"/>
-      <c r="AA26" s="209"/>
-      <c r="AB26" s="209"/>
-      <c r="AC26" s="209"/>
-      <c r="AD26" s="209"/>
-      <c r="AE26" s="210"/>
-      <c r="AF26" s="205"/>
-      <c r="AG26" s="206"/>
-      <c r="AH26" s="206"/>
-      <c r="AI26" s="207"/>
+      <c r="B26" s="163"/>
+      <c r="C26" s="164"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="168"/>
+      <c r="I26" s="164"/>
+      <c r="J26" s="169"/>
+      <c r="K26" s="170"/>
+      <c r="L26" s="170"/>
+      <c r="M26" s="170"/>
+      <c r="N26" s="170"/>
+      <c r="O26" s="170"/>
+      <c r="P26" s="171"/>
+      <c r="Q26" s="172"/>
+      <c r="R26" s="173"/>
+      <c r="S26" s="173"/>
+      <c r="T26" s="173"/>
+      <c r="U26" s="173"/>
+      <c r="V26" s="173"/>
+      <c r="W26" s="173"/>
+      <c r="X26" s="173"/>
+      <c r="Y26" s="173"/>
+      <c r="Z26" s="173"/>
+      <c r="AA26" s="173"/>
+      <c r="AB26" s="173"/>
+      <c r="AC26" s="173"/>
+      <c r="AD26" s="173"/>
+      <c r="AE26" s="174"/>
+      <c r="AF26" s="169"/>
+      <c r="AG26" s="170"/>
+      <c r="AH26" s="170"/>
+      <c r="AI26" s="171"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="22"/>
-      <c r="B27" s="199"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="201"/>
-      <c r="E27" s="202"/>
-      <c r="F27" s="203"/>
-      <c r="G27" s="199"/>
-      <c r="H27" s="204"/>
-      <c r="I27" s="200"/>
-      <c r="J27" s="205"/>
-      <c r="K27" s="206"/>
-      <c r="L27" s="206"/>
-      <c r="M27" s="206"/>
-      <c r="N27" s="206"/>
-      <c r="O27" s="206"/>
-      <c r="P27" s="207"/>
-      <c r="Q27" s="208"/>
-      <c r="R27" s="209"/>
-      <c r="S27" s="209"/>
-      <c r="T27" s="209"/>
-      <c r="U27" s="209"/>
-      <c r="V27" s="209"/>
-      <c r="W27" s="209"/>
-      <c r="X27" s="209"/>
-      <c r="Y27" s="209"/>
-      <c r="Z27" s="209"/>
-      <c r="AA27" s="209"/>
-      <c r="AB27" s="209"/>
-      <c r="AC27" s="209"/>
-      <c r="AD27" s="209"/>
-      <c r="AE27" s="210"/>
-      <c r="AF27" s="205"/>
-      <c r="AG27" s="206"/>
-      <c r="AH27" s="206"/>
-      <c r="AI27" s="207"/>
+      <c r="B27" s="163"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="167"/>
+      <c r="G27" s="163"/>
+      <c r="H27" s="168"/>
+      <c r="I27" s="164"/>
+      <c r="J27" s="169"/>
+      <c r="K27" s="170"/>
+      <c r="L27" s="170"/>
+      <c r="M27" s="170"/>
+      <c r="N27" s="170"/>
+      <c r="O27" s="170"/>
+      <c r="P27" s="171"/>
+      <c r="Q27" s="172"/>
+      <c r="R27" s="173"/>
+      <c r="S27" s="173"/>
+      <c r="T27" s="173"/>
+      <c r="U27" s="173"/>
+      <c r="V27" s="173"/>
+      <c r="W27" s="173"/>
+      <c r="X27" s="173"/>
+      <c r="Y27" s="173"/>
+      <c r="Z27" s="173"/>
+      <c r="AA27" s="173"/>
+      <c r="AB27" s="173"/>
+      <c r="AC27" s="173"/>
+      <c r="AD27" s="173"/>
+      <c r="AE27" s="174"/>
+      <c r="AF27" s="169"/>
+      <c r="AG27" s="170"/>
+      <c r="AH27" s="170"/>
+      <c r="AI27" s="171"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="22"/>
-      <c r="B28" s="199"/>
-      <c r="C28" s="200"/>
-      <c r="D28" s="201"/>
-      <c r="E28" s="202"/>
-      <c r="F28" s="203"/>
-      <c r="G28" s="199"/>
-      <c r="H28" s="204"/>
-      <c r="I28" s="200"/>
-      <c r="J28" s="205"/>
-      <c r="K28" s="206"/>
-      <c r="L28" s="206"/>
-      <c r="M28" s="206"/>
-      <c r="N28" s="206"/>
-      <c r="O28" s="206"/>
-      <c r="P28" s="207"/>
-      <c r="Q28" s="208"/>
-      <c r="R28" s="209"/>
-      <c r="S28" s="209"/>
-      <c r="T28" s="209"/>
-      <c r="U28" s="209"/>
-      <c r="V28" s="209"/>
-      <c r="W28" s="209"/>
-      <c r="X28" s="209"/>
-      <c r="Y28" s="209"/>
-      <c r="Z28" s="209"/>
-      <c r="AA28" s="209"/>
-      <c r="AB28" s="209"/>
-      <c r="AC28" s="209"/>
-      <c r="AD28" s="209"/>
-      <c r="AE28" s="210"/>
-      <c r="AF28" s="205"/>
-      <c r="AG28" s="206"/>
-      <c r="AH28" s="206"/>
-      <c r="AI28" s="207"/>
+      <c r="B28" s="163"/>
+      <c r="C28" s="164"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="163"/>
+      <c r="H28" s="168"/>
+      <c r="I28" s="164"/>
+      <c r="J28" s="169"/>
+      <c r="K28" s="170"/>
+      <c r="L28" s="170"/>
+      <c r="M28" s="170"/>
+      <c r="N28" s="170"/>
+      <c r="O28" s="170"/>
+      <c r="P28" s="171"/>
+      <c r="Q28" s="172"/>
+      <c r="R28" s="173"/>
+      <c r="S28" s="173"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
+      <c r="V28" s="173"/>
+      <c r="W28" s="173"/>
+      <c r="X28" s="173"/>
+      <c r="Y28" s="173"/>
+      <c r="Z28" s="173"/>
+      <c r="AA28" s="173"/>
+      <c r="AB28" s="173"/>
+      <c r="AC28" s="173"/>
+      <c r="AD28" s="173"/>
+      <c r="AE28" s="174"/>
+      <c r="AF28" s="169"/>
+      <c r="AG28" s="170"/>
+      <c r="AH28" s="170"/>
+      <c r="AI28" s="171"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="22"/>
-      <c r="B29" s="199"/>
-      <c r="C29" s="200"/>
-      <c r="D29" s="201"/>
-      <c r="E29" s="202"/>
-      <c r="F29" s="203"/>
-      <c r="G29" s="199"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="200"/>
-      <c r="J29" s="205"/>
-      <c r="K29" s="206"/>
-      <c r="L29" s="206"/>
-      <c r="M29" s="206"/>
-      <c r="N29" s="206"/>
-      <c r="O29" s="206"/>
-      <c r="P29" s="207"/>
-      <c r="Q29" s="208"/>
-      <c r="R29" s="209"/>
-      <c r="S29" s="209"/>
-      <c r="T29" s="209"/>
-      <c r="U29" s="209"/>
-      <c r="V29" s="209"/>
-      <c r="W29" s="209"/>
-      <c r="X29" s="209"/>
-      <c r="Y29" s="209"/>
-      <c r="Z29" s="209"/>
-      <c r="AA29" s="209"/>
-      <c r="AB29" s="209"/>
-      <c r="AC29" s="209"/>
-      <c r="AD29" s="209"/>
-      <c r="AE29" s="210"/>
-      <c r="AF29" s="205"/>
-      <c r="AG29" s="206"/>
-      <c r="AH29" s="206"/>
-      <c r="AI29" s="207"/>
+      <c r="B29" s="163"/>
+      <c r="C29" s="164"/>
+      <c r="D29" s="165"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="167"/>
+      <c r="G29" s="163"/>
+      <c r="H29" s="168"/>
+      <c r="I29" s="164"/>
+      <c r="J29" s="169"/>
+      <c r="K29" s="170"/>
+      <c r="L29" s="170"/>
+      <c r="M29" s="170"/>
+      <c r="N29" s="170"/>
+      <c r="O29" s="170"/>
+      <c r="P29" s="171"/>
+      <c r="Q29" s="172"/>
+      <c r="R29" s="173"/>
+      <c r="S29" s="173"/>
+      <c r="T29" s="173"/>
+      <c r="U29" s="173"/>
+      <c r="V29" s="173"/>
+      <c r="W29" s="173"/>
+      <c r="X29" s="173"/>
+      <c r="Y29" s="173"/>
+      <c r="Z29" s="173"/>
+      <c r="AA29" s="173"/>
+      <c r="AB29" s="173"/>
+      <c r="AC29" s="173"/>
+      <c r="AD29" s="173"/>
+      <c r="AE29" s="174"/>
+      <c r="AF29" s="169"/>
+      <c r="AG29" s="170"/>
+      <c r="AH29" s="170"/>
+      <c r="AI29" s="171"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="22"/>
-      <c r="B30" s="199"/>
-      <c r="C30" s="200"/>
-      <c r="D30" s="201"/>
-      <c r="E30" s="202"/>
-      <c r="F30" s="203"/>
-      <c r="G30" s="199"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="200"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="206"/>
-      <c r="L30" s="206"/>
-      <c r="M30" s="206"/>
-      <c r="N30" s="206"/>
-      <c r="O30" s="206"/>
-      <c r="P30" s="207"/>
-      <c r="Q30" s="208"/>
-      <c r="R30" s="209"/>
-      <c r="S30" s="209"/>
-      <c r="T30" s="209"/>
-      <c r="U30" s="209"/>
-      <c r="V30" s="209"/>
-      <c r="W30" s="209"/>
-      <c r="X30" s="209"/>
-      <c r="Y30" s="209"/>
-      <c r="Z30" s="209"/>
-      <c r="AA30" s="209"/>
-      <c r="AB30" s="209"/>
-      <c r="AC30" s="209"/>
-      <c r="AD30" s="209"/>
-      <c r="AE30" s="210"/>
-      <c r="AF30" s="205"/>
-      <c r="AG30" s="206"/>
-      <c r="AH30" s="206"/>
-      <c r="AI30" s="207"/>
+      <c r="B30" s="163"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="165"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="170"/>
+      <c r="L30" s="170"/>
+      <c r="M30" s="170"/>
+      <c r="N30" s="170"/>
+      <c r="O30" s="170"/>
+      <c r="P30" s="171"/>
+      <c r="Q30" s="172"/>
+      <c r="R30" s="173"/>
+      <c r="S30" s="173"/>
+      <c r="T30" s="173"/>
+      <c r="U30" s="173"/>
+      <c r="V30" s="173"/>
+      <c r="W30" s="173"/>
+      <c r="X30" s="173"/>
+      <c r="Y30" s="173"/>
+      <c r="Z30" s="173"/>
+      <c r="AA30" s="173"/>
+      <c r="AB30" s="173"/>
+      <c r="AC30" s="173"/>
+      <c r="AD30" s="173"/>
+      <c r="AE30" s="174"/>
+      <c r="AF30" s="169"/>
+      <c r="AG30" s="170"/>
+      <c r="AH30" s="170"/>
+      <c r="AI30" s="171"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="22"/>
-      <c r="B31" s="199"/>
-      <c r="C31" s="200"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="202"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="199"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="200"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="206"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="206"/>
-      <c r="N31" s="206"/>
-      <c r="O31" s="206"/>
-      <c r="P31" s="207"/>
-      <c r="Q31" s="208"/>
-      <c r="R31" s="209"/>
-      <c r="S31" s="209"/>
-      <c r="T31" s="209"/>
-      <c r="U31" s="209"/>
-      <c r="V31" s="209"/>
-      <c r="W31" s="209"/>
-      <c r="X31" s="209"/>
-      <c r="Y31" s="209"/>
-      <c r="Z31" s="209"/>
-      <c r="AA31" s="209"/>
-      <c r="AB31" s="209"/>
-      <c r="AC31" s="209"/>
-      <c r="AD31" s="209"/>
-      <c r="AE31" s="210"/>
-      <c r="AF31" s="205"/>
-      <c r="AG31" s="206"/>
-      <c r="AH31" s="206"/>
-      <c r="AI31" s="207"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="167"/>
+      <c r="G31" s="163"/>
+      <c r="H31" s="168"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="169"/>
+      <c r="K31" s="170"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="170"/>
+      <c r="N31" s="170"/>
+      <c r="O31" s="170"/>
+      <c r="P31" s="171"/>
+      <c r="Q31" s="172"/>
+      <c r="R31" s="173"/>
+      <c r="S31" s="173"/>
+      <c r="T31" s="173"/>
+      <c r="U31" s="173"/>
+      <c r="V31" s="173"/>
+      <c r="W31" s="173"/>
+      <c r="X31" s="173"/>
+      <c r="Y31" s="173"/>
+      <c r="Z31" s="173"/>
+      <c r="AA31" s="173"/>
+      <c r="AB31" s="173"/>
+      <c r="AC31" s="173"/>
+      <c r="AD31" s="173"/>
+      <c r="AE31" s="174"/>
+      <c r="AF31" s="169"/>
+      <c r="AG31" s="170"/>
+      <c r="AH31" s="170"/>
+      <c r="AI31" s="171"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="22"/>
-      <c r="B32" s="199"/>
-      <c r="C32" s="200"/>
-      <c r="D32" s="201"/>
-      <c r="E32" s="202"/>
-      <c r="F32" s="203"/>
-      <c r="G32" s="199"/>
-      <c r="H32" s="204"/>
-      <c r="I32" s="200"/>
-      <c r="J32" s="205"/>
-      <c r="K32" s="224"/>
-      <c r="L32" s="206"/>
-      <c r="M32" s="206"/>
-      <c r="N32" s="206"/>
-      <c r="O32" s="206"/>
-      <c r="P32" s="207"/>
-      <c r="Q32" s="208"/>
-      <c r="R32" s="209"/>
-      <c r="S32" s="209"/>
-      <c r="T32" s="209"/>
-      <c r="U32" s="209"/>
-      <c r="V32" s="209"/>
-      <c r="W32" s="209"/>
-      <c r="X32" s="209"/>
-      <c r="Y32" s="209"/>
-      <c r="Z32" s="209"/>
-      <c r="AA32" s="209"/>
-      <c r="AB32" s="209"/>
-      <c r="AC32" s="209"/>
-      <c r="AD32" s="209"/>
-      <c r="AE32" s="210"/>
-      <c r="AF32" s="205"/>
-      <c r="AG32" s="206"/>
-      <c r="AH32" s="206"/>
-      <c r="AI32" s="207"/>
+      <c r="B32" s="163"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="167"/>
+      <c r="G32" s="163"/>
+      <c r="H32" s="168"/>
+      <c r="I32" s="164"/>
+      <c r="J32" s="169"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="170"/>
+      <c r="M32" s="170"/>
+      <c r="N32" s="170"/>
+      <c r="O32" s="170"/>
+      <c r="P32" s="171"/>
+      <c r="Q32" s="172"/>
+      <c r="R32" s="173"/>
+      <c r="S32" s="173"/>
+      <c r="T32" s="173"/>
+      <c r="U32" s="173"/>
+      <c r="V32" s="173"/>
+      <c r="W32" s="173"/>
+      <c r="X32" s="173"/>
+      <c r="Y32" s="173"/>
+      <c r="Z32" s="173"/>
+      <c r="AA32" s="173"/>
+      <c r="AB32" s="173"/>
+      <c r="AC32" s="173"/>
+      <c r="AD32" s="173"/>
+      <c r="AE32" s="174"/>
+      <c r="AF32" s="169"/>
+      <c r="AG32" s="170"/>
+      <c r="AH32" s="170"/>
+      <c r="AI32" s="171"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="22"/>
-      <c r="B33" s="199"/>
-      <c r="C33" s="200"/>
-      <c r="D33" s="201"/>
-      <c r="E33" s="202"/>
-      <c r="F33" s="203"/>
-      <c r="G33" s="199"/>
-      <c r="H33" s="204"/>
-      <c r="I33" s="200"/>
-      <c r="J33" s="205"/>
-      <c r="K33" s="206"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="206"/>
-      <c r="N33" s="206"/>
-      <c r="O33" s="206"/>
-      <c r="P33" s="207"/>
-      <c r="Q33" s="208"/>
-      <c r="R33" s="209"/>
-      <c r="S33" s="209"/>
-      <c r="T33" s="209"/>
-      <c r="U33" s="209"/>
-      <c r="V33" s="209"/>
-      <c r="W33" s="209"/>
-      <c r="X33" s="209"/>
-      <c r="Y33" s="209"/>
-      <c r="Z33" s="209"/>
-      <c r="AA33" s="209"/>
-      <c r="AB33" s="209"/>
-      <c r="AC33" s="209"/>
-      <c r="AD33" s="209"/>
-      <c r="AE33" s="210"/>
-      <c r="AF33" s="205"/>
-      <c r="AG33" s="206"/>
-      <c r="AH33" s="206"/>
-      <c r="AI33" s="207"/>
+      <c r="B33" s="163"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="163"/>
+      <c r="H33" s="168"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="169"/>
+      <c r="K33" s="170"/>
+      <c r="L33" s="170"/>
+      <c r="M33" s="170"/>
+      <c r="N33" s="170"/>
+      <c r="O33" s="170"/>
+      <c r="P33" s="171"/>
+      <c r="Q33" s="172"/>
+      <c r="R33" s="173"/>
+      <c r="S33" s="173"/>
+      <c r="T33" s="173"/>
+      <c r="U33" s="173"/>
+      <c r="V33" s="173"/>
+      <c r="W33" s="173"/>
+      <c r="X33" s="173"/>
+      <c r="Y33" s="173"/>
+      <c r="Z33" s="173"/>
+      <c r="AA33" s="173"/>
+      <c r="AB33" s="173"/>
+      <c r="AC33" s="173"/>
+      <c r="AD33" s="173"/>
+      <c r="AE33" s="174"/>
+      <c r="AF33" s="169"/>
+      <c r="AG33" s="170"/>
+      <c r="AH33" s="170"/>
+      <c r="AI33" s="171"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -11864,6 +11708,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -34822,7 +34822,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -34859,7 +34859,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -34892,7 +34892,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -34925,7 +34925,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -34958,7 +34958,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -34993,7 +34993,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -35026,7 +35026,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -35059,7 +35059,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -35092,7 +35092,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -35127,7 +35127,7 @@
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
 _xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
-_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0)),
+_xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D11AB5E-CF61-443E-BF4D-0D9EE7A7AD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B588E4B-C0D6-4AC4-8E06-4E081316372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="555">
   <si>
     <t>更新者：</t>
     <rPh sb="0" eb="3">
@@ -7626,6 +7626,10 @@
   <si>
     <t>ケースNo.</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>リクエストID：</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -21868,7 +21872,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="27"/>
+      <c r="A8" s="27" t="s">
+        <v>554</v>
+      </c>
       <c r="B8" s="27"/>
       <c r="C8" s="28"/>
       <c r="D8" s="27"/>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B588E4B-C0D6-4AC4-8E06-4E081316372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18465A8C-F0CB-4A40-8A76-A4E0BD41F383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="19" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="20" r:id="rId2"/>
     <sheet name="【テストターゲット名】_クラス単体" sheetId="26" r:id="rId3"/>
-    <sheet name="【テストターゲット名】_リクエスト単体" sheetId="25" r:id="rId4"/>
+    <sheet name="【リクエストID】_リクエスト単体" sheetId="25" r:id="rId4"/>
     <sheet name="取引単体" sheetId="24" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【テストターゲット名】_リクエスト単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$295</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【テストターゲット名】_リクエスト単体!$A$1:$R$382</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$382</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$Q$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【テストターゲット名】_リクエスト単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -8855,84 +8855,6 @@
     <xf numFmtId="31" fontId="11" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9039,6 +8961,84 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="34" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="33" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10494,55 +10494,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="204" t="s">
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="205"/>
-      <c r="Q1" s="205"/>
-      <c r="R1" s="206"/>
-      <c r="S1" s="213" t="s">
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
+      <c r="R1" s="180"/>
+      <c r="S1" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="214"/>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="215"/>
-      <c r="AA1" s="195" t="s">
+      <c r="T1" s="188"/>
+      <c r="U1" s="188"/>
+      <c r="V1" s="188"/>
+      <c r="W1" s="188"/>
+      <c r="X1" s="188"/>
+      <c r="Y1" s="188"/>
+      <c r="Z1" s="189"/>
+      <c r="AA1" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="AB1" s="197"/>
-      <c r="AC1" s="222" t="str">
+      <c r="AB1" s="171"/>
+      <c r="AC1" s="196" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v/>
       </c>
-      <c r="AD1" s="223"/>
-      <c r="AE1" s="223"/>
-      <c r="AF1" s="224"/>
-      <c r="AG1" s="189" t="str">
+      <c r="AD1" s="197"/>
+      <c r="AE1" s="197"/>
+      <c r="AF1" s="198"/>
+      <c r="AG1" s="163" t="str">
         <f>IF(D8="","",D8)</f>
         <v/>
       </c>
-      <c r="AH1" s="190"/>
-      <c r="AI1" s="191"/>
+      <c r="AH1" s="164"/>
+      <c r="AI1" s="165"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -10550,51 +10550,51 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="196"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
-      <c r="J2" s="199"/>
-      <c r="K2" s="199"/>
-      <c r="L2" s="199"/>
-      <c r="M2" s="199"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="207"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="209"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="217"/>
-      <c r="V2" s="217"/>
-      <c r="W2" s="217"/>
-      <c r="X2" s="217"/>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="195" t="s">
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="182"/>
+      <c r="Q2" s="182"/>
+      <c r="R2" s="183"/>
+      <c r="S2" s="190"/>
+      <c r="T2" s="191"/>
+      <c r="U2" s="191"/>
+      <c r="V2" s="191"/>
+      <c r="W2" s="191"/>
+      <c r="X2" s="191"/>
+      <c r="Y2" s="191"/>
+      <c r="Z2" s="192"/>
+      <c r="AA2" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="AB2" s="197"/>
-      <c r="AC2" s="201" t="str">
+      <c r="AB2" s="171"/>
+      <c r="AC2" s="175" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v/>
       </c>
-      <c r="AD2" s="202"/>
-      <c r="AE2" s="202"/>
-      <c r="AF2" s="203"/>
-      <c r="AG2" s="189" t="str">
+      <c r="AD2" s="176"/>
+      <c r="AE2" s="176"/>
+      <c r="AF2" s="177"/>
+      <c r="AG2" s="163" t="str">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v/>
       </c>
-      <c r="AH2" s="190"/>
-      <c r="AI2" s="191"/>
+      <c r="AH2" s="164"/>
+      <c r="AI2" s="165"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -10602,43 +10602,43 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="199"/>
-      <c r="N3" s="200"/>
-      <c r="O3" s="210"/>
-      <c r="P3" s="211"/>
-      <c r="Q3" s="211"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="219"/>
-      <c r="T3" s="220"/>
-      <c r="U3" s="220"/>
-      <c r="V3" s="220"/>
-      <c r="W3" s="220"/>
-      <c r="X3" s="220"/>
-      <c r="Y3" s="220"/>
-      <c r="Z3" s="221"/>
-      <c r="AA3" s="195"/>
-      <c r="AB3" s="197"/>
-      <c r="AC3" s="222"/>
-      <c r="AD3" s="223"/>
-      <c r="AE3" s="223"/>
-      <c r="AF3" s="224"/>
-      <c r="AG3" s="189"/>
-      <c r="AH3" s="190"/>
-      <c r="AI3" s="191"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="184"/>
+      <c r="P3" s="185"/>
+      <c r="Q3" s="185"/>
+      <c r="R3" s="186"/>
+      <c r="S3" s="193"/>
+      <c r="T3" s="194"/>
+      <c r="U3" s="194"/>
+      <c r="V3" s="194"/>
+      <c r="W3" s="194"/>
+      <c r="X3" s="194"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="195"/>
+      <c r="AA3" s="169"/>
+      <c r="AB3" s="171"/>
+      <c r="AC3" s="196"/>
+      <c r="AD3" s="197"/>
+      <c r="AE3" s="197"/>
+      <c r="AF3" s="198"/>
+      <c r="AG3" s="163"/>
+      <c r="AH3" s="164"/>
+      <c r="AI3" s="165"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -10675,1020 +10675,1176 @@
       <c r="A7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="192" t="s">
+      <c r="B7" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="193"/>
-      <c r="D7" s="192" t="s">
+      <c r="C7" s="167"/>
+      <c r="D7" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="194"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="192" t="s">
+      <c r="E7" s="168"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="194"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="192" t="s">
+      <c r="H7" s="168"/>
+      <c r="I7" s="167"/>
+      <c r="J7" s="166" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="194"/>
-      <c r="L7" s="194"/>
-      <c r="M7" s="194"/>
-      <c r="N7" s="194"/>
-      <c r="O7" s="194"/>
-      <c r="P7" s="193"/>
-      <c r="Q7" s="192" t="s">
+      <c r="K7" s="168"/>
+      <c r="L7" s="168"/>
+      <c r="M7" s="168"/>
+      <c r="N7" s="168"/>
+      <c r="O7" s="168"/>
+      <c r="P7" s="167"/>
+      <c r="Q7" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="R7" s="194"/>
-      <c r="S7" s="194"/>
-      <c r="T7" s="194"/>
-      <c r="U7" s="194"/>
-      <c r="V7" s="194"/>
-      <c r="W7" s="194"/>
-      <c r="X7" s="194"/>
-      <c r="Y7" s="194"/>
-      <c r="Z7" s="194"/>
-      <c r="AA7" s="194"/>
-      <c r="AB7" s="194"/>
-      <c r="AC7" s="194"/>
-      <c r="AD7" s="194"/>
-      <c r="AE7" s="193"/>
-      <c r="AF7" s="192" t="s">
+      <c r="R7" s="168"/>
+      <c r="S7" s="168"/>
+      <c r="T7" s="168"/>
+      <c r="U7" s="168"/>
+      <c r="V7" s="168"/>
+      <c r="W7" s="168"/>
+      <c r="X7" s="168"/>
+      <c r="Y7" s="168"/>
+      <c r="Z7" s="168"/>
+      <c r="AA7" s="168"/>
+      <c r="AB7" s="168"/>
+      <c r="AC7" s="168"/>
+      <c r="AD7" s="168"/>
+      <c r="AE7" s="167"/>
+      <c r="AF7" s="166" t="s">
         <v>61</v>
       </c>
-      <c r="AG7" s="194"/>
-      <c r="AH7" s="194"/>
-      <c r="AI7" s="193"/>
+      <c r="AG7" s="168"/>
+      <c r="AH7" s="168"/>
+      <c r="AI7" s="167"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="21"/>
-      <c r="B8" s="176"/>
-      <c r="C8" s="177"/>
-      <c r="D8" s="178"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="181"/>
-      <c r="H8" s="182"/>
-      <c r="I8" s="177"/>
-      <c r="J8" s="183"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="185"/>
-      <c r="Q8" s="186"/>
-      <c r="R8" s="187"/>
-      <c r="S8" s="187"/>
-      <c r="T8" s="187"/>
-      <c r="U8" s="187"/>
-      <c r="V8" s="187"/>
-      <c r="W8" s="187"/>
-      <c r="X8" s="187"/>
-      <c r="Y8" s="187"/>
-      <c r="Z8" s="187"/>
-      <c r="AA8" s="187"/>
-      <c r="AB8" s="187"/>
-      <c r="AC8" s="187"/>
-      <c r="AD8" s="187"/>
-      <c r="AE8" s="188"/>
-      <c r="AF8" s="183"/>
-      <c r="AG8" s="184"/>
-      <c r="AH8" s="184"/>
-      <c r="AI8" s="185"/>
+      <c r="B8" s="211"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="213"/>
+      <c r="E8" s="214"/>
+      <c r="F8" s="215"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="212"/>
+      <c r="J8" s="218"/>
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="220"/>
+      <c r="Q8" s="221"/>
+      <c r="R8" s="222"/>
+      <c r="S8" s="222"/>
+      <c r="T8" s="222"/>
+      <c r="U8" s="222"/>
+      <c r="V8" s="222"/>
+      <c r="W8" s="222"/>
+      <c r="X8" s="222"/>
+      <c r="Y8" s="222"/>
+      <c r="Z8" s="222"/>
+      <c r="AA8" s="222"/>
+      <c r="AB8" s="222"/>
+      <c r="AC8" s="222"/>
+      <c r="AD8" s="222"/>
+      <c r="AE8" s="223"/>
+      <c r="AF8" s="218"/>
+      <c r="AG8" s="219"/>
+      <c r="AH8" s="219"/>
+      <c r="AI8" s="220"/>
     </row>
     <row r="9" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="22"/>
-      <c r="B9" s="163"/>
-      <c r="C9" s="164"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="166"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="168"/>
-      <c r="I9" s="164"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="170"/>
-      <c r="L9" s="170"/>
-      <c r="M9" s="170"/>
-      <c r="N9" s="170"/>
-      <c r="O9" s="170"/>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="172"/>
-      <c r="R9" s="173"/>
-      <c r="S9" s="173"/>
-      <c r="T9" s="173"/>
-      <c r="U9" s="173"/>
-      <c r="V9" s="173"/>
-      <c r="W9" s="173"/>
-      <c r="X9" s="173"/>
-      <c r="Y9" s="173"/>
-      <c r="Z9" s="173"/>
-      <c r="AA9" s="173"/>
-      <c r="AB9" s="173"/>
-      <c r="AC9" s="173"/>
-      <c r="AD9" s="173"/>
-      <c r="AE9" s="174"/>
-      <c r="AF9" s="169"/>
-      <c r="AG9" s="170"/>
-      <c r="AH9" s="170"/>
-      <c r="AI9" s="171"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="202"/>
+      <c r="F9" s="203"/>
+      <c r="G9" s="201"/>
+      <c r="H9" s="204"/>
+      <c r="I9" s="200"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="206"/>
+      <c r="O9" s="206"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="209"/>
+      <c r="S9" s="209"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="209"/>
+      <c r="V9" s="209"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
+      <c r="AD9" s="209"/>
+      <c r="AE9" s="210"/>
+      <c r="AF9" s="205"/>
+      <c r="AG9" s="206"/>
+      <c r="AH9" s="206"/>
+      <c r="AI9" s="207"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="22"/>
-      <c r="B10" s="163"/>
-      <c r="C10" s="164"/>
-      <c r="D10" s="165"/>
-      <c r="E10" s="166"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="164"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="170"/>
-      <c r="L10" s="170"/>
-      <c r="M10" s="170"/>
-      <c r="N10" s="170"/>
-      <c r="O10" s="170"/>
-      <c r="P10" s="171"/>
-      <c r="Q10" s="172"/>
-      <c r="R10" s="173"/>
-      <c r="S10" s="173"/>
-      <c r="T10" s="173"/>
-      <c r="U10" s="173"/>
-      <c r="V10" s="173"/>
-      <c r="W10" s="173"/>
-      <c r="X10" s="173"/>
-      <c r="Y10" s="173"/>
-      <c r="Z10" s="173"/>
-      <c r="AA10" s="173"/>
-      <c r="AB10" s="173"/>
-      <c r="AC10" s="173"/>
-      <c r="AD10" s="173"/>
-      <c r="AE10" s="174"/>
-      <c r="AF10" s="169"/>
-      <c r="AG10" s="170"/>
-      <c r="AH10" s="170"/>
-      <c r="AI10" s="171"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="202"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="199"/>
+      <c r="H10" s="204"/>
+      <c r="I10" s="200"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="206"/>
+      <c r="L10" s="206"/>
+      <c r="M10" s="206"/>
+      <c r="N10" s="206"/>
+      <c r="O10" s="206"/>
+      <c r="P10" s="207"/>
+      <c r="Q10" s="208"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="209"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="209"/>
+      <c r="V10" s="209"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
+      <c r="Z10" s="209"/>
+      <c r="AA10" s="209"/>
+      <c r="AB10" s="209"/>
+      <c r="AC10" s="209"/>
+      <c r="AD10" s="209"/>
+      <c r="AE10" s="210"/>
+      <c r="AF10" s="205"/>
+      <c r="AG10" s="206"/>
+      <c r="AH10" s="206"/>
+      <c r="AI10" s="207"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="22"/>
-      <c r="B11" s="163"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="166"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="168"/>
-      <c r="I11" s="164"/>
-      <c r="J11" s="169"/>
-      <c r="K11" s="170"/>
-      <c r="L11" s="170"/>
-      <c r="M11" s="170"/>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="172"/>
-      <c r="R11" s="173"/>
-      <c r="S11" s="173"/>
-      <c r="T11" s="173"/>
-      <c r="U11" s="173"/>
-      <c r="V11" s="173"/>
-      <c r="W11" s="173"/>
-      <c r="X11" s="173"/>
-      <c r="Y11" s="173"/>
-      <c r="Z11" s="173"/>
-      <c r="AA11" s="173"/>
-      <c r="AB11" s="173"/>
-      <c r="AC11" s="173"/>
-      <c r="AD11" s="173"/>
-      <c r="AE11" s="174"/>
-      <c r="AF11" s="169"/>
-      <c r="AG11" s="170"/>
-      <c r="AH11" s="170"/>
-      <c r="AI11" s="171"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="201"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="203"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="204"/>
+      <c r="I11" s="200"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="206"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="206"/>
+      <c r="P11" s="207"/>
+      <c r="Q11" s="208"/>
+      <c r="R11" s="209"/>
+      <c r="S11" s="209"/>
+      <c r="T11" s="209"/>
+      <c r="U11" s="209"/>
+      <c r="V11" s="209"/>
+      <c r="W11" s="209"/>
+      <c r="X11" s="209"/>
+      <c r="Y11" s="209"/>
+      <c r="Z11" s="209"/>
+      <c r="AA11" s="209"/>
+      <c r="AB11" s="209"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="209"/>
+      <c r="AE11" s="210"/>
+      <c r="AF11" s="205"/>
+      <c r="AG11" s="206"/>
+      <c r="AH11" s="206"/>
+      <c r="AI11" s="207"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="22"/>
-      <c r="B12" s="163"/>
-      <c r="C12" s="164"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="166"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="168"/>
-      <c r="I12" s="164"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="170"/>
-      <c r="L12" s="170"/>
-      <c r="M12" s="170"/>
-      <c r="N12" s="170"/>
-      <c r="O12" s="170"/>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="173"/>
-      <c r="S12" s="173"/>
-      <c r="T12" s="173"/>
-      <c r="U12" s="173"/>
-      <c r="V12" s="173"/>
-      <c r="W12" s="173"/>
-      <c r="X12" s="173"/>
-      <c r="Y12" s="173"/>
-      <c r="Z12" s="173"/>
-      <c r="AA12" s="173"/>
-      <c r="AB12" s="173"/>
-      <c r="AC12" s="173"/>
-      <c r="AD12" s="173"/>
-      <c r="AE12" s="174"/>
-      <c r="AF12" s="169"/>
-      <c r="AG12" s="170"/>
-      <c r="AH12" s="170"/>
-      <c r="AI12" s="171"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="200"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="199"/>
+      <c r="H12" s="204"/>
+      <c r="I12" s="200"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="206"/>
+      <c r="L12" s="206"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="206"/>
+      <c r="O12" s="206"/>
+      <c r="P12" s="207"/>
+      <c r="Q12" s="208"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="209"/>
+      <c r="T12" s="209"/>
+      <c r="U12" s="209"/>
+      <c r="V12" s="209"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
+      <c r="Z12" s="209"/>
+      <c r="AA12" s="209"/>
+      <c r="AB12" s="209"/>
+      <c r="AC12" s="209"/>
+      <c r="AD12" s="209"/>
+      <c r="AE12" s="210"/>
+      <c r="AF12" s="205"/>
+      <c r="AG12" s="206"/>
+      <c r="AH12" s="206"/>
+      <c r="AI12" s="207"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="22"/>
-      <c r="B13" s="163"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="167"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="168"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="169"/>
-      <c r="K13" s="170"/>
-      <c r="L13" s="170"/>
-      <c r="M13" s="170"/>
-      <c r="N13" s="170"/>
-      <c r="O13" s="170"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="172"/>
-      <c r="R13" s="173"/>
-      <c r="S13" s="173"/>
-      <c r="T13" s="173"/>
-      <c r="U13" s="173"/>
-      <c r="V13" s="173"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="173"/>
-      <c r="Y13" s="173"/>
-      <c r="Z13" s="173"/>
-      <c r="AA13" s="173"/>
-      <c r="AB13" s="173"/>
-      <c r="AC13" s="173"/>
-      <c r="AD13" s="173"/>
-      <c r="AE13" s="174"/>
-      <c r="AF13" s="169"/>
-      <c r="AG13" s="170"/>
-      <c r="AH13" s="170"/>
-      <c r="AI13" s="171"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="201"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="199"/>
+      <c r="H13" s="204"/>
+      <c r="I13" s="200"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="206"/>
+      <c r="L13" s="206"/>
+      <c r="M13" s="206"/>
+      <c r="N13" s="206"/>
+      <c r="O13" s="206"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="208"/>
+      <c r="R13" s="209"/>
+      <c r="S13" s="209"/>
+      <c r="T13" s="209"/>
+      <c r="U13" s="209"/>
+      <c r="V13" s="209"/>
+      <c r="W13" s="209"/>
+      <c r="X13" s="209"/>
+      <c r="Y13" s="209"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="209"/>
+      <c r="AB13" s="209"/>
+      <c r="AC13" s="209"/>
+      <c r="AD13" s="209"/>
+      <c r="AE13" s="210"/>
+      <c r="AF13" s="205"/>
+      <c r="AG13" s="206"/>
+      <c r="AH13" s="206"/>
+      <c r="AI13" s="207"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="22"/>
-      <c r="B14" s="163"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="165"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="168"/>
-      <c r="I14" s="164"/>
-      <c r="J14" s="169"/>
-      <c r="K14" s="170"/>
-      <c r="L14" s="170"/>
-      <c r="M14" s="170"/>
-      <c r="N14" s="170"/>
-      <c r="O14" s="170"/>
-      <c r="P14" s="171"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="173"/>
-      <c r="S14" s="173"/>
-      <c r="T14" s="173"/>
-      <c r="U14" s="173"/>
-      <c r="V14" s="173"/>
-      <c r="W14" s="173"/>
-      <c r="X14" s="173"/>
-      <c r="Y14" s="173"/>
-      <c r="Z14" s="173"/>
-      <c r="AA14" s="173"/>
-      <c r="AB14" s="173"/>
-      <c r="AC14" s="173"/>
-      <c r="AD14" s="173"/>
-      <c r="AE14" s="174"/>
-      <c r="AF14" s="169"/>
-      <c r="AG14" s="170"/>
-      <c r="AH14" s="170"/>
-      <c r="AI14" s="171"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="199"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="200"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="206"/>
+      <c r="L14" s="206"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="206"/>
+      <c r="O14" s="206"/>
+      <c r="P14" s="207"/>
+      <c r="Q14" s="208"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="209"/>
+      <c r="T14" s="209"/>
+      <c r="U14" s="209"/>
+      <c r="V14" s="209"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
+      <c r="Z14" s="209"/>
+      <c r="AA14" s="209"/>
+      <c r="AB14" s="209"/>
+      <c r="AC14" s="209"/>
+      <c r="AD14" s="209"/>
+      <c r="AE14" s="210"/>
+      <c r="AF14" s="205"/>
+      <c r="AG14" s="206"/>
+      <c r="AH14" s="206"/>
+      <c r="AI14" s="207"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="22"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="166"/>
-      <c r="F15" s="167"/>
-      <c r="G15" s="163"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="164"/>
-      <c r="J15" s="169"/>
-      <c r="K15" s="170"/>
-      <c r="L15" s="170"/>
-      <c r="M15" s="170"/>
-      <c r="N15" s="170"/>
-      <c r="O15" s="170"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="172"/>
-      <c r="R15" s="173"/>
-      <c r="S15" s="173"/>
-      <c r="T15" s="173"/>
-      <c r="U15" s="173"/>
-      <c r="V15" s="173"/>
-      <c r="W15" s="173"/>
-      <c r="X15" s="173"/>
-      <c r="Y15" s="173"/>
-      <c r="Z15" s="173"/>
-      <c r="AA15" s="173"/>
-      <c r="AB15" s="173"/>
-      <c r="AC15" s="173"/>
-      <c r="AD15" s="173"/>
-      <c r="AE15" s="174"/>
-      <c r="AF15" s="169"/>
-      <c r="AG15" s="170"/>
-      <c r="AH15" s="170"/>
-      <c r="AI15" s="171"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="199"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="206"/>
+      <c r="L15" s="206"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="206"/>
+      <c r="P15" s="207"/>
+      <c r="Q15" s="208"/>
+      <c r="R15" s="209"/>
+      <c r="S15" s="209"/>
+      <c r="T15" s="209"/>
+      <c r="U15" s="209"/>
+      <c r="V15" s="209"/>
+      <c r="W15" s="209"/>
+      <c r="X15" s="209"/>
+      <c r="Y15" s="209"/>
+      <c r="Z15" s="209"/>
+      <c r="AA15" s="209"/>
+      <c r="AB15" s="209"/>
+      <c r="AC15" s="209"/>
+      <c r="AD15" s="209"/>
+      <c r="AE15" s="210"/>
+      <c r="AF15" s="205"/>
+      <c r="AG15" s="206"/>
+      <c r="AH15" s="206"/>
+      <c r="AI15" s="207"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="22"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="164"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="170"/>
-      <c r="L16" s="170"/>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="170"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="172"/>
-      <c r="R16" s="173"/>
-      <c r="S16" s="173"/>
-      <c r="T16" s="173"/>
-      <c r="U16" s="173"/>
-      <c r="V16" s="173"/>
-      <c r="W16" s="173"/>
-      <c r="X16" s="173"/>
-      <c r="Y16" s="173"/>
-      <c r="Z16" s="173"/>
-      <c r="AA16" s="173"/>
-      <c r="AB16" s="173"/>
-      <c r="AC16" s="173"/>
-      <c r="AD16" s="173"/>
-      <c r="AE16" s="174"/>
-      <c r="AF16" s="169"/>
-      <c r="AG16" s="170"/>
-      <c r="AH16" s="170"/>
-      <c r="AI16" s="171"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="202"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="199"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="200"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="206"/>
+      <c r="L16" s="206"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="206"/>
+      <c r="O16" s="206"/>
+      <c r="P16" s="207"/>
+      <c r="Q16" s="208"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="209"/>
+      <c r="U16" s="209"/>
+      <c r="V16" s="209"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
+      <c r="Z16" s="209"/>
+      <c r="AA16" s="209"/>
+      <c r="AB16" s="209"/>
+      <c r="AC16" s="209"/>
+      <c r="AD16" s="209"/>
+      <c r="AE16" s="210"/>
+      <c r="AF16" s="205"/>
+      <c r="AG16" s="206"/>
+      <c r="AH16" s="206"/>
+      <c r="AI16" s="207"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="22"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="166"/>
-      <c r="F17" s="167"/>
-      <c r="G17" s="163"/>
-      <c r="H17" s="168"/>
-      <c r="I17" s="164"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="170"/>
-      <c r="L17" s="170"/>
-      <c r="M17" s="170"/>
-      <c r="N17" s="170"/>
-      <c r="O17" s="170"/>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="172"/>
-      <c r="R17" s="173"/>
-      <c r="S17" s="173"/>
-      <c r="T17" s="173"/>
-      <c r="U17" s="173"/>
-      <c r="V17" s="173"/>
-      <c r="W17" s="173"/>
-      <c r="X17" s="173"/>
-      <c r="Y17" s="173"/>
-      <c r="Z17" s="173"/>
-      <c r="AA17" s="173"/>
-      <c r="AB17" s="173"/>
-      <c r="AC17" s="173"/>
-      <c r="AD17" s="173"/>
-      <c r="AE17" s="174"/>
-      <c r="AF17" s="169"/>
-      <c r="AG17" s="170"/>
-      <c r="AH17" s="170"/>
-      <c r="AI17" s="171"/>
+      <c r="B17" s="199"/>
+      <c r="C17" s="200"/>
+      <c r="D17" s="201"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="203"/>
+      <c r="G17" s="199"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="200"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="206"/>
+      <c r="L17" s="206"/>
+      <c r="M17" s="206"/>
+      <c r="N17" s="206"/>
+      <c r="O17" s="206"/>
+      <c r="P17" s="207"/>
+      <c r="Q17" s="208"/>
+      <c r="R17" s="209"/>
+      <c r="S17" s="209"/>
+      <c r="T17" s="209"/>
+      <c r="U17" s="209"/>
+      <c r="V17" s="209"/>
+      <c r="W17" s="209"/>
+      <c r="X17" s="209"/>
+      <c r="Y17" s="209"/>
+      <c r="Z17" s="209"/>
+      <c r="AA17" s="209"/>
+      <c r="AB17" s="209"/>
+      <c r="AC17" s="209"/>
+      <c r="AD17" s="209"/>
+      <c r="AE17" s="210"/>
+      <c r="AF17" s="205"/>
+      <c r="AG17" s="206"/>
+      <c r="AH17" s="206"/>
+      <c r="AI17" s="207"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="B18" s="163"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="168"/>
-      <c r="I18" s="164"/>
-      <c r="J18" s="169"/>
-      <c r="K18" s="170"/>
-      <c r="L18" s="170"/>
-      <c r="M18" s="170"/>
-      <c r="N18" s="170"/>
-      <c r="O18" s="170"/>
-      <c r="P18" s="171"/>
-      <c r="Q18" s="172"/>
-      <c r="R18" s="173"/>
-      <c r="S18" s="173"/>
-      <c r="T18" s="173"/>
-      <c r="U18" s="173"/>
-      <c r="V18" s="173"/>
-      <c r="W18" s="173"/>
-      <c r="X18" s="173"/>
-      <c r="Y18" s="173"/>
-      <c r="Z18" s="173"/>
-      <c r="AA18" s="173"/>
-      <c r="AB18" s="173"/>
-      <c r="AC18" s="173"/>
-      <c r="AD18" s="173"/>
-      <c r="AE18" s="174"/>
-      <c r="AF18" s="169"/>
-      <c r="AG18" s="170"/>
-      <c r="AH18" s="170"/>
-      <c r="AI18" s="171"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="200"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="199"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="200"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="206"/>
+      <c r="L18" s="206"/>
+      <c r="M18" s="206"/>
+      <c r="N18" s="206"/>
+      <c r="O18" s="206"/>
+      <c r="P18" s="207"/>
+      <c r="Q18" s="208"/>
+      <c r="R18" s="209"/>
+      <c r="S18" s="209"/>
+      <c r="T18" s="209"/>
+      <c r="U18" s="209"/>
+      <c r="V18" s="209"/>
+      <c r="W18" s="209"/>
+      <c r="X18" s="209"/>
+      <c r="Y18" s="209"/>
+      <c r="Z18" s="209"/>
+      <c r="AA18" s="209"/>
+      <c r="AB18" s="209"/>
+      <c r="AC18" s="209"/>
+      <c r="AD18" s="209"/>
+      <c r="AE18" s="210"/>
+      <c r="AF18" s="205"/>
+      <c r="AG18" s="206"/>
+      <c r="AH18" s="206"/>
+      <c r="AI18" s="207"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="22"/>
-      <c r="B19" s="163"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="167"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="168"/>
-      <c r="I19" s="164"/>
-      <c r="J19" s="169"/>
-      <c r="K19" s="170"/>
-      <c r="L19" s="170"/>
-      <c r="M19" s="170"/>
-      <c r="N19" s="170"/>
-      <c r="O19" s="170"/>
-      <c r="P19" s="171"/>
-      <c r="Q19" s="172"/>
-      <c r="R19" s="173"/>
-      <c r="S19" s="173"/>
-      <c r="T19" s="173"/>
-      <c r="U19" s="173"/>
-      <c r="V19" s="173"/>
-      <c r="W19" s="173"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="173"/>
-      <c r="AA19" s="173"/>
-      <c r="AB19" s="173"/>
-      <c r="AC19" s="173"/>
-      <c r="AD19" s="173"/>
-      <c r="AE19" s="174"/>
-      <c r="AF19" s="169"/>
-      <c r="AG19" s="170"/>
-      <c r="AH19" s="170"/>
-      <c r="AI19" s="171"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="200"/>
+      <c r="D19" s="201"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="199"/>
+      <c r="H19" s="204"/>
+      <c r="I19" s="200"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="206"/>
+      <c r="L19" s="206"/>
+      <c r="M19" s="206"/>
+      <c r="N19" s="206"/>
+      <c r="O19" s="206"/>
+      <c r="P19" s="207"/>
+      <c r="Q19" s="208"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
+      <c r="W19" s="209"/>
+      <c r="X19" s="209"/>
+      <c r="Y19" s="209"/>
+      <c r="Z19" s="209"/>
+      <c r="AA19" s="209"/>
+      <c r="AB19" s="209"/>
+      <c r="AC19" s="209"/>
+      <c r="AD19" s="209"/>
+      <c r="AE19" s="210"/>
+      <c r="AF19" s="205"/>
+      <c r="AG19" s="206"/>
+      <c r="AH19" s="206"/>
+      <c r="AI19" s="207"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="22"/>
-      <c r="B20" s="163"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="166"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="168"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="170"/>
-      <c r="L20" s="170"/>
-      <c r="M20" s="170"/>
-      <c r="N20" s="170"/>
-      <c r="O20" s="170"/>
-      <c r="P20" s="171"/>
-      <c r="Q20" s="172"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="173"/>
-      <c r="T20" s="173"/>
-      <c r="U20" s="173"/>
-      <c r="V20" s="173"/>
-      <c r="W20" s="173"/>
-      <c r="X20" s="173"/>
-      <c r="Y20" s="173"/>
-      <c r="Z20" s="173"/>
-      <c r="AA20" s="173"/>
-      <c r="AB20" s="173"/>
-      <c r="AC20" s="173"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="174"/>
-      <c r="AF20" s="169"/>
-      <c r="AG20" s="170"/>
-      <c r="AH20" s="170"/>
-      <c r="AI20" s="171"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="201"/>
+      <c r="E20" s="202"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="199"/>
+      <c r="H20" s="204"/>
+      <c r="I20" s="200"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="206"/>
+      <c r="L20" s="206"/>
+      <c r="M20" s="206"/>
+      <c r="N20" s="206"/>
+      <c r="O20" s="206"/>
+      <c r="P20" s="207"/>
+      <c r="Q20" s="208"/>
+      <c r="R20" s="209"/>
+      <c r="S20" s="209"/>
+      <c r="T20" s="209"/>
+      <c r="U20" s="209"/>
+      <c r="V20" s="209"/>
+      <c r="W20" s="209"/>
+      <c r="X20" s="209"/>
+      <c r="Y20" s="209"/>
+      <c r="Z20" s="209"/>
+      <c r="AA20" s="209"/>
+      <c r="AB20" s="209"/>
+      <c r="AC20" s="209"/>
+      <c r="AD20" s="209"/>
+      <c r="AE20" s="210"/>
+      <c r="AF20" s="205"/>
+      <c r="AG20" s="206"/>
+      <c r="AH20" s="206"/>
+      <c r="AI20" s="207"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="22"/>
-      <c r="B21" s="163"/>
-      <c r="C21" s="164"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="167"/>
-      <c r="G21" s="163"/>
-      <c r="H21" s="168"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="170"/>
-      <c r="L21" s="170"/>
-      <c r="M21" s="170"/>
-      <c r="N21" s="170"/>
-      <c r="O21" s="170"/>
-      <c r="P21" s="171"/>
-      <c r="Q21" s="172"/>
-      <c r="R21" s="173"/>
-      <c r="S21" s="173"/>
-      <c r="T21" s="173"/>
-      <c r="U21" s="173"/>
-      <c r="V21" s="173"/>
-      <c r="W21" s="173"/>
-      <c r="X21" s="173"/>
-      <c r="Y21" s="173"/>
-      <c r="Z21" s="173"/>
-      <c r="AA21" s="173"/>
-      <c r="AB21" s="173"/>
-      <c r="AC21" s="173"/>
-      <c r="AD21" s="173"/>
-      <c r="AE21" s="174"/>
-      <c r="AF21" s="169"/>
-      <c r="AG21" s="170"/>
-      <c r="AH21" s="170"/>
-      <c r="AI21" s="171"/>
+      <c r="B21" s="199"/>
+      <c r="C21" s="200"/>
+      <c r="D21" s="201"/>
+      <c r="E21" s="202"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="199"/>
+      <c r="H21" s="204"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="206"/>
+      <c r="L21" s="206"/>
+      <c r="M21" s="206"/>
+      <c r="N21" s="206"/>
+      <c r="O21" s="206"/>
+      <c r="P21" s="207"/>
+      <c r="Q21" s="208"/>
+      <c r="R21" s="209"/>
+      <c r="S21" s="209"/>
+      <c r="T21" s="209"/>
+      <c r="U21" s="209"/>
+      <c r="V21" s="209"/>
+      <c r="W21" s="209"/>
+      <c r="X21" s="209"/>
+      <c r="Y21" s="209"/>
+      <c r="Z21" s="209"/>
+      <c r="AA21" s="209"/>
+      <c r="AB21" s="209"/>
+      <c r="AC21" s="209"/>
+      <c r="AD21" s="209"/>
+      <c r="AE21" s="210"/>
+      <c r="AF21" s="205"/>
+      <c r="AG21" s="206"/>
+      <c r="AH21" s="206"/>
+      <c r="AI21" s="207"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="22"/>
-      <c r="B22" s="163"/>
-      <c r="C22" s="164"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="167"/>
-      <c r="G22" s="163"/>
-      <c r="H22" s="168"/>
-      <c r="I22" s="164"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="170"/>
-      <c r="M22" s="170"/>
-      <c r="N22" s="170"/>
-      <c r="O22" s="170"/>
-      <c r="P22" s="171"/>
-      <c r="Q22" s="172"/>
-      <c r="R22" s="173"/>
-      <c r="S22" s="173"/>
-      <c r="T22" s="173"/>
-      <c r="U22" s="173"/>
-      <c r="V22" s="173"/>
-      <c r="W22" s="173"/>
-      <c r="X22" s="173"/>
-      <c r="Y22" s="173"/>
-      <c r="Z22" s="173"/>
-      <c r="AA22" s="173"/>
-      <c r="AB22" s="173"/>
-      <c r="AC22" s="173"/>
-      <c r="AD22" s="173"/>
-      <c r="AE22" s="174"/>
-      <c r="AF22" s="169"/>
-      <c r="AG22" s="170"/>
-      <c r="AH22" s="170"/>
-      <c r="AI22" s="171"/>
+      <c r="B22" s="199"/>
+      <c r="C22" s="200"/>
+      <c r="D22" s="201"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="204"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="206"/>
+      <c r="L22" s="206"/>
+      <c r="M22" s="206"/>
+      <c r="N22" s="206"/>
+      <c r="O22" s="206"/>
+      <c r="P22" s="207"/>
+      <c r="Q22" s="208"/>
+      <c r="R22" s="209"/>
+      <c r="S22" s="209"/>
+      <c r="T22" s="209"/>
+      <c r="U22" s="209"/>
+      <c r="V22" s="209"/>
+      <c r="W22" s="209"/>
+      <c r="X22" s="209"/>
+      <c r="Y22" s="209"/>
+      <c r="Z22" s="209"/>
+      <c r="AA22" s="209"/>
+      <c r="AB22" s="209"/>
+      <c r="AC22" s="209"/>
+      <c r="AD22" s="209"/>
+      <c r="AE22" s="210"/>
+      <c r="AF22" s="205"/>
+      <c r="AG22" s="206"/>
+      <c r="AH22" s="206"/>
+      <c r="AI22" s="207"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="22"/>
-      <c r="B23" s="163"/>
-      <c r="C23" s="164"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="167"/>
-      <c r="G23" s="163"/>
-      <c r="H23" s="168"/>
-      <c r="I23" s="164"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="170"/>
-      <c r="L23" s="170"/>
-      <c r="M23" s="170"/>
-      <c r="N23" s="170"/>
-      <c r="O23" s="170"/>
-      <c r="P23" s="171"/>
-      <c r="Q23" s="172"/>
-      <c r="R23" s="173"/>
-      <c r="S23" s="173"/>
-      <c r="T23" s="173"/>
-      <c r="U23" s="173"/>
-      <c r="V23" s="173"/>
-      <c r="W23" s="173"/>
-      <c r="X23" s="173"/>
-      <c r="Y23" s="173"/>
-      <c r="Z23" s="173"/>
-      <c r="AA23" s="173"/>
-      <c r="AB23" s="173"/>
-      <c r="AC23" s="173"/>
-      <c r="AD23" s="173"/>
-      <c r="AE23" s="174"/>
-      <c r="AF23" s="169"/>
-      <c r="AG23" s="170"/>
-      <c r="AH23" s="170"/>
-      <c r="AI23" s="171"/>
+      <c r="B23" s="199"/>
+      <c r="C23" s="200"/>
+      <c r="D23" s="201"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="199"/>
+      <c r="H23" s="204"/>
+      <c r="I23" s="200"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="206"/>
+      <c r="L23" s="206"/>
+      <c r="M23" s="206"/>
+      <c r="N23" s="206"/>
+      <c r="O23" s="206"/>
+      <c r="P23" s="207"/>
+      <c r="Q23" s="208"/>
+      <c r="R23" s="209"/>
+      <c r="S23" s="209"/>
+      <c r="T23" s="209"/>
+      <c r="U23" s="209"/>
+      <c r="V23" s="209"/>
+      <c r="W23" s="209"/>
+      <c r="X23" s="209"/>
+      <c r="Y23" s="209"/>
+      <c r="Z23" s="209"/>
+      <c r="AA23" s="209"/>
+      <c r="AB23" s="209"/>
+      <c r="AC23" s="209"/>
+      <c r="AD23" s="209"/>
+      <c r="AE23" s="210"/>
+      <c r="AF23" s="205"/>
+      <c r="AG23" s="206"/>
+      <c r="AH23" s="206"/>
+      <c r="AI23" s="207"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="22"/>
-      <c r="B24" s="163"/>
-      <c r="C24" s="164"/>
-      <c r="D24" s="165"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="164"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="170"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="170"/>
-      <c r="N24" s="170"/>
-      <c r="O24" s="170"/>
-      <c r="P24" s="171"/>
-      <c r="Q24" s="172"/>
-      <c r="R24" s="173"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="174"/>
-      <c r="AF24" s="169"/>
-      <c r="AG24" s="170"/>
-      <c r="AH24" s="170"/>
-      <c r="AI24" s="171"/>
+      <c r="B24" s="199"/>
+      <c r="C24" s="200"/>
+      <c r="D24" s="201"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="199"/>
+      <c r="H24" s="204"/>
+      <c r="I24" s="200"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="206"/>
+      <c r="L24" s="206"/>
+      <c r="M24" s="206"/>
+      <c r="N24" s="206"/>
+      <c r="O24" s="206"/>
+      <c r="P24" s="207"/>
+      <c r="Q24" s="208"/>
+      <c r="R24" s="209"/>
+      <c r="S24" s="209"/>
+      <c r="T24" s="209"/>
+      <c r="U24" s="209"/>
+      <c r="V24" s="209"/>
+      <c r="W24" s="209"/>
+      <c r="X24" s="209"/>
+      <c r="Y24" s="209"/>
+      <c r="Z24" s="209"/>
+      <c r="AA24" s="209"/>
+      <c r="AB24" s="209"/>
+      <c r="AC24" s="209"/>
+      <c r="AD24" s="209"/>
+      <c r="AE24" s="210"/>
+      <c r="AF24" s="205"/>
+      <c r="AG24" s="206"/>
+      <c r="AH24" s="206"/>
+      <c r="AI24" s="207"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="22"/>
-      <c r="B25" s="163"/>
-      <c r="C25" s="164"/>
-      <c r="D25" s="165"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="167"/>
-      <c r="G25" s="163"/>
-      <c r="H25" s="168"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="170"/>
-      <c r="L25" s="170"/>
-      <c r="M25" s="170"/>
-      <c r="N25" s="170"/>
-      <c r="O25" s="170"/>
-      <c r="P25" s="171"/>
-      <c r="Q25" s="172"/>
-      <c r="R25" s="173"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="173"/>
-      <c r="U25" s="173"/>
-      <c r="V25" s="173"/>
-      <c r="W25" s="173"/>
-      <c r="X25" s="173"/>
-      <c r="Y25" s="173"/>
-      <c r="Z25" s="173"/>
-      <c r="AA25" s="173"/>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="173"/>
-      <c r="AD25" s="173"/>
-      <c r="AE25" s="174"/>
-      <c r="AF25" s="169"/>
-      <c r="AG25" s="170"/>
-      <c r="AH25" s="170"/>
-      <c r="AI25" s="171"/>
+      <c r="B25" s="199"/>
+      <c r="C25" s="200"/>
+      <c r="D25" s="201"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="199"/>
+      <c r="H25" s="204"/>
+      <c r="I25" s="200"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="206"/>
+      <c r="L25" s="206"/>
+      <c r="M25" s="206"/>
+      <c r="N25" s="206"/>
+      <c r="O25" s="206"/>
+      <c r="P25" s="207"/>
+      <c r="Q25" s="208"/>
+      <c r="R25" s="209"/>
+      <c r="S25" s="209"/>
+      <c r="T25" s="209"/>
+      <c r="U25" s="209"/>
+      <c r="V25" s="209"/>
+      <c r="W25" s="209"/>
+      <c r="X25" s="209"/>
+      <c r="Y25" s="209"/>
+      <c r="Z25" s="209"/>
+      <c r="AA25" s="209"/>
+      <c r="AB25" s="209"/>
+      <c r="AC25" s="209"/>
+      <c r="AD25" s="209"/>
+      <c r="AE25" s="210"/>
+      <c r="AF25" s="205"/>
+      <c r="AG25" s="206"/>
+      <c r="AH25" s="206"/>
+      <c r="AI25" s="207"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="22"/>
-      <c r="B26" s="163"/>
-      <c r="C26" s="164"/>
-      <c r="D26" s="165"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="163"/>
-      <c r="H26" s="168"/>
-      <c r="I26" s="164"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="170"/>
-      <c r="L26" s="170"/>
-      <c r="M26" s="170"/>
-      <c r="N26" s="170"/>
-      <c r="O26" s="170"/>
-      <c r="P26" s="171"/>
-      <c r="Q26" s="172"/>
-      <c r="R26" s="173"/>
-      <c r="S26" s="173"/>
-      <c r="T26" s="173"/>
-      <c r="U26" s="173"/>
-      <c r="V26" s="173"/>
-      <c r="W26" s="173"/>
-      <c r="X26" s="173"/>
-      <c r="Y26" s="173"/>
-      <c r="Z26" s="173"/>
-      <c r="AA26" s="173"/>
-      <c r="AB26" s="173"/>
-      <c r="AC26" s="173"/>
-      <c r="AD26" s="173"/>
-      <c r="AE26" s="174"/>
-      <c r="AF26" s="169"/>
-      <c r="AG26" s="170"/>
-      <c r="AH26" s="170"/>
-      <c r="AI26" s="171"/>
+      <c r="B26" s="199"/>
+      <c r="C26" s="200"/>
+      <c r="D26" s="201"/>
+      <c r="E26" s="202"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="199"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="206"/>
+      <c r="L26" s="206"/>
+      <c r="M26" s="206"/>
+      <c r="N26" s="206"/>
+      <c r="O26" s="206"/>
+      <c r="P26" s="207"/>
+      <c r="Q26" s="208"/>
+      <c r="R26" s="209"/>
+      <c r="S26" s="209"/>
+      <c r="T26" s="209"/>
+      <c r="U26" s="209"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="209"/>
+      <c r="X26" s="209"/>
+      <c r="Y26" s="209"/>
+      <c r="Z26" s="209"/>
+      <c r="AA26" s="209"/>
+      <c r="AB26" s="209"/>
+      <c r="AC26" s="209"/>
+      <c r="AD26" s="209"/>
+      <c r="AE26" s="210"/>
+      <c r="AF26" s="205"/>
+      <c r="AG26" s="206"/>
+      <c r="AH26" s="206"/>
+      <c r="AI26" s="207"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="22"/>
-      <c r="B27" s="163"/>
-      <c r="C27" s="164"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="166"/>
-      <c r="F27" s="167"/>
-      <c r="G27" s="163"/>
-      <c r="H27" s="168"/>
-      <c r="I27" s="164"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="170"/>
-      <c r="L27" s="170"/>
-      <c r="M27" s="170"/>
-      <c r="N27" s="170"/>
-      <c r="O27" s="170"/>
-      <c r="P27" s="171"/>
-      <c r="Q27" s="172"/>
-      <c r="R27" s="173"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="173"/>
-      <c r="U27" s="173"/>
-      <c r="V27" s="173"/>
-      <c r="W27" s="173"/>
-      <c r="X27" s="173"/>
-      <c r="Y27" s="173"/>
-      <c r="Z27" s="173"/>
-      <c r="AA27" s="173"/>
-      <c r="AB27" s="173"/>
-      <c r="AC27" s="173"/>
-      <c r="AD27" s="173"/>
-      <c r="AE27" s="174"/>
-      <c r="AF27" s="169"/>
-      <c r="AG27" s="170"/>
-      <c r="AH27" s="170"/>
-      <c r="AI27" s="171"/>
+      <c r="B27" s="199"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="199"/>
+      <c r="H27" s="204"/>
+      <c r="I27" s="200"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="206"/>
+      <c r="L27" s="206"/>
+      <c r="M27" s="206"/>
+      <c r="N27" s="206"/>
+      <c r="O27" s="206"/>
+      <c r="P27" s="207"/>
+      <c r="Q27" s="208"/>
+      <c r="R27" s="209"/>
+      <c r="S27" s="209"/>
+      <c r="T27" s="209"/>
+      <c r="U27" s="209"/>
+      <c r="V27" s="209"/>
+      <c r="W27" s="209"/>
+      <c r="X27" s="209"/>
+      <c r="Y27" s="209"/>
+      <c r="Z27" s="209"/>
+      <c r="AA27" s="209"/>
+      <c r="AB27" s="209"/>
+      <c r="AC27" s="209"/>
+      <c r="AD27" s="209"/>
+      <c r="AE27" s="210"/>
+      <c r="AF27" s="205"/>
+      <c r="AG27" s="206"/>
+      <c r="AH27" s="206"/>
+      <c r="AI27" s="207"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="22"/>
-      <c r="B28" s="163"/>
-      <c r="C28" s="164"/>
-      <c r="D28" s="165"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="168"/>
-      <c r="I28" s="164"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="170"/>
-      <c r="L28" s="170"/>
-      <c r="M28" s="170"/>
-      <c r="N28" s="170"/>
-      <c r="O28" s="170"/>
-      <c r="P28" s="171"/>
-      <c r="Q28" s="172"/>
-      <c r="R28" s="173"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="173"/>
-      <c r="U28" s="173"/>
-      <c r="V28" s="173"/>
-      <c r="W28" s="173"/>
-      <c r="X28" s="173"/>
-      <c r="Y28" s="173"/>
-      <c r="Z28" s="173"/>
-      <c r="AA28" s="173"/>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="173"/>
-      <c r="AD28" s="173"/>
-      <c r="AE28" s="174"/>
-      <c r="AF28" s="169"/>
-      <c r="AG28" s="170"/>
-      <c r="AH28" s="170"/>
-      <c r="AI28" s="171"/>
+      <c r="B28" s="199"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="201"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="199"/>
+      <c r="H28" s="204"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="206"/>
+      <c r="L28" s="206"/>
+      <c r="M28" s="206"/>
+      <c r="N28" s="206"/>
+      <c r="O28" s="206"/>
+      <c r="P28" s="207"/>
+      <c r="Q28" s="208"/>
+      <c r="R28" s="209"/>
+      <c r="S28" s="209"/>
+      <c r="T28" s="209"/>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="209"/>
+      <c r="Z28" s="209"/>
+      <c r="AA28" s="209"/>
+      <c r="AB28" s="209"/>
+      <c r="AC28" s="209"/>
+      <c r="AD28" s="209"/>
+      <c r="AE28" s="210"/>
+      <c r="AF28" s="205"/>
+      <c r="AG28" s="206"/>
+      <c r="AH28" s="206"/>
+      <c r="AI28" s="207"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="22"/>
-      <c r="B29" s="163"/>
-      <c r="C29" s="164"/>
-      <c r="D29" s="165"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
-      <c r="G29" s="163"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="169"/>
-      <c r="K29" s="170"/>
-      <c r="L29" s="170"/>
-      <c r="M29" s="170"/>
-      <c r="N29" s="170"/>
-      <c r="O29" s="170"/>
-      <c r="P29" s="171"/>
-      <c r="Q29" s="172"/>
-      <c r="R29" s="173"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="173"/>
-      <c r="U29" s="173"/>
-      <c r="V29" s="173"/>
-      <c r="W29" s="173"/>
-      <c r="X29" s="173"/>
-      <c r="Y29" s="173"/>
-      <c r="Z29" s="173"/>
-      <c r="AA29" s="173"/>
-      <c r="AB29" s="173"/>
-      <c r="AC29" s="173"/>
-      <c r="AD29" s="173"/>
-      <c r="AE29" s="174"/>
-      <c r="AF29" s="169"/>
-      <c r="AG29" s="170"/>
-      <c r="AH29" s="170"/>
-      <c r="AI29" s="171"/>
+      <c r="B29" s="199"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="201"/>
+      <c r="E29" s="202"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="199"/>
+      <c r="H29" s="204"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="206"/>
+      <c r="L29" s="206"/>
+      <c r="M29" s="206"/>
+      <c r="N29" s="206"/>
+      <c r="O29" s="206"/>
+      <c r="P29" s="207"/>
+      <c r="Q29" s="208"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="209"/>
+      <c r="T29" s="209"/>
+      <c r="U29" s="209"/>
+      <c r="V29" s="209"/>
+      <c r="W29" s="209"/>
+      <c r="X29" s="209"/>
+      <c r="Y29" s="209"/>
+      <c r="Z29" s="209"/>
+      <c r="AA29" s="209"/>
+      <c r="AB29" s="209"/>
+      <c r="AC29" s="209"/>
+      <c r="AD29" s="209"/>
+      <c r="AE29" s="210"/>
+      <c r="AF29" s="205"/>
+      <c r="AG29" s="206"/>
+      <c r="AH29" s="206"/>
+      <c r="AI29" s="207"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="22"/>
-      <c r="B30" s="163"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="166"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="163"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="170"/>
-      <c r="L30" s="170"/>
-      <c r="M30" s="170"/>
-      <c r="N30" s="170"/>
-      <c r="O30" s="170"/>
-      <c r="P30" s="171"/>
-      <c r="Q30" s="172"/>
-      <c r="R30" s="173"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="173"/>
-      <c r="U30" s="173"/>
-      <c r="V30" s="173"/>
-      <c r="W30" s="173"/>
-      <c r="X30" s="173"/>
-      <c r="Y30" s="173"/>
-      <c r="Z30" s="173"/>
-      <c r="AA30" s="173"/>
-      <c r="AB30" s="173"/>
-      <c r="AC30" s="173"/>
-      <c r="AD30" s="173"/>
-      <c r="AE30" s="174"/>
-      <c r="AF30" s="169"/>
-      <c r="AG30" s="170"/>
-      <c r="AH30" s="170"/>
-      <c r="AI30" s="171"/>
+      <c r="B30" s="199"/>
+      <c r="C30" s="200"/>
+      <c r="D30" s="201"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="199"/>
+      <c r="H30" s="204"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="206"/>
+      <c r="L30" s="206"/>
+      <c r="M30" s="206"/>
+      <c r="N30" s="206"/>
+      <c r="O30" s="206"/>
+      <c r="P30" s="207"/>
+      <c r="Q30" s="208"/>
+      <c r="R30" s="209"/>
+      <c r="S30" s="209"/>
+      <c r="T30" s="209"/>
+      <c r="U30" s="209"/>
+      <c r="V30" s="209"/>
+      <c r="W30" s="209"/>
+      <c r="X30" s="209"/>
+      <c r="Y30" s="209"/>
+      <c r="Z30" s="209"/>
+      <c r="AA30" s="209"/>
+      <c r="AB30" s="209"/>
+      <c r="AC30" s="209"/>
+      <c r="AD30" s="209"/>
+      <c r="AE30" s="210"/>
+      <c r="AF30" s="205"/>
+      <c r="AG30" s="206"/>
+      <c r="AH30" s="206"/>
+      <c r="AI30" s="207"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="22"/>
-      <c r="B31" s="163"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="165"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="167"/>
-      <c r="G31" s="163"/>
-      <c r="H31" s="168"/>
-      <c r="I31" s="164"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="170"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="170"/>
-      <c r="P31" s="171"/>
-      <c r="Q31" s="172"/>
-      <c r="R31" s="173"/>
-      <c r="S31" s="173"/>
-      <c r="T31" s="173"/>
-      <c r="U31" s="173"/>
-      <c r="V31" s="173"/>
-      <c r="W31" s="173"/>
-      <c r="X31" s="173"/>
-      <c r="Y31" s="173"/>
-      <c r="Z31" s="173"/>
-      <c r="AA31" s="173"/>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="173"/>
-      <c r="AD31" s="173"/>
-      <c r="AE31" s="174"/>
-      <c r="AF31" s="169"/>
-      <c r="AG31" s="170"/>
-      <c r="AH31" s="170"/>
-      <c r="AI31" s="171"/>
+      <c r="B31" s="199"/>
+      <c r="C31" s="200"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="199"/>
+      <c r="H31" s="204"/>
+      <c r="I31" s="200"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="206"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="206"/>
+      <c r="N31" s="206"/>
+      <c r="O31" s="206"/>
+      <c r="P31" s="207"/>
+      <c r="Q31" s="208"/>
+      <c r="R31" s="209"/>
+      <c r="S31" s="209"/>
+      <c r="T31" s="209"/>
+      <c r="U31" s="209"/>
+      <c r="V31" s="209"/>
+      <c r="W31" s="209"/>
+      <c r="X31" s="209"/>
+      <c r="Y31" s="209"/>
+      <c r="Z31" s="209"/>
+      <c r="AA31" s="209"/>
+      <c r="AB31" s="209"/>
+      <c r="AC31" s="209"/>
+      <c r="AD31" s="209"/>
+      <c r="AE31" s="210"/>
+      <c r="AF31" s="205"/>
+      <c r="AG31" s="206"/>
+      <c r="AH31" s="206"/>
+      <c r="AI31" s="207"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="22"/>
-      <c r="B32" s="163"/>
-      <c r="C32" s="164"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="166"/>
-      <c r="F32" s="167"/>
-      <c r="G32" s="163"/>
-      <c r="H32" s="168"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
-      <c r="P32" s="171"/>
-      <c r="Q32" s="172"/>
-      <c r="R32" s="173"/>
-      <c r="S32" s="173"/>
-      <c r="T32" s="173"/>
-      <c r="U32" s="173"/>
-      <c r="V32" s="173"/>
-      <c r="W32" s="173"/>
-      <c r="X32" s="173"/>
-      <c r="Y32" s="173"/>
-      <c r="Z32" s="173"/>
-      <c r="AA32" s="173"/>
-      <c r="AB32" s="173"/>
-      <c r="AC32" s="173"/>
-      <c r="AD32" s="173"/>
-      <c r="AE32" s="174"/>
-      <c r="AF32" s="169"/>
-      <c r="AG32" s="170"/>
-      <c r="AH32" s="170"/>
-      <c r="AI32" s="171"/>
+      <c r="B32" s="199"/>
+      <c r="C32" s="200"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="199"/>
+      <c r="H32" s="204"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="206"/>
+      <c r="M32" s="206"/>
+      <c r="N32" s="206"/>
+      <c r="O32" s="206"/>
+      <c r="P32" s="207"/>
+      <c r="Q32" s="208"/>
+      <c r="R32" s="209"/>
+      <c r="S32" s="209"/>
+      <c r="T32" s="209"/>
+      <c r="U32" s="209"/>
+      <c r="V32" s="209"/>
+      <c r="W32" s="209"/>
+      <c r="X32" s="209"/>
+      <c r="Y32" s="209"/>
+      <c r="Z32" s="209"/>
+      <c r="AA32" s="209"/>
+      <c r="AB32" s="209"/>
+      <c r="AC32" s="209"/>
+      <c r="AD32" s="209"/>
+      <c r="AE32" s="210"/>
+      <c r="AF32" s="205"/>
+      <c r="AG32" s="206"/>
+      <c r="AH32" s="206"/>
+      <c r="AI32" s="207"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="22"/>
-      <c r="B33" s="163"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="165"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="167"/>
-      <c r="G33" s="163"/>
-      <c r="H33" s="168"/>
-      <c r="I33" s="164"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="170"/>
-      <c r="L33" s="170"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="170"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="171"/>
-      <c r="Q33" s="172"/>
-      <c r="R33" s="173"/>
-      <c r="S33" s="173"/>
-      <c r="T33" s="173"/>
-      <c r="U33" s="173"/>
-      <c r="V33" s="173"/>
-      <c r="W33" s="173"/>
-      <c r="X33" s="173"/>
-      <c r="Y33" s="173"/>
-      <c r="Z33" s="173"/>
-      <c r="AA33" s="173"/>
-      <c r="AB33" s="173"/>
-      <c r="AC33" s="173"/>
-      <c r="AD33" s="173"/>
-      <c r="AE33" s="174"/>
-      <c r="AF33" s="169"/>
-      <c r="AG33" s="170"/>
-      <c r="AH33" s="170"/>
-      <c r="AI33" s="171"/>
+      <c r="B33" s="199"/>
+      <c r="C33" s="200"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="202"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="199"/>
+      <c r="H33" s="204"/>
+      <c r="I33" s="200"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="206"/>
+      <c r="L33" s="206"/>
+      <c r="M33" s="206"/>
+      <c r="N33" s="206"/>
+      <c r="O33" s="206"/>
+      <c r="P33" s="207"/>
+      <c r="Q33" s="208"/>
+      <c r="R33" s="209"/>
+      <c r="S33" s="209"/>
+      <c r="T33" s="209"/>
+      <c r="U33" s="209"/>
+      <c r="V33" s="209"/>
+      <c r="W33" s="209"/>
+      <c r="X33" s="209"/>
+      <c r="Y33" s="209"/>
+      <c r="Z33" s="209"/>
+      <c r="AA33" s="209"/>
+      <c r="AB33" s="209"/>
+      <c r="AC33" s="209"/>
+      <c r="AD33" s="209"/>
+      <c r="AE33" s="210"/>
+      <c r="AF33" s="205"/>
+      <c r="AG33" s="206"/>
+      <c r="AH33" s="206"/>
+      <c r="AI33" s="207"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -11712,162 +11868,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/030_設計ドキュメント/010_フォーマット/110_テスト仕様書/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -12025,8 +12025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -12066,8 +12066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -12101,8 +12101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -12138,8 +12138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -12171,8 +12171,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -12204,8 +12204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -12237,8 +12237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -12270,8 +12270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -12307,8 +12307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -12340,8 +12340,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -12373,8 +12373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -12408,8 +12408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -12441,8 +12441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -12474,8 +12474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -12507,8 +12507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -12544,8 +12544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -12577,8 +12577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -12614,8 +12614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -12647,8 +12647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -12682,8 +12682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -12715,8 +12715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -12748,8 +12748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -12781,8 +12781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -12816,8 +12816,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -12849,8 +12849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -12884,8 +12884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -12923,8 +12923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -12956,8 +12956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -12989,8 +12989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -13022,8 +13022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -13059,8 +13059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -13092,8 +13092,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -13133,8 +13133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -13166,8 +13166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13199,8 +13199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -13234,8 +13234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -13267,8 +13267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -13300,8 +13300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -13335,8 +13335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -13368,8 +13368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -13403,8 +13403,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -13436,8 +13436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -13469,8 +13469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -13502,8 +13502,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -13535,8 +13535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -13568,8 +13568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -13603,8 +13603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -13638,8 +13638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -13673,8 +13673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -13710,8 +13710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -13743,8 +13743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -13776,8 +13776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -13809,8 +13809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -13842,8 +13842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -13877,8 +13877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -13910,8 +13910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -13943,8 +13943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -13976,8 +13976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -14009,8 +14009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -14042,8 +14042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -14075,8 +14075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -14108,8 +14108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -14143,8 +14143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14178,8 +14178,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -14211,8 +14211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -14244,8 +14244,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -14277,8 +14277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -14310,8 +14310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -14349,8 +14349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -14382,8 +14382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -14417,8 +14417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -14452,8 +14452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -14485,8 +14485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -14520,8 +14520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -14555,8 +14555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -14594,8 +14594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -14629,8 +14629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -14664,8 +14664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -14703,8 +14703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -14736,8 +14736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -14771,8 +14771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -14806,8 +14806,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -14839,8 +14839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -14874,8 +14874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -14913,8 +14913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -14946,8 +14946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -14979,8 +14979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -15012,8 +15012,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -15045,8 +15045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -15080,8 +15080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -15113,8 +15113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15146,8 +15146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -15179,8 +15179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -15212,8 +15212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -15247,8 +15247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -15288,8 +15288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -15327,8 +15327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -15360,8 +15360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -15399,8 +15399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -15438,8 +15438,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -15471,8 +15471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -15512,8 +15512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -15547,8 +15547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -15580,8 +15580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -15613,8 +15613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -15648,8 +15648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -15681,8 +15681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -15714,8 +15714,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -15747,8 +15747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -15780,8 +15780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -15815,8 +15815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -15848,8 +15848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -15881,8 +15881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -15914,8 +15914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -15947,8 +15947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -15982,8 +15982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -16019,8 +16019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -16058,8 +16058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -16093,8 +16093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16126,8 +16126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -16159,8 +16159,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -16200,8 +16200,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -16235,8 +16235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -16268,8 +16268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -16301,8 +16301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -16336,8 +16336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -16369,8 +16369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -16406,8 +16406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -16445,8 +16445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -16480,8 +16480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -16515,8 +16515,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -16550,8 +16550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -16585,8 +16585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -16620,8 +16620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -16653,8 +16653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -16686,8 +16686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -16719,8 +16719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -16752,8 +16752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -16785,8 +16785,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -16822,8 +16822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -16855,8 +16855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -16890,8 +16890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -16923,8 +16923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -16956,8 +16956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -16989,8 +16989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -17022,8 +17022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -17055,8 +17055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17088,8 +17088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17121,8 +17121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17154,8 +17154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -17187,8 +17187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -17220,8 +17220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -17255,8 +17255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -17288,8 +17288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -17321,8 +17321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -17354,8 +17354,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -17387,8 +17387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -17420,8 +17420,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -17453,8 +17453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -17488,8 +17488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -17521,8 +17521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -17554,8 +17554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -17587,8 +17587,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -17620,8 +17620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -17653,8 +17653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -17686,8 +17686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -17719,8 +17719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -17752,8 +17752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -17787,8 +17787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -17822,8 +17822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -17863,8 +17863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -17900,8 +17900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -17937,8 +17937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -17978,8 +17978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -18013,8 +18013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18046,8 +18046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18081,8 +18081,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18114,8 +18114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18151,8 +18151,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -18190,8 +18190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -18223,8 +18223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -18256,8 +18256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -18289,8 +18289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -18322,8 +18322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -18355,8 +18355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -18388,8 +18388,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -18423,8 +18423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -18460,8 +18460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -18493,8 +18493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -18526,8 +18526,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -18559,8 +18559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -18592,8 +18592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -18625,8 +18625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -18658,8 +18658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -18691,8 +18691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -18724,8 +18724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -18757,8 +18757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -18790,8 +18790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -18823,8 +18823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -18856,8 +18856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -18893,8 +18893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -18926,8 +18926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -18959,8 +18959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -18992,8 +18992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19025,8 +19025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19058,8 +19058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19091,8 +19091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19124,8 +19124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -19157,8 +19157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -19190,8 +19190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -19223,8 +19223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -19256,8 +19256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -19289,8 +19289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -19322,8 +19322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -19355,8 +19355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -19390,8 +19390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -19423,8 +19423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -19456,8 +19456,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -19491,8 +19491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -19526,8 +19526,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -19567,8 +19567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -19602,8 +19602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -19635,8 +19635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -19668,8 +19668,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -19701,8 +19701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -19734,8 +19734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -19769,8 +19769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -19802,8 +19802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -19835,8 +19835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -19868,8 +19868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -19901,8 +19901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -19936,8 +19936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -19975,8 +19975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20016,8 +20016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20049,8 +20049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20086,8 +20086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -20119,8 +20119,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -20158,8 +20158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -20193,8 +20193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -20228,8 +20228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -20263,8 +20263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -20300,8 +20300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -20333,8 +20333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -20368,8 +20368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -20401,8 +20401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -20434,8 +20434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -20467,8 +20467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -20500,8 +20500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -20533,8 +20533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -20566,8 +20566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -20599,8 +20599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -20632,8 +20632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -20665,8 +20665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -20698,8 +20698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -20733,8 +20733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -20766,8 +20766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -20799,8 +20799,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -20832,8 +20832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -20865,8 +20865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -20898,8 +20898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -20933,8 +20933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -20966,8 +20966,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -20999,8 +20999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21032,8 +21032,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21065,8 +21065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -21098,8 +21098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -21131,8 +21131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -21164,8 +21164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -21199,8 +21199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -21240,8 +21240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -21273,8 +21273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -21306,8 +21306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -21339,8 +21339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -21378,8 +21378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -21413,8 +21413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -21448,8 +21448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -21483,8 +21483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -21520,8 +21520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -21553,8 +21553,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -21586,8 +21586,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -21619,8 +21619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -21652,8 +21652,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -21685,8 +21685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -21718,8 +21718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -21751,8 +21751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -21958,8 +21958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -21999,8 +21999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -22034,8 +22034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -22071,8 +22071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -22104,8 +22104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -22137,8 +22137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -22170,8 +22170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -22203,8 +22203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -22240,8 +22240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -22273,8 +22273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -22306,8 +22306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -22341,8 +22341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -22374,8 +22374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -22407,8 +22407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -22440,8 +22440,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -22477,8 +22477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -22510,8 +22510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -22547,8 +22547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -22580,8 +22580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -22615,8 +22615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -22648,8 +22648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -22681,8 +22681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -22714,8 +22714,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -22749,8 +22749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -22782,8 +22782,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -22817,8 +22817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -22856,8 +22856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -22889,8 +22889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -22922,8 +22922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -22955,8 +22955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -22992,8 +22992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -23025,8 +23025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -23066,8 +23066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -23099,8 +23099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -23132,8 +23132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -23167,8 +23167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -23200,8 +23200,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -23233,8 +23233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -23268,8 +23268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -23301,8 +23301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -23336,8 +23336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -23369,8 +23369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -23402,8 +23402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -23435,8 +23435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -23468,8 +23468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -23501,8 +23501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -23536,8 +23536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -23571,8 +23571,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -23606,8 +23606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -23643,8 +23643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -23676,8 +23676,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -23709,8 +23709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -23742,8 +23742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -23775,8 +23775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -23810,8 +23810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -23843,8 +23843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -23876,8 +23876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -23909,8 +23909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -23942,8 +23942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -23975,8 +23975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -24008,8 +24008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -24041,8 +24041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -24076,8 +24076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -24111,8 +24111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -24144,8 +24144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -24177,8 +24177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -24210,8 +24210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -24243,8 +24243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -24282,8 +24282,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -24315,8 +24315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -24350,8 +24350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -24385,8 +24385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -24418,8 +24418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -24453,8 +24453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -24488,8 +24488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -24527,8 +24527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -24562,8 +24562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -24597,8 +24597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -24636,8 +24636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -24669,8 +24669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -24704,8 +24704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -24739,8 +24739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -24772,8 +24772,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -24807,8 +24807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -24846,8 +24846,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -24879,8 +24879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -24912,8 +24912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -24945,8 +24945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -24978,8 +24978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -25013,8 +25013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -25046,8 +25046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -25079,8 +25079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -25112,8 +25112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -25145,8 +25145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -25180,8 +25180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -25221,8 +25221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -25260,8 +25260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -25293,8 +25293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -25332,8 +25332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -25371,8 +25371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -25404,8 +25404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -25445,8 +25445,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -25480,8 +25480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -25513,8 +25513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -25546,8 +25546,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -25581,8 +25581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -25614,8 +25614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -25647,8 +25647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -25680,8 +25680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -25713,8 +25713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -25748,8 +25748,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -25781,8 +25781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -25814,8 +25814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -25847,8 +25847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -25880,8 +25880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -25915,8 +25915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -25952,8 +25952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -25991,8 +25991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -26026,8 +26026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -26059,8 +26059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -26092,8 +26092,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -26133,8 +26133,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -26168,8 +26168,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -26201,8 +26201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -26234,8 +26234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -26269,8 +26269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -26302,8 +26302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -26339,8 +26339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -26378,8 +26378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -26413,8 +26413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -26448,8 +26448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -26483,8 +26483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -26518,8 +26518,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -26553,8 +26553,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -26586,8 +26586,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -26619,8 +26619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -26652,8 +26652,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -26685,8 +26685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -26718,8 +26718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -26755,8 +26755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -26788,8 +26788,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -26823,8 +26823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -26856,8 +26856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -26889,8 +26889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -26922,8 +26922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -26955,8 +26955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -26988,8 +26988,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -27021,8 +27021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -27054,8 +27054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -27087,8 +27087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -27120,8 +27120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -27153,8 +27153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -27188,8 +27188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -27221,8 +27221,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -27254,8 +27254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -27287,8 +27287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -27320,8 +27320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -27353,8 +27353,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -27386,8 +27386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -27421,8 +27421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -27454,8 +27454,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -27487,8 +27487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -27520,8 +27520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -27553,8 +27553,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -27586,8 +27586,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -27619,8 +27619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -27652,8 +27652,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -27685,8 +27685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -27720,8 +27720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -27755,8 +27755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -27796,8 +27796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -27833,8 +27833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -27870,8 +27870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -27911,8 +27911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -27946,8 +27946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -27979,8 +27979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -28014,8 +28014,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -28047,8 +28047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -28084,8 +28084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -28123,8 +28123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -28156,8 +28156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -28189,8 +28189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -28222,8 +28222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -28255,8 +28255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -28288,8 +28288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -28321,8 +28321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -28356,8 +28356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -28393,8 +28393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -28426,8 +28426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -28459,8 +28459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -28492,8 +28492,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -28525,8 +28525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -28558,8 +28558,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -28591,8 +28591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -28624,8 +28624,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -28657,8 +28657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -28690,8 +28690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -28723,8 +28723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -28756,8 +28756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -28789,8 +28789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -28826,8 +28826,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -28859,8 +28859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -28892,8 +28892,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -28925,8 +28925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -28958,8 +28958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -28991,8 +28991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -29024,8 +29024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -29057,8 +29057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -29090,8 +29090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -29123,8 +29123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -29156,8 +29156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -29189,8 +29189,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -29222,8 +29222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -29255,8 +29255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -29288,8 +29288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -29323,8 +29323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -29356,8 +29356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -29389,8 +29389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -29424,8 +29424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -29459,8 +29459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -29500,8 +29500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -29535,8 +29535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -29568,8 +29568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -29601,8 +29601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -29634,8 +29634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -29667,8 +29667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -29702,8 +29702,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -29735,8 +29735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -29768,8 +29768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -29801,8 +29801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -29834,8 +29834,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -29869,8 +29869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -29908,8 +29908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -29949,8 +29949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -29982,8 +29982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -30019,8 +30019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -30052,8 +30052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -30091,8 +30091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -30126,8 +30126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -30161,8 +30161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -30196,8 +30196,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -30233,8 +30233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -30266,8 +30266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -30301,8 +30301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -30334,8 +30334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -30367,8 +30367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -30400,8 +30400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -30433,8 +30433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -30466,8 +30466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -30499,8 +30499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -30532,8 +30532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -30565,8 +30565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -30598,8 +30598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -30631,8 +30631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -30666,8 +30666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -30699,8 +30699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -30732,8 +30732,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -30765,8 +30765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -30798,8 +30798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -30831,8 +30831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -30866,8 +30866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -30899,8 +30899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -30932,8 +30932,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -30965,8 +30965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -30998,8 +30998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -31031,8 +31031,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -31064,8 +31064,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -31097,8 +31097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -31132,8 +31132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -31173,8 +31173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -31206,8 +31206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -31239,8 +31239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -31272,8 +31272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -31311,8 +31311,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -31346,8 +31346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -31381,8 +31381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -31416,8 +31416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -31453,8 +31453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -31486,8 +31486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -31519,8 +31519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -31552,8 +31552,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -31585,8 +31585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -31618,8 +31618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -31651,8 +31651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -31684,8 +31684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -31717,8 +31717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -31758,8 +31758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -31791,8 +31791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -31824,8 +31824,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -31857,8 +31857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-5-1</v>
       </c>
@@ -31890,8 +31890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-6-1</v>
       </c>
@@ -31923,8 +31923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-7-1</v>
       </c>
@@ -31956,8 +31956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-8-1</v>
       </c>
@@ -31989,8 +31989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-9-1</v>
       </c>
@@ -32022,8 +32022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-10-1</v>
       </c>
@@ -32055,8 +32055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-11-1</v>
       </c>
@@ -32088,8 +32088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-12-1</v>
       </c>
@@ -32121,8 +32121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-13-1</v>
       </c>
@@ -32154,8 +32154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-1</v>
       </c>
@@ -32187,8 +32187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-15-1</v>
       </c>
@@ -32220,8 +32220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-16-1</v>
       </c>
@@ -32253,8 +32253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-1</v>
       </c>
@@ -32286,8 +32286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-1</v>
       </c>
@@ -32319,8 +32319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-1</v>
       </c>
@@ -32352,8 +32352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-20-1</v>
       </c>
@@ -32385,8 +32385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-21-1</v>
       </c>
@@ -32418,8 +32418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -32453,8 +32453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -32486,8 +32486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -32521,8 +32521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-1</v>
       </c>
@@ -32554,8 +32554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -32589,8 +32589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -32624,8 +32624,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -32657,8 +32657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -32690,8 +32690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -32723,8 +32723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -32756,8 +32756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -32789,8 +32789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F328),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F328)&gt;0)*ROW($F$11:F328),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J328),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -32822,8 +32822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F329),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F329)&gt;0)*ROW($F$11:F329),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J329),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -32855,8 +32855,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F330),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F330)&gt;0)*ROW($F$11:F330),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J330),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -32888,8 +32888,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F331),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F331)&gt;0)*ROW($F$11:F331),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J331),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -32923,8 +32923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F332),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F332)&gt;0)*ROW($F$11:F332),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J332),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -32958,8 +32958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F333),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F333)&gt;0)*ROW($F$11:F333),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J333),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -32995,8 +32995,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F334),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F334)&gt;0)*ROW($F$11:F334),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J334),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -33030,8 +33030,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F335),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F335)&gt;0)*ROW($F$11:F335),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J335),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-2-1</v>
       </c>
@@ -33063,8 +33063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F336),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F336)&gt;0)*ROW($F$11:F336),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J336),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-3-1</v>
       </c>
@@ -33096,8 +33096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F337),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F337)&gt;0)*ROW($F$11:F337),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J337),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-4-1</v>
       </c>
@@ -33129,8 +33129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F338),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F338)&gt;0)*ROW($F$11:F338),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J338),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -33166,8 +33166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F339),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F339)&gt;0)*ROW($F$11:F339),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J339),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-2-1</v>
       </c>
@@ -33199,8 +33199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F340),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F340)&gt;0)*ROW($F$11:F340),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J340),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-3-1</v>
       </c>
@@ -33232,8 +33232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F341),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F341)&gt;0)*ROW($F$11:F341),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J341),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-1</v>
       </c>
@@ -33269,8 +33269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F342),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F342)&gt;0)*ROW($F$11:F342),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J342),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-1</v>
       </c>
@@ -33302,8 +33302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F343),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F343)&gt;0)*ROW($F$11:F343),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J343),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-1</v>
       </c>
@@ -33335,8 +33335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F344),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F344)&gt;0)*ROW($F$11:F344),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J344),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-4-1</v>
       </c>
@@ -33368,8 +33368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F345),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F345)&gt;0)*ROW($F$11:F345),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J345),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-5-1</v>
       </c>
@@ -33401,8 +33401,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F346),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F346)&gt;0)*ROW($F$11:F346),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J346),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-6-1</v>
       </c>
@@ -33434,8 +33434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F347),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F347)&gt;0)*ROW($F$11:F347),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J347),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-7-1</v>
       </c>
@@ -33467,8 +33467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F348),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F348)&gt;0)*ROW($F$11:F348),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J348),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-8-1</v>
       </c>
@@ -33500,8 +33500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F349),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F349)&gt;0)*ROW($F$11:F349),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J349),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-9-1</v>
       </c>
@@ -33533,8 +33533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F350),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F350)&gt;0)*ROW($F$11:F350),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J350),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-10-1</v>
       </c>
@@ -33566,8 +33566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F351),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F351)&gt;0)*ROW($F$11:F351),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J351),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-11-1</v>
       </c>
@@ -33599,8 +33599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F352),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F352)&gt;0)*ROW($F$11:F352),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J352),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-12-1</v>
       </c>
@@ -33632,8 +33632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F353),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F353)&gt;0)*ROW($F$11:F353),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J353),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-13-1</v>
       </c>
@@ -33665,8 +33665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F354),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F354)&gt;0)*ROW($F$11:F354),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J354),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-14-1</v>
       </c>
@@ -33698,8 +33698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F355),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F355)&gt;0)*ROW($F$11:F355),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J355),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-1-1</v>
       </c>
@@ -33733,8 +33733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F356),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F356)&gt;0)*ROW($F$11:F356),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J356),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-2-1</v>
       </c>
@@ -33766,8 +33766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F357),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F357)&gt;0)*ROW($F$11:F357),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J357),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-3-1</v>
       </c>
@@ -33799,8 +33799,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F358),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F358)&gt;0)*ROW($F$11:F358),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J358),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-4-1</v>
       </c>
@@ -33832,8 +33832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F359),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F359)&gt;0)*ROW($F$11:F359),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J359),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-5-1</v>
       </c>
@@ -33865,8 +33865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F360),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F360)&gt;0)*ROW($F$11:F360),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J360),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-6-1</v>
       </c>
@@ -33898,8 +33898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F361),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F361)&gt;0)*ROW($F$11:F361),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J361),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-7-1</v>
       </c>
@@ -33931,8 +33931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F362),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F362)&gt;0)*ROW($F$11:F362),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J362),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-1-1</v>
       </c>
@@ -33972,8 +33972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F363),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F363)&gt;0)*ROW($F$11:F363),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J363),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-2-1</v>
       </c>
@@ -34005,8 +34005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F364),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F364)&gt;0)*ROW($F$11:F364),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J364),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-3-1</v>
       </c>
@@ -34038,8 +34038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F365),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F365)&gt;0)*ROW($F$11:F365),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J365),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-4-1</v>
       </c>
@@ -34071,8 +34071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F366),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F366)&gt;0)*ROW($F$11:F366),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J366),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-5-1</v>
       </c>
@@ -34104,8 +34104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F367),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F367)&gt;0)*ROW($F$11:F367),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J367),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-1-1</v>
       </c>
@@ -34141,8 +34141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F368),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F368)&gt;0)*ROW($F$11:F368),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J368),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-2-1</v>
       </c>
@@ -34174,8 +34174,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F369),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F369)&gt;0)*ROW($F$11:F369),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J369),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-3-1</v>
       </c>
@@ -34207,8 +34207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F370),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F370)&gt;0)*ROW($F$11:F370),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J370),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-4-1</v>
       </c>
@@ -34240,8 +34240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F371),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F371)&gt;0)*ROW($F$11:F371),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J371),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-5-1</v>
       </c>
@@ -34273,8 +34273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F372),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F372)&gt;0)*ROW($F$11:F372),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J372),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-1</v>
       </c>
@@ -34312,8 +34312,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F373),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F373)&gt;0)*ROW($F$11:F373),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J373),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-2-1</v>
       </c>
@@ -34345,8 +34345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F374),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F374)&gt;0)*ROW($F$11:F374),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J374),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-1</v>
       </c>
@@ -34378,8 +34378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F375),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F375)&gt;0)*ROW($F$11:F375),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J375),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-4-1</v>
       </c>
@@ -34411,8 +34411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F376),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F376)&gt;0)*ROW($F$11:F376),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J376),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-5-1</v>
       </c>
@@ -34444,8 +34444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F377),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F377)&gt;0)*ROW($F$11:F377),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J377),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-6-1</v>
       </c>
@@ -34477,8 +34477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F378),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F378)&gt;0)*ROW($F$11:F378),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J378),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>116-1-1</v>
       </c>
@@ -34514,8 +34514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F379),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F379)&gt;0)*ROW($F$11:F379),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J379),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-1</v>
       </c>
@@ -34551,8 +34551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F380),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F380)&gt;0)*ROW($F$11:F380),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J380),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>118-1-1</v>
       </c>
@@ -34588,8 +34588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F381),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F381)&gt;0)*ROW($F$11:F381),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J381),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-1-1</v>
       </c>
@@ -34629,8 +34629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F382),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F382)&gt;0)*ROW($F$11:F382),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J382),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-2-1</v>
       </c>
@@ -34827,11 +34827,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D11),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -34864,11 +34864,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D12),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -34897,11 +34897,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D13),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -34930,11 +34930,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D14),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -34963,11 +34963,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D15),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -34998,11 +34998,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D16),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -35031,11 +35031,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D17),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -35064,11 +35064,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D18),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -35097,11 +35097,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D19),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -35132,11 +35132,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D20),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
